--- a/input/ACB_Voicebot_TLS.xlsx
+++ b/input/ACB_Voicebot_TLS.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/hieunguyen/cursor_project/auto_generate_test_cases/input/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4B85AA4A-0480-284E-A35C-D00BE847DA2F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3B841F8A-84AB-D544-B701-ABFA303DD8D6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="46460" yWindow="1840" windowWidth="19220" windowHeight="19940" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="640" windowWidth="29400" windowHeight="16960" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="27" state="hidden" r:id="rId1"/>
@@ -7817,65 +7817,8 @@
     <xf numFmtId="0" fontId="77" fillId="30" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="65" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="65" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="65" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="69" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="69" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="65" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="18" fillId="7" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -7901,6 +7844,12 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
@@ -7913,13 +7862,61 @@
     <xf numFmtId="0" fontId="19" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="69" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="69" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="16" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="65" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="65" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="65" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="65" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="65" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -7931,10 +7928,28 @@
     <xf numFmtId="0" fontId="16" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="55" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="66" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="63" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="63" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="63" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="63" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="75" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -7946,19 +7961,7 @@
     <xf numFmtId="0" fontId="43" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="63" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="63" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="55" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="66" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="65" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
@@ -8018,9 +8021,6 @@
     <xf numFmtId="0" fontId="16" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="65" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
@@ -8033,11 +8033,38 @@
     <xf numFmtId="0" fontId="18" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="65" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="19" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="19" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
@@ -8079,30 +8106,6 @@
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="43" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -8192,14 +8195,14 @@
     <xf numFmtId="0" fontId="0" fillId="14" borderId="17" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -8209,6 +8212,18 @@
     </xf>
     <xf numFmtId="0" fontId="26" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="7" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="7" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="7" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -8225,19 +8240,7 @@
     <xf numFmtId="0" fontId="17" fillId="7" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="7" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="13" fillId="7" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="7" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="7" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="7" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="71" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -8248,9 +8251,6 @@
     </xf>
     <xf numFmtId="0" fontId="30" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="7" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -9305,8 +9305,8 @@
       <c r="F1" s="188"/>
       <c r="G1" s="188"/>
       <c r="H1" s="105"/>
-      <c r="I1" s="413"/>
-      <c r="J1" s="413"/>
+      <c r="I1" s="394"/>
+      <c r="J1" s="394"/>
       <c r="L1" s="30"/>
       <c r="M1" s="30"/>
     </row>
@@ -9347,13 +9347,13 @@
       </c>
     </row>
     <row r="3" spans="1:138" ht="44.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="481">
+      <c r="A3" s="468">
         <v>1</v>
       </c>
-      <c r="B3" s="416" t="s">
+      <c r="B3" s="397" t="s">
         <v>50</v>
       </c>
-      <c r="C3" s="483" t="s">
+      <c r="C3" s="470" t="s">
         <v>320</v>
       </c>
       <c r="D3" s="73" t="s">
@@ -9381,9 +9381,9 @@
       </c>
     </row>
     <row r="4" spans="1:138" ht="45" x14ac:dyDescent="0.2">
-      <c r="A4" s="482"/>
-      <c r="B4" s="417"/>
-      <c r="C4" s="484"/>
+      <c r="A4" s="469"/>
+      <c r="B4" s="398"/>
+      <c r="C4" s="471"/>
       <c r="D4" s="73" t="s">
         <v>56</v>
       </c>
@@ -9405,9 +9405,9 @@
       <c r="M4" s="76"/>
     </row>
     <row r="5" spans="1:138" ht="75" x14ac:dyDescent="0.2">
-      <c r="A5" s="482"/>
-      <c r="B5" s="417"/>
-      <c r="C5" s="484"/>
+      <c r="A5" s="469"/>
+      <c r="B5" s="398"/>
+      <c r="C5" s="471"/>
       <c r="D5" s="73" t="s">
         <v>55</v>
       </c>
@@ -9432,9 +9432,9 @@
       </c>
     </row>
     <row r="6" spans="1:138" ht="225" x14ac:dyDescent="0.2">
-      <c r="A6" s="482"/>
-      <c r="B6" s="417"/>
-      <c r="C6" s="484"/>
+      <c r="A6" s="469"/>
+      <c r="B6" s="398"/>
+      <c r="C6" s="471"/>
       <c r="D6" s="73" t="s">
         <v>63</v>
       </c>
@@ -9457,9 +9457,9 @@
       <c r="M6" s="76"/>
     </row>
     <row r="7" spans="1:138" ht="165" x14ac:dyDescent="0.2">
-      <c r="A7" s="482"/>
-      <c r="B7" s="417"/>
-      <c r="C7" s="484"/>
+      <c r="A7" s="469"/>
+      <c r="B7" s="398"/>
+      <c r="C7" s="471"/>
       <c r="D7" s="73" t="s">
         <v>68</v>
       </c>
@@ -9481,9 +9481,9 @@
       <c r="M7" s="76"/>
     </row>
     <row r="8" spans="1:138" ht="60" x14ac:dyDescent="0.2">
-      <c r="A8" s="482"/>
-      <c r="B8" s="417"/>
-      <c r="C8" s="484"/>
+      <c r="A8" s="469"/>
+      <c r="B8" s="398"/>
+      <c r="C8" s="471"/>
       <c r="D8" s="73" t="s">
         <v>72</v>
       </c>
@@ -9505,9 +9505,9 @@
       <c r="M8" s="76"/>
     </row>
     <row r="9" spans="1:138" ht="60" x14ac:dyDescent="0.2">
-      <c r="A9" s="482"/>
-      <c r="B9" s="417"/>
-      <c r="C9" s="484"/>
+      <c r="A9" s="469"/>
+      <c r="B9" s="398"/>
+      <c r="C9" s="471"/>
       <c r="D9" s="73" t="s">
         <v>86</v>
       </c>
@@ -9531,9 +9531,9 @@
       <c r="M9" s="76"/>
     </row>
     <row r="10" spans="1:138" s="42" customFormat="1" ht="30" x14ac:dyDescent="0.2">
-      <c r="A10" s="482"/>
-      <c r="B10" s="417"/>
-      <c r="C10" s="484"/>
+      <c r="A10" s="469"/>
+      <c r="B10" s="398"/>
+      <c r="C10" s="471"/>
       <c r="D10" s="73" t="s">
         <v>92</v>
       </c>
@@ -9683,9 +9683,9 @@
       <c r="EH10" s="41"/>
     </row>
     <row r="11" spans="1:138" ht="60" x14ac:dyDescent="0.2">
-      <c r="A11" s="482"/>
-      <c r="B11" s="417"/>
-      <c r="C11" s="485"/>
+      <c r="A11" s="469"/>
+      <c r="B11" s="398"/>
+      <c r="C11" s="472"/>
       <c r="D11" s="73" t="s">
         <v>277</v>
       </c>
@@ -9707,13 +9707,13 @@
       <c r="M11" s="76"/>
     </row>
     <row r="12" spans="1:138" ht="45" x14ac:dyDescent="0.2">
-      <c r="A12" s="486">
+      <c r="A12" s="473">
         <v>1.1000000000000001</v>
       </c>
-      <c r="B12" s="487" t="s">
+      <c r="B12" s="474" t="s">
         <v>98</v>
       </c>
-      <c r="C12" s="421" t="s">
+      <c r="C12" s="404" t="s">
         <v>99</v>
       </c>
       <c r="D12" s="73" t="s">
@@ -9739,9 +9739,9 @@
       <c r="M12" s="76"/>
     </row>
     <row r="13" spans="1:138" ht="60" x14ac:dyDescent="0.2">
-      <c r="A13" s="486"/>
-      <c r="B13" s="487"/>
-      <c r="C13" s="422"/>
+      <c r="A13" s="473"/>
+      <c r="B13" s="474"/>
+      <c r="C13" s="405"/>
       <c r="D13" s="73" t="s">
         <v>56</v>
       </c>
@@ -9767,9 +9767,9 @@
       <c r="M13" s="76"/>
     </row>
     <row r="14" spans="1:138" ht="409.6" x14ac:dyDescent="0.2">
-      <c r="A14" s="486"/>
-      <c r="B14" s="487"/>
-      <c r="C14" s="422"/>
+      <c r="A14" s="473"/>
+      <c r="B14" s="474"/>
+      <c r="C14" s="405"/>
       <c r="D14" s="237" t="s">
         <v>279</v>
       </c>
@@ -9816,9 +9816,9 @@
       <c r="M14" s="76"/>
     </row>
     <row r="15" spans="1:138" ht="30" x14ac:dyDescent="0.2">
-      <c r="A15" s="486"/>
-      <c r="B15" s="487"/>
-      <c r="C15" s="422"/>
+      <c r="A15" s="473"/>
+      <c r="B15" s="474"/>
+      <c r="C15" s="405"/>
       <c r="D15" s="237" t="s">
         <v>281</v>
       </c>
@@ -9837,9 +9837,9 @@
       <c r="M15" s="76"/>
     </row>
     <row r="16" spans="1:138" s="47" customFormat="1" ht="409.6" x14ac:dyDescent="0.2">
-      <c r="A16" s="486"/>
-      <c r="B16" s="487"/>
-      <c r="C16" s="422"/>
+      <c r="A16" s="473"/>
+      <c r="B16" s="474"/>
+      <c r="C16" s="405"/>
       <c r="D16" s="76" t="s">
         <v>106</v>
       </c>
@@ -10000,9 +10000,9 @@
       <c r="EH16" s="36"/>
     </row>
     <row r="17" spans="1:138" s="47" customFormat="1" ht="409.6" x14ac:dyDescent="0.2">
-      <c r="A17" s="486"/>
-      <c r="B17" s="487"/>
-      <c r="C17" s="422"/>
+      <c r="A17" s="473"/>
+      <c r="B17" s="474"/>
+      <c r="C17" s="405"/>
       <c r="D17" s="76" t="s">
         <v>92</v>
       </c>
@@ -10163,9 +10163,9 @@
       <c r="EH17" s="36"/>
     </row>
     <row r="18" spans="1:138" ht="60" x14ac:dyDescent="0.2">
-      <c r="A18" s="481"/>
-      <c r="B18" s="488"/>
-      <c r="C18" s="422"/>
+      <c r="A18" s="468"/>
+      <c r="B18" s="475"/>
+      <c r="C18" s="405"/>
       <c r="D18" s="78" t="s">
         <v>277</v>
       </c>
@@ -10187,13 +10187,13 @@
       <c r="M18" s="76"/>
     </row>
     <row r="19" spans="1:138" ht="45" x14ac:dyDescent="0.2">
-      <c r="A19" s="467">
+      <c r="A19" s="476">
         <v>2</v>
       </c>
-      <c r="B19" s="468" t="s">
+      <c r="B19" s="477" t="s">
         <v>109</v>
       </c>
-      <c r="C19" s="469" t="s">
+      <c r="C19" s="478" t="s">
         <v>321</v>
       </c>
       <c r="D19" s="73" t="s">
@@ -10219,9 +10219,9 @@
       <c r="M19" s="76"/>
     </row>
     <row r="20" spans="1:138" ht="60" x14ac:dyDescent="0.2">
-      <c r="A20" s="467"/>
-      <c r="B20" s="468"/>
-      <c r="C20" s="470"/>
+      <c r="A20" s="476"/>
+      <c r="B20" s="477"/>
+      <c r="C20" s="479"/>
       <c r="D20" s="73" t="s">
         <v>56</v>
       </c>
@@ -10247,9 +10247,9 @@
       <c r="M20" s="76"/>
     </row>
     <row r="21" spans="1:138" ht="409.6" x14ac:dyDescent="0.2">
-      <c r="A21" s="467"/>
-      <c r="B21" s="468"/>
-      <c r="C21" s="470"/>
+      <c r="A21" s="476"/>
+      <c r="B21" s="477"/>
+      <c r="C21" s="479"/>
       <c r="D21" s="240" t="s">
         <v>279</v>
       </c>
@@ -10280,9 +10280,9 @@
       <c r="M21" s="76"/>
     </row>
     <row r="22" spans="1:138" ht="30" x14ac:dyDescent="0.2">
-      <c r="A22" s="467"/>
-      <c r="B22" s="468"/>
-      <c r="C22" s="471"/>
+      <c r="A22" s="476"/>
+      <c r="B22" s="477"/>
+      <c r="C22" s="480"/>
       <c r="D22" s="237" t="s">
         <v>281</v>
       </c>
@@ -10300,9 +10300,9 @@
       <c r="M22" s="76"/>
     </row>
     <row r="23" spans="1:138" s="47" customFormat="1" ht="409.6" x14ac:dyDescent="0.2">
-      <c r="A23" s="467"/>
-      <c r="B23" s="468"/>
-      <c r="C23" s="470"/>
+      <c r="A23" s="476"/>
+      <c r="B23" s="477"/>
+      <c r="C23" s="479"/>
       <c r="D23" s="88" t="s">
         <v>114</v>
       </c>
@@ -10459,9 +10459,9 @@
       <c r="EH23" s="36"/>
     </row>
     <row r="24" spans="1:138" s="47" customFormat="1" ht="409.6" x14ac:dyDescent="0.2">
-      <c r="A24" s="467"/>
-      <c r="B24" s="468"/>
-      <c r="C24" s="470"/>
+      <c r="A24" s="476"/>
+      <c r="B24" s="477"/>
+      <c r="C24" s="479"/>
       <c r="D24" s="86" t="s">
         <v>92</v>
       </c>
@@ -10618,9 +10618,9 @@
       <c r="EH24" s="36"/>
     </row>
     <row r="25" spans="1:138" ht="196.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A25" s="467"/>
-      <c r="B25" s="468"/>
-      <c r="C25" s="471"/>
+      <c r="A25" s="476"/>
+      <c r="B25" s="477"/>
+      <c r="C25" s="480"/>
       <c r="D25" s="76" t="s">
         <v>94</v>
       </c>
@@ -10642,13 +10642,13 @@
       <c r="M25" s="76"/>
     </row>
     <row r="26" spans="1:138" ht="60" x14ac:dyDescent="0.2">
-      <c r="A26" s="472">
+      <c r="A26" s="481">
         <v>2.1</v>
       </c>
-      <c r="B26" s="475" t="s">
+      <c r="B26" s="484" t="s">
         <v>116</v>
       </c>
-      <c r="C26" s="478" t="s">
+      <c r="C26" s="487" t="s">
         <v>117</v>
       </c>
       <c r="D26" s="237" t="s">
@@ -10674,9 +10674,9 @@
       <c r="M26" s="76"/>
     </row>
     <row r="27" spans="1:138" ht="60" x14ac:dyDescent="0.2">
-      <c r="A27" s="473"/>
-      <c r="B27" s="476"/>
-      <c r="C27" s="479"/>
+      <c r="A27" s="482"/>
+      <c r="B27" s="485"/>
+      <c r="C27" s="488"/>
       <c r="D27" s="237" t="s">
         <v>122</v>
       </c>
@@ -10696,9 +10696,9 @@
       <c r="M27" s="76"/>
     </row>
     <row r="28" spans="1:138" ht="135" x14ac:dyDescent="0.2">
-      <c r="A28" s="473"/>
-      <c r="B28" s="476"/>
-      <c r="C28" s="479"/>
+      <c r="A28" s="482"/>
+      <c r="B28" s="485"/>
+      <c r="C28" s="488"/>
       <c r="D28" s="76" t="s">
         <v>130</v>
       </c>
@@ -10722,9 +10722,9 @@
       <c r="M28" s="76"/>
     </row>
     <row r="29" spans="1:138" ht="75" x14ac:dyDescent="0.2">
-      <c r="A29" s="473"/>
-      <c r="B29" s="476"/>
-      <c r="C29" s="479"/>
+      <c r="A29" s="482"/>
+      <c r="B29" s="485"/>
+      <c r="C29" s="488"/>
       <c r="D29" s="189" t="s">
         <v>55</v>
       </c>
@@ -10748,9 +10748,9 @@
       <c r="M29" s="76"/>
     </row>
     <row r="30" spans="1:138" ht="45" x14ac:dyDescent="0.2">
-      <c r="A30" s="473"/>
-      <c r="B30" s="476"/>
-      <c r="C30" s="479"/>
+      <c r="A30" s="482"/>
+      <c r="B30" s="485"/>
+      <c r="C30" s="488"/>
       <c r="D30" s="37" t="s">
         <v>134</v>
       </c>
@@ -10774,9 +10774,9 @@
       </c>
     </row>
     <row r="31" spans="1:138" ht="60" x14ac:dyDescent="0.2">
-      <c r="A31" s="473"/>
-      <c r="B31" s="476"/>
-      <c r="C31" s="479"/>
+      <c r="A31" s="482"/>
+      <c r="B31" s="485"/>
+      <c r="C31" s="488"/>
       <c r="D31" s="88" t="s">
         <v>114</v>
       </c>
@@ -10800,9 +10800,9 @@
       <c r="M31" s="76"/>
     </row>
     <row r="32" spans="1:138" ht="30" x14ac:dyDescent="0.2">
-      <c r="A32" s="473"/>
-      <c r="B32" s="476"/>
-      <c r="C32" s="479"/>
+      <c r="A32" s="482"/>
+      <c r="B32" s="485"/>
+      <c r="C32" s="488"/>
       <c r="D32" s="86" t="s">
         <v>92</v>
       </c>
@@ -10826,9 +10826,9 @@
       <c r="M32" s="76"/>
     </row>
     <row r="33" spans="1:13" ht="45" x14ac:dyDescent="0.2">
-      <c r="A33" s="474"/>
-      <c r="B33" s="477"/>
-      <c r="C33" s="480"/>
+      <c r="A33" s="483"/>
+      <c r="B33" s="486"/>
+      <c r="C33" s="489"/>
       <c r="D33" s="76" t="s">
         <v>94</v>
       </c>
@@ -10855,6 +10855,12 @@
   </sheetData>
   <autoFilter ref="A2:EH33" xr:uid="{92218EDD-6442-41B5-9565-D949ECDDA5BC}"/>
   <mergeCells count="13">
+    <mergeCell ref="A19:A25"/>
+    <mergeCell ref="B19:B25"/>
+    <mergeCell ref="C19:C25"/>
+    <mergeCell ref="A26:A33"/>
+    <mergeCell ref="B26:B33"/>
+    <mergeCell ref="C26:C33"/>
     <mergeCell ref="I1:J1"/>
     <mergeCell ref="A3:A11"/>
     <mergeCell ref="B3:B11"/>
@@ -10862,12 +10868,6 @@
     <mergeCell ref="A12:A18"/>
     <mergeCell ref="B12:B18"/>
     <mergeCell ref="C12:C18"/>
-    <mergeCell ref="A19:A25"/>
-    <mergeCell ref="B19:B25"/>
-    <mergeCell ref="C19:C25"/>
-    <mergeCell ref="A26:A33"/>
-    <mergeCell ref="B26:B33"/>
-    <mergeCell ref="C26:C33"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait"/>
@@ -10906,11 +10906,11 @@
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A4" s="4"/>
-      <c r="B4" s="452" t="s">
+      <c r="B4" s="453" t="s">
         <v>157</v>
       </c>
-      <c r="C4" s="453"/>
-      <c r="D4" s="454"/>
+      <c r="C4" s="454"/>
+      <c r="D4" s="455"/>
       <c r="E4" s="153" t="s">
         <v>158</v>
       </c>
@@ -10933,12 +10933,12 @@
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="B7" s="455" t="s">
+      <c r="B7" s="456" t="s">
         <v>163</v>
       </c>
-      <c r="C7" s="455"/>
-      <c r="D7" s="455"/>
-      <c r="E7" s="455"/>
+      <c r="C7" s="456"/>
+      <c r="D7" s="456"/>
+      <c r="E7" s="456"/>
       <c r="F7" s="222"/>
     </row>
     <row r="8" spans="1:6" ht="16" x14ac:dyDescent="0.2">
@@ -11006,12 +11006,12 @@
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="B12" s="455" t="s">
+      <c r="B12" s="456" t="s">
         <v>175</v>
       </c>
-      <c r="C12" s="455"/>
-      <c r="D12" s="455"/>
-      <c r="E12" s="455"/>
+      <c r="C12" s="456"/>
+      <c r="D12" s="456"/>
+      <c r="E12" s="456"/>
       <c r="F12" s="223"/>
     </row>
     <row r="13" spans="1:6" ht="16" x14ac:dyDescent="0.2">
@@ -11418,51 +11418,51 @@
       </c>
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="C45" s="456" t="s">
+      <c r="C45" s="457" t="s">
         <v>125</v>
       </c>
-      <c r="D45" s="465" t="s">
+      <c r="D45" s="466" t="s">
         <v>259</v>
       </c>
-      <c r="E45" s="466" t="s">
+      <c r="E45" s="467" t="s">
         <v>205</v>
       </c>
       <c r="F45" s="250"/>
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="C46" s="456"/>
-      <c r="D46" s="465"/>
-      <c r="E46" s="466"/>
+      <c r="C46" s="457"/>
+      <c r="D46" s="466"/>
+      <c r="E46" s="467"/>
       <c r="F46" s="250"/>
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="C47" s="456"/>
-      <c r="D47" s="465"/>
-      <c r="E47" s="466"/>
+      <c r="C47" s="457"/>
+      <c r="D47" s="466"/>
+      <c r="E47" s="467"/>
       <c r="F47" s="250"/>
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="C48" s="450" t="s">
+      <c r="C48" s="451" t="s">
         <v>133</v>
       </c>
-      <c r="D48" s="450" t="s">
+      <c r="D48" s="451" t="s">
         <v>206</v>
       </c>
-      <c r="E48" s="451" t="s">
+      <c r="E48" s="452" t="s">
         <v>205</v>
       </c>
       <c r="F48" s="250"/>
     </row>
     <row r="49" spans="3:6" x14ac:dyDescent="0.2">
-      <c r="C49" s="450"/>
-      <c r="D49" s="450"/>
-      <c r="E49" s="451"/>
+      <c r="C49" s="451"/>
+      <c r="D49" s="451"/>
+      <c r="E49" s="452"/>
       <c r="F49" s="250"/>
     </row>
     <row r="50" spans="3:6" x14ac:dyDescent="0.2">
-      <c r="C50" s="450"/>
-      <c r="D50" s="450"/>
-      <c r="E50" s="451"/>
+      <c r="C50" s="451"/>
+      <c r="D50" s="451"/>
+      <c r="E50" s="452"/>
       <c r="F50" s="250"/>
     </row>
     <row r="51" spans="3:6" x14ac:dyDescent="0.2">
@@ -11593,7 +11593,7 @@
       </c>
     </row>
     <row r="2" spans="2:7" s="219" customFormat="1" ht="409.6" x14ac:dyDescent="0.2">
-      <c r="B2" s="489" t="s">
+      <c r="B2" s="490" t="s">
         <v>327</v>
       </c>
       <c r="C2" s="282" t="s">
@@ -11607,13 +11607,13 @@
       </c>
     </row>
     <row r="3" spans="2:7" ht="96" x14ac:dyDescent="0.2">
-      <c r="B3" s="490"/>
+      <c r="B3" s="491"/>
       <c r="C3" s="220" t="s">
         <v>331</v>
       </c>
     </row>
     <row r="4" spans="2:7" ht="137.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B4" s="490"/>
+      <c r="B4" s="491"/>
       <c r="C4" s="221" t="s">
         <v>332</v>
       </c>
@@ -11666,8 +11666,8 @@
       <c r="F1" s="188"/>
       <c r="G1" s="188"/>
       <c r="H1" s="105"/>
-      <c r="I1" s="413"/>
-      <c r="J1" s="413"/>
+      <c r="I1" s="394"/>
+      <c r="J1" s="394"/>
       <c r="L1" s="30"/>
       <c r="M1" s="30"/>
     </row>
@@ -11708,13 +11708,13 @@
       </c>
     </row>
     <row r="3" spans="1:138" ht="44.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="481">
+      <c r="A3" s="468">
         <v>1</v>
       </c>
-      <c r="B3" s="416" t="s">
+      <c r="B3" s="397" t="s">
         <v>50</v>
       </c>
-      <c r="C3" s="483" t="s">
+      <c r="C3" s="470" t="s">
         <v>335</v>
       </c>
       <c r="D3" s="73" t="s">
@@ -11742,9 +11742,9 @@
       </c>
     </row>
     <row r="4" spans="1:138" ht="45" x14ac:dyDescent="0.2">
-      <c r="A4" s="482"/>
-      <c r="B4" s="417"/>
-      <c r="C4" s="484"/>
+      <c r="A4" s="469"/>
+      <c r="B4" s="398"/>
+      <c r="C4" s="471"/>
       <c r="D4" s="73" t="s">
         <v>56</v>
       </c>
@@ -11766,9 +11766,9 @@
       <c r="M4" s="76"/>
     </row>
     <row r="5" spans="1:138" ht="75" x14ac:dyDescent="0.2">
-      <c r="A5" s="482"/>
-      <c r="B5" s="417"/>
-      <c r="C5" s="484"/>
+      <c r="A5" s="469"/>
+      <c r="B5" s="398"/>
+      <c r="C5" s="471"/>
       <c r="D5" s="73" t="s">
         <v>55</v>
       </c>
@@ -11790,9 +11790,9 @@
       <c r="M5" s="76"/>
     </row>
     <row r="6" spans="1:138" ht="240" x14ac:dyDescent="0.2">
-      <c r="A6" s="482"/>
-      <c r="B6" s="417"/>
-      <c r="C6" s="484"/>
+      <c r="A6" s="469"/>
+      <c r="B6" s="398"/>
+      <c r="C6" s="471"/>
       <c r="D6" s="73" t="s">
         <v>63</v>
       </c>
@@ -11815,9 +11815,9 @@
       <c r="M6" s="76"/>
     </row>
     <row r="7" spans="1:138" ht="180" x14ac:dyDescent="0.2">
-      <c r="A7" s="482"/>
-      <c r="B7" s="417"/>
-      <c r="C7" s="484"/>
+      <c r="A7" s="469"/>
+      <c r="B7" s="398"/>
+      <c r="C7" s="471"/>
       <c r="D7" s="73" t="s">
         <v>68</v>
       </c>
@@ -11839,9 +11839,9 @@
       <c r="M7" s="76"/>
     </row>
     <row r="8" spans="1:138" ht="60" x14ac:dyDescent="0.2">
-      <c r="A8" s="482"/>
-      <c r="B8" s="417"/>
-      <c r="C8" s="484"/>
+      <c r="A8" s="469"/>
+      <c r="B8" s="398"/>
+      <c r="C8" s="471"/>
       <c r="D8" s="73" t="s">
         <v>72</v>
       </c>
@@ -11863,9 +11863,9 @@
       <c r="M8" s="76"/>
     </row>
     <row r="9" spans="1:138" ht="60" x14ac:dyDescent="0.2">
-      <c r="A9" s="482"/>
-      <c r="B9" s="417"/>
-      <c r="C9" s="484"/>
+      <c r="A9" s="469"/>
+      <c r="B9" s="398"/>
+      <c r="C9" s="471"/>
       <c r="D9" s="73" t="s">
         <v>86</v>
       </c>
@@ -11889,9 +11889,9 @@
       <c r="M9" s="76"/>
     </row>
     <row r="10" spans="1:138" s="42" customFormat="1" ht="30" x14ac:dyDescent="0.2">
-      <c r="A10" s="482"/>
-      <c r="B10" s="417"/>
-      <c r="C10" s="484"/>
+      <c r="A10" s="469"/>
+      <c r="B10" s="398"/>
+      <c r="C10" s="471"/>
       <c r="D10" s="73" t="s">
         <v>92</v>
       </c>
@@ -12041,9 +12041,9 @@
       <c r="EH10" s="41"/>
     </row>
     <row r="11" spans="1:138" ht="60" x14ac:dyDescent="0.2">
-      <c r="A11" s="482"/>
-      <c r="B11" s="417"/>
-      <c r="C11" s="485"/>
+      <c r="A11" s="469"/>
+      <c r="B11" s="398"/>
+      <c r="C11" s="472"/>
       <c r="D11" s="73" t="s">
         <v>277</v>
       </c>
@@ -12065,13 +12065,13 @@
       <c r="M11" s="76"/>
     </row>
     <row r="12" spans="1:138" ht="45" x14ac:dyDescent="0.2">
-      <c r="A12" s="486">
+      <c r="A12" s="473">
         <v>1.1000000000000001</v>
       </c>
-      <c r="B12" s="487" t="s">
+      <c r="B12" s="474" t="s">
         <v>98</v>
       </c>
-      <c r="C12" s="421" t="s">
+      <c r="C12" s="404" t="s">
         <v>99</v>
       </c>
       <c r="D12" s="73" t="s">
@@ -12097,9 +12097,9 @@
       <c r="M12" s="76"/>
     </row>
     <row r="13" spans="1:138" ht="60" x14ac:dyDescent="0.2">
-      <c r="A13" s="486"/>
-      <c r="B13" s="487"/>
-      <c r="C13" s="422"/>
+      <c r="A13" s="473"/>
+      <c r="B13" s="474"/>
+      <c r="C13" s="405"/>
       <c r="D13" s="73" t="s">
         <v>56</v>
       </c>
@@ -12125,9 +12125,9 @@
       <c r="M13" s="76"/>
     </row>
     <row r="14" spans="1:138" ht="409.6" x14ac:dyDescent="0.2">
-      <c r="A14" s="486"/>
-      <c r="B14" s="487"/>
-      <c r="C14" s="422"/>
+      <c r="A14" s="473"/>
+      <c r="B14" s="474"/>
+      <c r="C14" s="405"/>
       <c r="D14" s="237" t="s">
         <v>279</v>
       </c>
@@ -12163,9 +12163,9 @@
       <c r="M14" s="76"/>
     </row>
     <row r="15" spans="1:138" ht="30" x14ac:dyDescent="0.2">
-      <c r="A15" s="486"/>
-      <c r="B15" s="487"/>
-      <c r="C15" s="422"/>
+      <c r="A15" s="473"/>
+      <c r="B15" s="474"/>
+      <c r="C15" s="405"/>
       <c r="D15" s="237" t="s">
         <v>281</v>
       </c>
@@ -12184,9 +12184,9 @@
       <c r="M15" s="76"/>
     </row>
     <row r="16" spans="1:138" s="47" customFormat="1" ht="409.6" x14ac:dyDescent="0.2">
-      <c r="A16" s="486"/>
-      <c r="B16" s="487"/>
-      <c r="C16" s="422"/>
+      <c r="A16" s="473"/>
+      <c r="B16" s="474"/>
+      <c r="C16" s="405"/>
       <c r="D16" s="76" t="s">
         <v>106</v>
       </c>
@@ -12347,9 +12347,9 @@
       <c r="EH16" s="36"/>
     </row>
     <row r="17" spans="1:138" s="47" customFormat="1" ht="409.6" x14ac:dyDescent="0.2">
-      <c r="A17" s="486"/>
-      <c r="B17" s="487"/>
-      <c r="C17" s="422"/>
+      <c r="A17" s="473"/>
+      <c r="B17" s="474"/>
+      <c r="C17" s="405"/>
       <c r="D17" s="76" t="s">
         <v>92</v>
       </c>
@@ -12510,9 +12510,9 @@
       <c r="EH17" s="36"/>
     </row>
     <row r="18" spans="1:138" ht="60" x14ac:dyDescent="0.2">
-      <c r="A18" s="481"/>
-      <c r="B18" s="488"/>
-      <c r="C18" s="422"/>
+      <c r="A18" s="468"/>
+      <c r="B18" s="475"/>
+      <c r="C18" s="405"/>
       <c r="D18" s="78" t="s">
         <v>277</v>
       </c>
@@ -12534,13 +12534,13 @@
       <c r="M18" s="76"/>
     </row>
     <row r="19" spans="1:138" ht="45" x14ac:dyDescent="0.2">
-      <c r="A19" s="467">
+      <c r="A19" s="476">
         <v>2</v>
       </c>
-      <c r="B19" s="468" t="s">
+      <c r="B19" s="477" t="s">
         <v>109</v>
       </c>
-      <c r="C19" s="469" t="s">
+      <c r="C19" s="478" t="s">
         <v>321</v>
       </c>
       <c r="D19" s="73" t="s">
@@ -12566,9 +12566,9 @@
       <c r="M19" s="76"/>
     </row>
     <row r="20" spans="1:138" ht="60" x14ac:dyDescent="0.2">
-      <c r="A20" s="467"/>
-      <c r="B20" s="468"/>
-      <c r="C20" s="470"/>
+      <c r="A20" s="476"/>
+      <c r="B20" s="477"/>
+      <c r="C20" s="479"/>
       <c r="D20" s="73" t="s">
         <v>56</v>
       </c>
@@ -12594,9 +12594,9 @@
       <c r="M20" s="76"/>
     </row>
     <row r="21" spans="1:138" ht="409.6" x14ac:dyDescent="0.2">
-      <c r="A21" s="467"/>
-      <c r="B21" s="468"/>
-      <c r="C21" s="470"/>
+      <c r="A21" s="476"/>
+      <c r="B21" s="477"/>
+      <c r="C21" s="479"/>
       <c r="D21" s="240" t="s">
         <v>279</v>
       </c>
@@ -12627,9 +12627,9 @@
       <c r="M21" s="76"/>
     </row>
     <row r="22" spans="1:138" ht="30" x14ac:dyDescent="0.2">
-      <c r="A22" s="467"/>
-      <c r="B22" s="468"/>
-      <c r="C22" s="471"/>
+      <c r="A22" s="476"/>
+      <c r="B22" s="477"/>
+      <c r="C22" s="480"/>
       <c r="D22" s="237" t="s">
         <v>281</v>
       </c>
@@ -12647,9 +12647,9 @@
       <c r="M22" s="76"/>
     </row>
     <row r="23" spans="1:138" s="47" customFormat="1" ht="409.6" x14ac:dyDescent="0.2">
-      <c r="A23" s="467"/>
-      <c r="B23" s="468"/>
-      <c r="C23" s="470"/>
+      <c r="A23" s="476"/>
+      <c r="B23" s="477"/>
+      <c r="C23" s="479"/>
       <c r="D23" s="88" t="s">
         <v>114</v>
       </c>
@@ -12806,9 +12806,9 @@
       <c r="EH23" s="36"/>
     </row>
     <row r="24" spans="1:138" s="47" customFormat="1" ht="409.6" x14ac:dyDescent="0.2">
-      <c r="A24" s="467"/>
-      <c r="B24" s="468"/>
-      <c r="C24" s="470"/>
+      <c r="A24" s="476"/>
+      <c r="B24" s="477"/>
+      <c r="C24" s="479"/>
       <c r="D24" s="86" t="s">
         <v>92</v>
       </c>
@@ -12965,9 +12965,9 @@
       <c r="EH24" s="36"/>
     </row>
     <row r="25" spans="1:138" ht="196.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A25" s="467"/>
-      <c r="B25" s="468"/>
-      <c r="C25" s="471"/>
+      <c r="A25" s="476"/>
+      <c r="B25" s="477"/>
+      <c r="C25" s="480"/>
       <c r="D25" s="76" t="s">
         <v>94</v>
       </c>
@@ -12989,13 +12989,13 @@
       <c r="M25" s="76"/>
     </row>
     <row r="26" spans="1:138" ht="60" x14ac:dyDescent="0.2">
-      <c r="A26" s="472">
+      <c r="A26" s="481">
         <v>2.1</v>
       </c>
-      <c r="B26" s="475" t="s">
+      <c r="B26" s="484" t="s">
         <v>116</v>
       </c>
-      <c r="C26" s="478" t="s">
+      <c r="C26" s="487" t="s">
         <v>117</v>
       </c>
       <c r="D26" s="237" t="s">
@@ -13021,9 +13021,9 @@
       <c r="M26" s="76"/>
     </row>
     <row r="27" spans="1:138" ht="60" x14ac:dyDescent="0.2">
-      <c r="A27" s="473"/>
-      <c r="B27" s="476"/>
-      <c r="C27" s="479"/>
+      <c r="A27" s="482"/>
+      <c r="B27" s="485"/>
+      <c r="C27" s="488"/>
       <c r="D27" s="237" t="s">
         <v>122</v>
       </c>
@@ -13043,9 +13043,9 @@
       <c r="M27" s="76"/>
     </row>
     <row r="28" spans="1:138" ht="135" x14ac:dyDescent="0.2">
-      <c r="A28" s="473"/>
-      <c r="B28" s="476"/>
-      <c r="C28" s="479"/>
+      <c r="A28" s="482"/>
+      <c r="B28" s="485"/>
+      <c r="C28" s="488"/>
       <c r="D28" s="76" t="s">
         <v>130</v>
       </c>
@@ -13069,9 +13069,9 @@
       <c r="M28" s="76"/>
     </row>
     <row r="29" spans="1:138" ht="75" x14ac:dyDescent="0.2">
-      <c r="A29" s="473"/>
-      <c r="B29" s="476"/>
-      <c r="C29" s="479"/>
+      <c r="A29" s="482"/>
+      <c r="B29" s="485"/>
+      <c r="C29" s="488"/>
       <c r="D29" s="189" t="s">
         <v>55</v>
       </c>
@@ -13095,9 +13095,9 @@
       <c r="M29" s="76"/>
     </row>
     <row r="30" spans="1:138" ht="45" x14ac:dyDescent="0.2">
-      <c r="A30" s="473"/>
-      <c r="B30" s="476"/>
-      <c r="C30" s="479"/>
+      <c r="A30" s="482"/>
+      <c r="B30" s="485"/>
+      <c r="C30" s="488"/>
       <c r="D30" s="37" t="s">
         <v>134</v>
       </c>
@@ -13121,9 +13121,9 @@
       </c>
     </row>
     <row r="31" spans="1:138" ht="60" x14ac:dyDescent="0.2">
-      <c r="A31" s="473"/>
-      <c r="B31" s="476"/>
-      <c r="C31" s="479"/>
+      <c r="A31" s="482"/>
+      <c r="B31" s="485"/>
+      <c r="C31" s="488"/>
       <c r="D31" s="88" t="s">
         <v>114</v>
       </c>
@@ -13147,9 +13147,9 @@
       <c r="M31" s="76"/>
     </row>
     <row r="32" spans="1:138" ht="30" x14ac:dyDescent="0.2">
-      <c r="A32" s="473"/>
-      <c r="B32" s="476"/>
-      <c r="C32" s="479"/>
+      <c r="A32" s="482"/>
+      <c r="B32" s="485"/>
+      <c r="C32" s="488"/>
       <c r="D32" s="86" t="s">
         <v>92</v>
       </c>
@@ -13173,9 +13173,9 @@
       <c r="M32" s="76"/>
     </row>
     <row r="33" spans="1:13" ht="45" x14ac:dyDescent="0.2">
-      <c r="A33" s="474"/>
-      <c r="B33" s="477"/>
-      <c r="C33" s="480"/>
+      <c r="A33" s="483"/>
+      <c r="B33" s="486"/>
+      <c r="C33" s="489"/>
       <c r="D33" s="76" t="s">
         <v>94</v>
       </c>
@@ -13197,13 +13197,13 @@
       <c r="M33" s="76"/>
     </row>
     <row r="34" spans="1:13" ht="90" x14ac:dyDescent="0.2">
-      <c r="A34" s="491">
+      <c r="A34" s="492">
         <v>3</v>
       </c>
-      <c r="B34" s="494" t="s">
+      <c r="B34" s="495" t="s">
         <v>336</v>
       </c>
-      <c r="C34" s="497" t="s">
+      <c r="C34" s="498" t="s">
         <v>337</v>
       </c>
       <c r="D34" s="208" t="s">
@@ -13229,9 +13229,9 @@
       <c r="M34" s="76"/>
     </row>
     <row r="35" spans="1:13" ht="135" x14ac:dyDescent="0.2">
-      <c r="A35" s="492"/>
-      <c r="B35" s="495"/>
-      <c r="C35" s="498"/>
+      <c r="A35" s="493"/>
+      <c r="B35" s="496"/>
+      <c r="C35" s="499"/>
       <c r="D35" s="208" t="s">
         <v>341</v>
       </c>
@@ -13253,9 +13253,9 @@
       <c r="M35" s="76"/>
     </row>
     <row r="36" spans="1:13" ht="90" x14ac:dyDescent="0.2">
-      <c r="A36" s="492"/>
-      <c r="B36" s="495"/>
-      <c r="C36" s="498"/>
+      <c r="A36" s="493"/>
+      <c r="B36" s="496"/>
+      <c r="C36" s="499"/>
       <c r="D36" s="209" t="s">
         <v>114</v>
       </c>
@@ -13279,9 +13279,9 @@
       <c r="M36" s="76"/>
     </row>
     <row r="37" spans="1:13" ht="90" x14ac:dyDescent="0.2">
-      <c r="A37" s="492"/>
-      <c r="B37" s="495"/>
-      <c r="C37" s="498"/>
+      <c r="A37" s="493"/>
+      <c r="B37" s="496"/>
+      <c r="C37" s="499"/>
       <c r="D37" s="215" t="s">
         <v>92</v>
       </c>
@@ -13305,9 +13305,9 @@
       <c r="M37" s="76"/>
     </row>
     <row r="38" spans="1:13" ht="90" x14ac:dyDescent="0.2">
-      <c r="A38" s="493"/>
-      <c r="B38" s="496"/>
-      <c r="C38" s="499"/>
+      <c r="A38" s="494"/>
+      <c r="B38" s="497"/>
+      <c r="C38" s="500"/>
       <c r="D38" s="216" t="s">
         <v>94</v>
       </c>
@@ -13334,13 +13334,6 @@
   </sheetData>
   <autoFilter ref="A2:EH34" xr:uid="{92218EDD-6442-41B5-9565-D949ECDDA5BC}"/>
   <mergeCells count="16">
-    <mergeCell ref="I1:J1"/>
-    <mergeCell ref="A3:A11"/>
-    <mergeCell ref="B3:B11"/>
-    <mergeCell ref="C3:C11"/>
-    <mergeCell ref="A12:A18"/>
-    <mergeCell ref="B12:B18"/>
-    <mergeCell ref="C12:C18"/>
     <mergeCell ref="A34:A38"/>
     <mergeCell ref="B34:B38"/>
     <mergeCell ref="C34:C38"/>
@@ -13350,6 +13343,13 @@
     <mergeCell ref="A26:A33"/>
     <mergeCell ref="B26:B33"/>
     <mergeCell ref="C26:C33"/>
+    <mergeCell ref="I1:J1"/>
+    <mergeCell ref="A3:A11"/>
+    <mergeCell ref="B3:B11"/>
+    <mergeCell ref="C3:C11"/>
+    <mergeCell ref="A12:A18"/>
+    <mergeCell ref="B12:B18"/>
+    <mergeCell ref="C12:C18"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait"/>
@@ -13388,8 +13388,8 @@
       <c r="F1" s="188"/>
       <c r="G1" s="188"/>
       <c r="H1" s="105"/>
-      <c r="I1" s="413"/>
-      <c r="J1" s="413"/>
+      <c r="I1" s="394"/>
+      <c r="J1" s="394"/>
       <c r="L1" s="30"/>
       <c r="M1" s="30"/>
     </row>
@@ -13430,13 +13430,13 @@
       </c>
     </row>
     <row r="3" spans="1:138" ht="60" x14ac:dyDescent="0.2">
-      <c r="A3" s="481">
+      <c r="A3" s="468">
         <v>1</v>
       </c>
-      <c r="B3" s="416" t="s">
+      <c r="B3" s="397" t="s">
         <v>50</v>
       </c>
-      <c r="C3" s="500" t="s">
+      <c r="C3" s="501" t="s">
         <v>346</v>
       </c>
       <c r="D3" s="73" t="s">
@@ -13464,8 +13464,8 @@
       </c>
     </row>
     <row r="4" spans="1:138" ht="45" x14ac:dyDescent="0.2">
-      <c r="A4" s="482"/>
-      <c r="B4" s="417"/>
+      <c r="A4" s="469"/>
+      <c r="B4" s="398"/>
       <c r="C4" s="464"/>
       <c r="D4" s="73" t="s">
         <v>56</v>
@@ -13488,8 +13488,8 @@
       <c r="M4" s="76"/>
     </row>
     <row r="5" spans="1:138" ht="60" x14ac:dyDescent="0.2">
-      <c r="A5" s="482"/>
-      <c r="B5" s="417"/>
+      <c r="A5" s="469"/>
+      <c r="B5" s="398"/>
       <c r="C5" s="464"/>
       <c r="D5" s="73" t="s">
         <v>55</v>
@@ -13512,8 +13512,8 @@
       <c r="M5" s="76"/>
     </row>
     <row r="6" spans="1:138" ht="210" x14ac:dyDescent="0.2">
-      <c r="A6" s="482"/>
-      <c r="B6" s="417"/>
+      <c r="A6" s="469"/>
+      <c r="B6" s="398"/>
       <c r="C6" s="464"/>
       <c r="D6" s="73" t="s">
         <v>63</v>
@@ -13537,8 +13537,8 @@
       <c r="M6" s="76"/>
     </row>
     <row r="7" spans="1:138" ht="150" x14ac:dyDescent="0.2">
-      <c r="A7" s="482"/>
-      <c r="B7" s="417"/>
+      <c r="A7" s="469"/>
+      <c r="B7" s="398"/>
       <c r="C7" s="464"/>
       <c r="D7" s="73" t="s">
         <v>68</v>
@@ -13561,8 +13561,8 @@
       <c r="M7" s="76"/>
     </row>
     <row r="8" spans="1:138" ht="60" x14ac:dyDescent="0.2">
-      <c r="A8" s="482"/>
-      <c r="B8" s="417"/>
+      <c r="A8" s="469"/>
+      <c r="B8" s="398"/>
       <c r="C8" s="464"/>
       <c r="D8" s="73" t="s">
         <v>72</v>
@@ -13585,8 +13585,8 @@
       <c r="M8" s="76"/>
     </row>
     <row r="9" spans="1:138" ht="409.6" x14ac:dyDescent="0.2">
-      <c r="A9" s="482"/>
-      <c r="B9" s="417"/>
+      <c r="A9" s="469"/>
+      <c r="B9" s="398"/>
       <c r="C9" s="464"/>
       <c r="D9" s="73" t="s">
         <v>86</v>
@@ -13625,8 +13625,8 @@
       <c r="M9" s="76"/>
     </row>
     <row r="10" spans="1:138" s="42" customFormat="1" ht="409.6" x14ac:dyDescent="0.2">
-      <c r="A10" s="482"/>
-      <c r="B10" s="417"/>
+      <c r="A10" s="469"/>
+      <c r="B10" s="398"/>
       <c r="C10" s="464"/>
       <c r="D10" s="73" t="s">
         <v>92</v>
@@ -13791,8 +13791,8 @@
       <c r="EH10" s="41"/>
     </row>
     <row r="11" spans="1:138" ht="60" x14ac:dyDescent="0.2">
-      <c r="A11" s="482"/>
-      <c r="B11" s="417"/>
+      <c r="A11" s="469"/>
+      <c r="B11" s="398"/>
       <c r="C11" s="464"/>
       <c r="D11" s="73" t="s">
         <v>277</v>
@@ -13815,13 +13815,13 @@
       <c r="M11" s="76"/>
     </row>
     <row r="12" spans="1:138" ht="45" x14ac:dyDescent="0.2">
-      <c r="A12" s="486">
+      <c r="A12" s="473">
         <v>1.1000000000000001</v>
       </c>
-      <c r="B12" s="487" t="s">
+      <c r="B12" s="474" t="s">
         <v>98</v>
       </c>
-      <c r="C12" s="421" t="s">
+      <c r="C12" s="404" t="s">
         <v>99</v>
       </c>
       <c r="D12" s="73" t="s">
@@ -13847,9 +13847,9 @@
       <c r="M12" s="76"/>
     </row>
     <row r="13" spans="1:138" ht="60" x14ac:dyDescent="0.2">
-      <c r="A13" s="486"/>
-      <c r="B13" s="487"/>
-      <c r="C13" s="422"/>
+      <c r="A13" s="473"/>
+      <c r="B13" s="474"/>
+      <c r="C13" s="405"/>
       <c r="D13" s="73" t="s">
         <v>56</v>
       </c>
@@ -13875,9 +13875,9 @@
       <c r="M13" s="76"/>
     </row>
     <row r="14" spans="1:138" ht="409.6" x14ac:dyDescent="0.2">
-      <c r="A14" s="486"/>
-      <c r="B14" s="487"/>
-      <c r="C14" s="422"/>
+      <c r="A14" s="473"/>
+      <c r="B14" s="474"/>
+      <c r="C14" s="405"/>
       <c r="D14" s="73" t="s">
         <v>55</v>
       </c>
@@ -13913,9 +13913,9 @@
       <c r="M14" s="76"/>
     </row>
     <row r="15" spans="1:138" s="47" customFormat="1" ht="409.6" x14ac:dyDescent="0.2">
-      <c r="A15" s="486"/>
-      <c r="B15" s="487"/>
-      <c r="C15" s="422"/>
+      <c r="A15" s="473"/>
+      <c r="B15" s="474"/>
+      <c r="C15" s="405"/>
       <c r="D15" s="76" t="s">
         <v>106</v>
       </c>
@@ -14076,9 +14076,9 @@
       <c r="EH15" s="36"/>
     </row>
     <row r="16" spans="1:138" s="47" customFormat="1" ht="409.6" x14ac:dyDescent="0.2">
-      <c r="A16" s="486"/>
-      <c r="B16" s="487"/>
-      <c r="C16" s="422"/>
+      <c r="A16" s="473"/>
+      <c r="B16" s="474"/>
+      <c r="C16" s="405"/>
       <c r="D16" s="76" t="s">
         <v>92</v>
       </c>
@@ -14239,9 +14239,9 @@
       <c r="EH16" s="36"/>
     </row>
     <row r="17" spans="1:138" ht="60" x14ac:dyDescent="0.2">
-      <c r="A17" s="481"/>
-      <c r="B17" s="488"/>
-      <c r="C17" s="422"/>
+      <c r="A17" s="468"/>
+      <c r="B17" s="475"/>
+      <c r="C17" s="405"/>
       <c r="D17" s="78" t="s">
         <v>277</v>
       </c>
@@ -14263,13 +14263,13 @@
       <c r="M17" s="76"/>
     </row>
     <row r="18" spans="1:138" ht="45" x14ac:dyDescent="0.2">
-      <c r="A18" s="467">
+      <c r="A18" s="476">
         <v>2</v>
       </c>
-      <c r="B18" s="468" t="s">
+      <c r="B18" s="477" t="s">
         <v>109</v>
       </c>
-      <c r="C18" s="469" t="s">
+      <c r="C18" s="478" t="s">
         <v>347</v>
       </c>
       <c r="D18" s="73" t="s">
@@ -14295,9 +14295,9 @@
       <c r="M18" s="76"/>
     </row>
     <row r="19" spans="1:138" ht="60" x14ac:dyDescent="0.2">
-      <c r="A19" s="467"/>
-      <c r="B19" s="468"/>
-      <c r="C19" s="470"/>
+      <c r="A19" s="476"/>
+      <c r="B19" s="477"/>
+      <c r="C19" s="479"/>
       <c r="D19" s="73" t="s">
         <v>56</v>
       </c>
@@ -14323,9 +14323,9 @@
       <c r="M19" s="76"/>
     </row>
     <row r="20" spans="1:138" ht="409.6" x14ac:dyDescent="0.2">
-      <c r="A20" s="467"/>
-      <c r="B20" s="468"/>
-      <c r="C20" s="470"/>
+      <c r="A20" s="476"/>
+      <c r="B20" s="477"/>
+      <c r="C20" s="479"/>
       <c r="D20" s="73" t="s">
         <v>55</v>
       </c>
@@ -14356,9 +14356,9 @@
       <c r="M20" s="76"/>
     </row>
     <row r="21" spans="1:138" s="47" customFormat="1" ht="409.6" x14ac:dyDescent="0.2">
-      <c r="A21" s="467"/>
-      <c r="B21" s="468"/>
-      <c r="C21" s="470"/>
+      <c r="A21" s="476"/>
+      <c r="B21" s="477"/>
+      <c r="C21" s="479"/>
       <c r="D21" s="61" t="s">
         <v>114</v>
       </c>
@@ -14515,9 +14515,9 @@
       <c r="EH21" s="36"/>
     </row>
     <row r="22" spans="1:138" s="47" customFormat="1" ht="409.6" x14ac:dyDescent="0.2">
-      <c r="A22" s="467"/>
-      <c r="B22" s="468"/>
-      <c r="C22" s="470"/>
+      <c r="A22" s="476"/>
+      <c r="B22" s="477"/>
+      <c r="C22" s="479"/>
       <c r="D22" s="86" t="s">
         <v>92</v>
       </c>
@@ -14674,9 +14674,9 @@
       <c r="EH22" s="36"/>
     </row>
     <row r="23" spans="1:138" ht="196.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A23" s="467"/>
-      <c r="B23" s="468"/>
-      <c r="C23" s="471"/>
+      <c r="A23" s="476"/>
+      <c r="B23" s="477"/>
+      <c r="C23" s="480"/>
       <c r="D23" s="76" t="s">
         <v>94</v>
       </c>
@@ -14698,13 +14698,13 @@
       <c r="M23" s="76"/>
     </row>
     <row r="24" spans="1:138" ht="60" x14ac:dyDescent="0.2">
-      <c r="A24" s="472">
+      <c r="A24" s="481">
         <v>2.1</v>
       </c>
-      <c r="B24" s="475" t="s">
+      <c r="B24" s="484" t="s">
         <v>116</v>
       </c>
-      <c r="C24" s="478" t="s">
+      <c r="C24" s="487" t="s">
         <v>117</v>
       </c>
       <c r="D24" s="76" t="s">
@@ -14730,9 +14730,9 @@
       <c r="M24" s="76"/>
     </row>
     <row r="25" spans="1:138" ht="105" x14ac:dyDescent="0.2">
-      <c r="A25" s="473"/>
-      <c r="B25" s="476"/>
-      <c r="C25" s="479"/>
+      <c r="A25" s="482"/>
+      <c r="B25" s="485"/>
+      <c r="C25" s="488"/>
       <c r="D25" s="76" t="s">
         <v>130</v>
       </c>
@@ -14756,9 +14756,9 @@
       <c r="M25" s="76"/>
     </row>
     <row r="26" spans="1:138" ht="60" x14ac:dyDescent="0.2">
-      <c r="A26" s="473"/>
-      <c r="B26" s="476"/>
-      <c r="C26" s="479"/>
+      <c r="A26" s="482"/>
+      <c r="B26" s="485"/>
+      <c r="C26" s="488"/>
       <c r="D26" s="189" t="s">
         <v>55</v>
       </c>
@@ -14782,9 +14782,9 @@
       <c r="M26" s="76"/>
     </row>
     <row r="27" spans="1:138" ht="45" x14ac:dyDescent="0.2">
-      <c r="A27" s="473"/>
-      <c r="B27" s="476"/>
-      <c r="C27" s="479"/>
+      <c r="A27" s="482"/>
+      <c r="B27" s="485"/>
+      <c r="C27" s="488"/>
       <c r="D27" s="37" t="s">
         <v>134</v>
       </c>
@@ -14808,9 +14808,9 @@
       </c>
     </row>
     <row r="28" spans="1:138" ht="60" x14ac:dyDescent="0.2">
-      <c r="A28" s="473"/>
-      <c r="B28" s="476"/>
-      <c r="C28" s="479"/>
+      <c r="A28" s="482"/>
+      <c r="B28" s="485"/>
+      <c r="C28" s="488"/>
       <c r="D28" s="88" t="s">
         <v>114</v>
       </c>
@@ -14834,9 +14834,9 @@
       <c r="M28" s="76"/>
     </row>
     <row r="29" spans="1:138" ht="30" x14ac:dyDescent="0.2">
-      <c r="A29" s="473"/>
-      <c r="B29" s="476"/>
-      <c r="C29" s="479"/>
+      <c r="A29" s="482"/>
+      <c r="B29" s="485"/>
+      <c r="C29" s="488"/>
       <c r="D29" s="86" t="s">
         <v>92</v>
       </c>
@@ -14860,9 +14860,9 @@
       <c r="M29" s="76"/>
     </row>
     <row r="30" spans="1:138" ht="30" x14ac:dyDescent="0.2">
-      <c r="A30" s="474"/>
-      <c r="B30" s="477"/>
-      <c r="C30" s="480"/>
+      <c r="A30" s="483"/>
+      <c r="B30" s="486"/>
+      <c r="C30" s="489"/>
       <c r="D30" s="76" t="s">
         <v>94</v>
       </c>
@@ -14884,13 +14884,13 @@
       <c r="M30" s="76"/>
     </row>
     <row r="31" spans="1:138" ht="60" x14ac:dyDescent="0.2">
-      <c r="A31" s="491">
+      <c r="A31" s="492">
         <v>3</v>
       </c>
-      <c r="B31" s="494" t="s">
+      <c r="B31" s="495" t="s">
         <v>336</v>
       </c>
-      <c r="C31" s="497" t="s">
+      <c r="C31" s="498" t="s">
         <v>337</v>
       </c>
       <c r="D31" s="208" t="s">
@@ -14916,9 +14916,9 @@
       <c r="M31" s="76"/>
     </row>
     <row r="32" spans="1:138" ht="135" x14ac:dyDescent="0.2">
-      <c r="A32" s="492"/>
-      <c r="B32" s="495"/>
-      <c r="C32" s="498"/>
+      <c r="A32" s="493"/>
+      <c r="B32" s="496"/>
+      <c r="C32" s="499"/>
       <c r="D32" s="208" t="s">
         <v>341</v>
       </c>
@@ -14940,9 +14940,9 @@
       <c r="M32" s="76"/>
     </row>
     <row r="33" spans="1:13" ht="90" x14ac:dyDescent="0.2">
-      <c r="A33" s="492"/>
-      <c r="B33" s="495"/>
-      <c r="C33" s="498"/>
+      <c r="A33" s="493"/>
+      <c r="B33" s="496"/>
+      <c r="C33" s="499"/>
       <c r="D33" s="209" t="s">
         <v>114</v>
       </c>
@@ -14966,9 +14966,9 @@
       <c r="M33" s="76"/>
     </row>
     <row r="34" spans="1:13" ht="90" x14ac:dyDescent="0.2">
-      <c r="A34" s="492"/>
-      <c r="B34" s="495"/>
-      <c r="C34" s="498"/>
+      <c r="A34" s="493"/>
+      <c r="B34" s="496"/>
+      <c r="C34" s="499"/>
       <c r="D34" s="215" t="s">
         <v>92</v>
       </c>
@@ -14992,9 +14992,9 @@
       <c r="M34" s="76"/>
     </row>
     <row r="35" spans="1:13" ht="90" x14ac:dyDescent="0.2">
-      <c r="A35" s="493"/>
-      <c r="B35" s="496"/>
-      <c r="C35" s="499"/>
+      <c r="A35" s="494"/>
+      <c r="B35" s="497"/>
+      <c r="C35" s="500"/>
       <c r="D35" s="216" t="s">
         <v>94</v>
       </c>
@@ -15021,13 +15021,6 @@
   </sheetData>
   <autoFilter ref="A2:EH31" xr:uid="{92218EDD-6442-41B5-9565-D949ECDDA5BC}"/>
   <mergeCells count="16">
-    <mergeCell ref="I1:J1"/>
-    <mergeCell ref="A3:A11"/>
-    <mergeCell ref="B3:B11"/>
-    <mergeCell ref="C3:C11"/>
-    <mergeCell ref="A12:A17"/>
-    <mergeCell ref="B12:B17"/>
-    <mergeCell ref="C12:C17"/>
     <mergeCell ref="A31:A35"/>
     <mergeCell ref="B31:B35"/>
     <mergeCell ref="C31:C35"/>
@@ -15037,6 +15030,13 @@
     <mergeCell ref="A24:A30"/>
     <mergeCell ref="B24:B30"/>
     <mergeCell ref="C24:C30"/>
+    <mergeCell ref="I1:J1"/>
+    <mergeCell ref="A3:A11"/>
+    <mergeCell ref="B3:B11"/>
+    <mergeCell ref="C3:C11"/>
+    <mergeCell ref="A12:A17"/>
+    <mergeCell ref="B12:B17"/>
+    <mergeCell ref="C12:C17"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait"/>
@@ -15898,10 +15898,10 @@
       <c r="F1" s="188"/>
       <c r="G1" s="188"/>
       <c r="H1" s="105"/>
-      <c r="I1" s="413" t="s">
+      <c r="I1" s="394" t="s">
         <v>376</v>
       </c>
-      <c r="J1" s="413"/>
+      <c r="J1" s="394"/>
     </row>
     <row r="2" spans="1:138" s="29" customFormat="1" ht="30" x14ac:dyDescent="0.2">
       <c r="A2" s="26" t="s">
@@ -15934,13 +15934,13 @@
       </c>
     </row>
     <row r="3" spans="1:138" ht="45" x14ac:dyDescent="0.2">
-      <c r="A3" s="481">
+      <c r="A3" s="468">
         <v>1</v>
       </c>
-      <c r="B3" s="416" t="s">
+      <c r="B3" s="397" t="s">
         <v>50</v>
       </c>
-      <c r="C3" s="421" t="s">
+      <c r="C3" s="404" t="s">
         <v>377</v>
       </c>
       <c r="D3" s="73" t="s">
@@ -15962,9 +15962,9 @@
       </c>
     </row>
     <row r="4" spans="1:138" ht="45" x14ac:dyDescent="0.2">
-      <c r="A4" s="482"/>
-      <c r="B4" s="417"/>
-      <c r="C4" s="422"/>
+      <c r="A4" s="469"/>
+      <c r="B4" s="398"/>
+      <c r="C4" s="405"/>
       <c r="D4" s="73" t="s">
         <v>56</v>
       </c>
@@ -15984,9 +15984,9 @@
       </c>
     </row>
     <row r="5" spans="1:138" ht="60" x14ac:dyDescent="0.2">
-      <c r="A5" s="482"/>
-      <c r="B5" s="417"/>
-      <c r="C5" s="422"/>
+      <c r="A5" s="469"/>
+      <c r="B5" s="398"/>
+      <c r="C5" s="405"/>
       <c r="D5" s="73" t="s">
         <v>55</v>
       </c>
@@ -16006,9 +16006,9 @@
       </c>
     </row>
     <row r="6" spans="1:138" ht="210" x14ac:dyDescent="0.2">
-      <c r="A6" s="482"/>
-      <c r="B6" s="417"/>
-      <c r="C6" s="422"/>
+      <c r="A6" s="469"/>
+      <c r="B6" s="398"/>
+      <c r="C6" s="405"/>
       <c r="D6" s="73" t="s">
         <v>63</v>
       </c>
@@ -16029,9 +16029,9 @@
       <c r="K6" s="38"/>
     </row>
     <row r="7" spans="1:138" ht="150" x14ac:dyDescent="0.2">
-      <c r="A7" s="482"/>
-      <c r="B7" s="417"/>
-      <c r="C7" s="422"/>
+      <c r="A7" s="469"/>
+      <c r="B7" s="398"/>
+      <c r="C7" s="405"/>
       <c r="D7" s="73" t="s">
         <v>68</v>
       </c>
@@ -16051,9 +16051,9 @@
       </c>
     </row>
     <row r="8" spans="1:138" ht="60" x14ac:dyDescent="0.2">
-      <c r="A8" s="482"/>
-      <c r="B8" s="417"/>
-      <c r="C8" s="422"/>
+      <c r="A8" s="469"/>
+      <c r="B8" s="398"/>
+      <c r="C8" s="405"/>
       <c r="D8" s="73" t="s">
         <v>72</v>
       </c>
@@ -16073,9 +16073,9 @@
       </c>
     </row>
     <row r="9" spans="1:138" ht="409.6" x14ac:dyDescent="0.2">
-      <c r="A9" s="482"/>
-      <c r="B9" s="417"/>
-      <c r="C9" s="422"/>
+      <c r="A9" s="469"/>
+      <c r="B9" s="398"/>
+      <c r="C9" s="405"/>
       <c r="D9" s="73" t="s">
         <v>86</v>
       </c>
@@ -16109,9 +16109,9 @@
       </c>
     </row>
     <row r="10" spans="1:138" s="42" customFormat="1" ht="409.6" x14ac:dyDescent="0.2">
-      <c r="A10" s="482"/>
-      <c r="B10" s="417"/>
-      <c r="C10" s="422"/>
+      <c r="A10" s="469"/>
+      <c r="B10" s="398"/>
+      <c r="C10" s="405"/>
       <c r="D10" s="73" t="s">
         <v>92</v>
       </c>
@@ -16273,9 +16273,9 @@
       <c r="EH10" s="41"/>
     </row>
     <row r="11" spans="1:138" ht="45" x14ac:dyDescent="0.2">
-      <c r="A11" s="482"/>
-      <c r="B11" s="417"/>
-      <c r="C11" s="422"/>
+      <c r="A11" s="469"/>
+      <c r="B11" s="398"/>
+      <c r="C11" s="405"/>
       <c r="D11" s="73" t="s">
         <v>277</v>
       </c>
@@ -16295,13 +16295,13 @@
       </c>
     </row>
     <row r="12" spans="1:138" ht="45" x14ac:dyDescent="0.2">
-      <c r="A12" s="486">
+      <c r="A12" s="473">
         <v>1.1000000000000001</v>
       </c>
-      <c r="B12" s="487" t="s">
+      <c r="B12" s="474" t="s">
         <v>98</v>
       </c>
-      <c r="C12" s="421" t="s">
+      <c r="C12" s="404" t="s">
         <v>378</v>
       </c>
       <c r="D12" s="73" t="s">
@@ -16323,9 +16323,9 @@
       </c>
     </row>
     <row r="13" spans="1:138" ht="45" x14ac:dyDescent="0.2">
-      <c r="A13" s="486"/>
-      <c r="B13" s="487"/>
-      <c r="C13" s="422"/>
+      <c r="A13" s="473"/>
+      <c r="B13" s="474"/>
+      <c r="C13" s="405"/>
       <c r="D13" s="73" t="s">
         <v>56</v>
       </c>
@@ -16347,9 +16347,9 @@
       </c>
     </row>
     <row r="14" spans="1:138" ht="409.6" x14ac:dyDescent="0.2">
-      <c r="A14" s="486"/>
-      <c r="B14" s="487"/>
-      <c r="C14" s="422"/>
+      <c r="A14" s="473"/>
+      <c r="B14" s="474"/>
+      <c r="C14" s="405"/>
       <c r="D14" s="73" t="s">
         <v>55</v>
       </c>
@@ -16384,9 +16384,9 @@
       <c r="K14" s="38"/>
     </row>
     <row r="15" spans="1:138" s="47" customFormat="1" ht="409.6" x14ac:dyDescent="0.2">
-      <c r="A15" s="486"/>
-      <c r="B15" s="487"/>
-      <c r="C15" s="422"/>
+      <c r="A15" s="473"/>
+      <c r="B15" s="474"/>
+      <c r="C15" s="405"/>
       <c r="D15" s="76" t="s">
         <v>106</v>
       </c>
@@ -16548,9 +16548,9 @@
       <c r="EH15" s="36"/>
     </row>
     <row r="16" spans="1:138" s="47" customFormat="1" ht="409.6" x14ac:dyDescent="0.2">
-      <c r="A16" s="486"/>
-      <c r="B16" s="487"/>
-      <c r="C16" s="422"/>
+      <c r="A16" s="473"/>
+      <c r="B16" s="474"/>
+      <c r="C16" s="405"/>
       <c r="D16" s="76" t="s">
         <v>92</v>
       </c>
@@ -16712,9 +16712,9 @@
       <c r="EH16" s="36"/>
     </row>
     <row r="17" spans="1:138" ht="45" x14ac:dyDescent="0.2">
-      <c r="A17" s="481"/>
-      <c r="B17" s="488"/>
-      <c r="C17" s="422"/>
+      <c r="A17" s="468"/>
+      <c r="B17" s="475"/>
+      <c r="C17" s="405"/>
       <c r="D17" s="78" t="s">
         <v>277</v>
       </c>
@@ -16734,10 +16734,10 @@
       </c>
     </row>
     <row r="18" spans="1:138" ht="45" x14ac:dyDescent="0.2">
-      <c r="A18" s="467">
+      <c r="A18" s="476">
         <v>2</v>
       </c>
-      <c r="B18" s="468" t="s">
+      <c r="B18" s="477" t="s">
         <v>109</v>
       </c>
       <c r="C18" s="461" t="s">
@@ -16762,9 +16762,9 @@
       </c>
     </row>
     <row r="19" spans="1:138" ht="45" x14ac:dyDescent="0.2">
-      <c r="A19" s="467"/>
-      <c r="B19" s="468"/>
-      <c r="C19" s="510"/>
+      <c r="A19" s="476"/>
+      <c r="B19" s="477"/>
+      <c r="C19" s="511"/>
       <c r="D19" s="73" t="s">
         <v>56</v>
       </c>
@@ -16786,9 +16786,9 @@
       </c>
     </row>
     <row r="20" spans="1:138" ht="90" x14ac:dyDescent="0.2">
-      <c r="A20" s="467"/>
-      <c r="B20" s="468"/>
-      <c r="C20" s="510"/>
+      <c r="A20" s="476"/>
+      <c r="B20" s="477"/>
+      <c r="C20" s="511"/>
       <c r="D20" s="73" t="s">
         <v>55</v>
       </c>
@@ -16810,9 +16810,9 @@
       </c>
     </row>
     <row r="21" spans="1:138" s="47" customFormat="1" ht="90" x14ac:dyDescent="0.2">
-      <c r="A21" s="467"/>
-      <c r="B21" s="468"/>
-      <c r="C21" s="510"/>
+      <c r="A21" s="476"/>
+      <c r="B21" s="477"/>
+      <c r="C21" s="511"/>
       <c r="D21" s="61" t="s">
         <v>114</v>
       </c>
@@ -16962,9 +16962,9 @@
       <c r="EH21" s="36"/>
     </row>
     <row r="22" spans="1:138" s="47" customFormat="1" ht="90" x14ac:dyDescent="0.2">
-      <c r="A22" s="467"/>
-      <c r="B22" s="468"/>
-      <c r="C22" s="510"/>
+      <c r="A22" s="476"/>
+      <c r="B22" s="477"/>
+      <c r="C22" s="511"/>
       <c r="D22" s="86" t="s">
         <v>92</v>
       </c>
@@ -17114,9 +17114,9 @@
       <c r="EH22" s="36"/>
     </row>
     <row r="23" spans="1:138" ht="30" x14ac:dyDescent="0.2">
-      <c r="A23" s="467"/>
-      <c r="B23" s="468"/>
-      <c r="C23" s="511"/>
+      <c r="A23" s="476"/>
+      <c r="B23" s="477"/>
+      <c r="C23" s="512"/>
       <c r="D23" s="76" t="s">
         <v>94</v>
       </c>
@@ -17136,13 +17136,13 @@
       </c>
     </row>
     <row r="24" spans="1:138" ht="60" x14ac:dyDescent="0.2">
-      <c r="A24" s="472">
+      <c r="A24" s="481">
         <v>2.1</v>
       </c>
-      <c r="B24" s="475" t="s">
+      <c r="B24" s="484" t="s">
         <v>116</v>
       </c>
-      <c r="C24" s="478" t="s">
+      <c r="C24" s="487" t="s">
         <v>117</v>
       </c>
       <c r="D24" s="83" t="s">
@@ -17167,9 +17167,9 @@
       </c>
     </row>
     <row r="25" spans="1:138" ht="105" x14ac:dyDescent="0.2">
-      <c r="A25" s="473"/>
-      <c r="B25" s="476"/>
-      <c r="C25" s="479"/>
+      <c r="A25" s="482"/>
+      <c r="B25" s="485"/>
+      <c r="C25" s="488"/>
       <c r="D25" s="83" t="s">
         <v>130</v>
       </c>
@@ -17192,9 +17192,9 @@
       </c>
     </row>
     <row r="26" spans="1:138" ht="60" x14ac:dyDescent="0.2">
-      <c r="A26" s="473"/>
-      <c r="B26" s="476"/>
-      <c r="C26" s="479"/>
+      <c r="A26" s="482"/>
+      <c r="B26" s="485"/>
+      <c r="C26" s="488"/>
       <c r="D26" s="73" t="s">
         <v>55</v>
       </c>
@@ -17219,9 +17219,9 @@
       </c>
     </row>
     <row r="27" spans="1:138" ht="60" x14ac:dyDescent="0.2">
-      <c r="A27" s="473"/>
-      <c r="B27" s="476"/>
-      <c r="C27" s="479"/>
+      <c r="A27" s="482"/>
+      <c r="B27" s="485"/>
+      <c r="C27" s="488"/>
       <c r="D27" s="61" t="s">
         <v>114</v>
       </c>
@@ -17243,9 +17243,9 @@
       </c>
     </row>
     <row r="28" spans="1:138" ht="30" x14ac:dyDescent="0.2">
-      <c r="A28" s="473"/>
-      <c r="B28" s="476"/>
-      <c r="C28" s="479"/>
+      <c r="A28" s="482"/>
+      <c r="B28" s="485"/>
+      <c r="C28" s="488"/>
       <c r="D28" s="86" t="s">
         <v>92</v>
       </c>
@@ -17267,9 +17267,9 @@
       </c>
     </row>
     <row r="29" spans="1:138" ht="30" x14ac:dyDescent="0.2">
-      <c r="A29" s="474"/>
-      <c r="B29" s="477"/>
-      <c r="C29" s="480"/>
+      <c r="A29" s="483"/>
+      <c r="B29" s="486"/>
+      <c r="C29" s="489"/>
       <c r="D29" s="76" t="s">
         <v>94</v>
       </c>
@@ -17289,13 +17289,13 @@
       </c>
     </row>
     <row r="30" spans="1:138" ht="60" x14ac:dyDescent="0.2">
-      <c r="A30" s="507">
+      <c r="A30" s="508">
         <v>3</v>
       </c>
-      <c r="B30" s="504" t="s">
+      <c r="B30" s="505" t="s">
         <v>336</v>
       </c>
-      <c r="C30" s="501" t="s">
+      <c r="C30" s="502" t="s">
         <v>337</v>
       </c>
       <c r="D30" s="157" t="s">
@@ -17317,9 +17317,9 @@
       </c>
     </row>
     <row r="31" spans="1:138" ht="105" x14ac:dyDescent="0.2">
-      <c r="A31" s="508"/>
-      <c r="B31" s="505"/>
-      <c r="C31" s="502"/>
+      <c r="A31" s="509"/>
+      <c r="B31" s="506"/>
+      <c r="C31" s="503"/>
       <c r="D31" s="157" t="s">
         <v>341</v>
       </c>
@@ -17339,9 +17339,9 @@
       </c>
     </row>
     <row r="32" spans="1:138" ht="90" x14ac:dyDescent="0.2">
-      <c r="A32" s="508"/>
-      <c r="B32" s="505"/>
-      <c r="C32" s="502"/>
+      <c r="A32" s="509"/>
+      <c r="B32" s="506"/>
+      <c r="C32" s="503"/>
       <c r="D32" s="80" t="s">
         <v>114</v>
       </c>
@@ -17363,9 +17363,9 @@
       </c>
     </row>
     <row r="33" spans="1:10" ht="90" x14ac:dyDescent="0.2">
-      <c r="A33" s="508"/>
-      <c r="B33" s="505"/>
-      <c r="C33" s="502"/>
+      <c r="A33" s="509"/>
+      <c r="B33" s="506"/>
+      <c r="C33" s="503"/>
       <c r="D33" s="91" t="s">
         <v>92</v>
       </c>
@@ -17387,9 +17387,9 @@
       </c>
     </row>
     <row r="34" spans="1:10" ht="90" x14ac:dyDescent="0.2">
-      <c r="A34" s="509"/>
-      <c r="B34" s="506"/>
-      <c r="C34" s="503"/>
+      <c r="A34" s="510"/>
+      <c r="B34" s="507"/>
+      <c r="C34" s="504"/>
       <c r="D34" s="83" t="s">
         <v>94</v>
       </c>
@@ -17411,6 +17411,13 @@
   </sheetData>
   <autoFilter ref="A2:EH30" xr:uid="{92218EDD-6442-41B5-9565-D949ECDDA5BC}"/>
   <mergeCells count="16">
+    <mergeCell ref="I1:J1"/>
+    <mergeCell ref="A3:A11"/>
+    <mergeCell ref="B3:B11"/>
+    <mergeCell ref="C3:C11"/>
+    <mergeCell ref="A12:A17"/>
+    <mergeCell ref="B12:B17"/>
+    <mergeCell ref="C12:C17"/>
     <mergeCell ref="C30:C34"/>
     <mergeCell ref="B30:B34"/>
     <mergeCell ref="A30:A34"/>
@@ -17420,13 +17427,6 @@
     <mergeCell ref="A24:A29"/>
     <mergeCell ref="B24:B29"/>
     <mergeCell ref="C24:C29"/>
-    <mergeCell ref="I1:J1"/>
-    <mergeCell ref="A3:A11"/>
-    <mergeCell ref="B3:B11"/>
-    <mergeCell ref="C3:C11"/>
-    <mergeCell ref="A12:A17"/>
-    <mergeCell ref="B12:B17"/>
-    <mergeCell ref="C12:C17"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait"/>
@@ -17452,18 +17452,18 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:133" s="31" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="425" t="s">
+      <c r="A1" s="410" t="s">
         <v>38</v>
       </c>
-      <c r="B1" s="425"/>
-      <c r="C1" s="425"/>
-      <c r="D1" s="425"/>
-      <c r="E1" s="425"/>
-      <c r="F1" s="425"/>
-      <c r="G1" s="425"/>
+      <c r="B1" s="410"/>
+      <c r="C1" s="410"/>
+      <c r="D1" s="410"/>
+      <c r="E1" s="410"/>
+      <c r="F1" s="410"/>
+      <c r="G1" s="410"/>
       <c r="H1" s="310"/>
-      <c r="I1" s="413"/>
-      <c r="J1" s="413"/>
+      <c r="I1" s="394"/>
+      <c r="J1" s="394"/>
     </row>
     <row r="2" spans="1:133" s="29" customFormat="1" ht="30" x14ac:dyDescent="0.2">
       <c r="A2" s="27" t="s">
@@ -17635,13 +17635,13 @@
       <c r="EC3" s="36"/>
     </row>
     <row r="4" spans="1:133" ht="36" x14ac:dyDescent="0.2">
-      <c r="A4" s="414">
+      <c r="A4" s="395">
         <v>1</v>
       </c>
-      <c r="B4" s="416" t="s">
+      <c r="B4" s="397" t="s">
         <v>50</v>
       </c>
-      <c r="C4" s="418" t="s">
+      <c r="C4" s="399" t="s">
         <v>51</v>
       </c>
       <c r="D4" s="73" t="s">
@@ -17663,9 +17663,9 @@
       </c>
     </row>
     <row r="5" spans="1:133" ht="24" x14ac:dyDescent="0.2">
-      <c r="A5" s="415"/>
-      <c r="B5" s="417"/>
-      <c r="C5" s="419"/>
+      <c r="A5" s="396"/>
+      <c r="B5" s="398"/>
+      <c r="C5" s="400"/>
       <c r="D5" s="73" t="s">
         <v>56</v>
       </c>
@@ -17685,9 +17685,9 @@
       </c>
     </row>
     <row r="6" spans="1:133" ht="24" x14ac:dyDescent="0.2">
-      <c r="A6" s="415"/>
-      <c r="B6" s="417"/>
-      <c r="C6" s="419"/>
+      <c r="A6" s="396"/>
+      <c r="B6" s="398"/>
+      <c r="C6" s="400"/>
       <c r="D6" s="237" t="s">
         <v>61</v>
       </c>
@@ -17707,9 +17707,9 @@
       </c>
     </row>
     <row r="7" spans="1:133" ht="144" x14ac:dyDescent="0.2">
-      <c r="A7" s="415"/>
-      <c r="B7" s="417"/>
-      <c r="C7" s="419"/>
+      <c r="A7" s="396"/>
+      <c r="B7" s="398"/>
+      <c r="C7" s="400"/>
       <c r="D7" s="73" t="s">
         <v>63</v>
       </c>
@@ -17729,9 +17729,9 @@
       </c>
     </row>
     <row r="8" spans="1:133" ht="108" x14ac:dyDescent="0.2">
-      <c r="A8" s="415"/>
-      <c r="B8" s="417"/>
-      <c r="C8" s="419"/>
+      <c r="A8" s="396"/>
+      <c r="B8" s="398"/>
+      <c r="C8" s="400"/>
       <c r="D8" s="73" t="s">
         <v>68</v>
       </c>
@@ -17751,9 +17751,9 @@
       </c>
     </row>
     <row r="9" spans="1:133" ht="36" x14ac:dyDescent="0.2">
-      <c r="A9" s="415"/>
-      <c r="B9" s="417"/>
-      <c r="C9" s="419"/>
+      <c r="A9" s="396"/>
+      <c r="B9" s="398"/>
+      <c r="C9" s="400"/>
       <c r="D9" s="73" t="s">
         <v>72</v>
       </c>
@@ -17773,9 +17773,9 @@
       </c>
     </row>
     <row r="10" spans="1:133" ht="30" x14ac:dyDescent="0.2">
-      <c r="A10" s="415"/>
-      <c r="B10" s="417"/>
-      <c r="C10" s="419"/>
+      <c r="A10" s="396"/>
+      <c r="B10" s="398"/>
+      <c r="C10" s="400"/>
       <c r="D10" s="237" t="s">
         <v>76</v>
       </c>
@@ -17795,9 +17795,9 @@
       </c>
     </row>
     <row r="11" spans="1:133" ht="75" x14ac:dyDescent="0.2">
-      <c r="A11" s="415"/>
-      <c r="B11" s="417"/>
-      <c r="C11" s="419"/>
+      <c r="A11" s="396"/>
+      <c r="B11" s="398"/>
+      <c r="C11" s="400"/>
       <c r="D11" s="237" t="s">
         <v>79</v>
       </c>
@@ -17819,9 +17819,9 @@
       </c>
     </row>
     <row r="12" spans="1:133" ht="60" x14ac:dyDescent="0.2">
-      <c r="A12" s="415"/>
-      <c r="B12" s="417"/>
-      <c r="C12" s="419"/>
+      <c r="A12" s="396"/>
+      <c r="B12" s="398"/>
+      <c r="C12" s="400"/>
       <c r="D12" s="237" t="s">
         <v>83</v>
       </c>
@@ -17843,9 +17843,9 @@
       </c>
     </row>
     <row r="13" spans="1:133" ht="48" x14ac:dyDescent="0.2">
-      <c r="A13" s="415"/>
-      <c r="B13" s="417"/>
-      <c r="C13" s="419"/>
+      <c r="A13" s="396"/>
+      <c r="B13" s="398"/>
+      <c r="C13" s="400"/>
       <c r="D13" s="73" t="s">
         <v>86</v>
       </c>
@@ -17867,9 +17867,9 @@
       </c>
     </row>
     <row r="14" spans="1:133" s="42" customFormat="1" ht="30" x14ac:dyDescent="0.2">
-      <c r="A14" s="415"/>
-      <c r="B14" s="417"/>
-      <c r="C14" s="419"/>
+      <c r="A14" s="396"/>
+      <c r="B14" s="398"/>
+      <c r="C14" s="400"/>
       <c r="D14" s="73" t="s">
         <v>92</v>
       </c>
@@ -18014,9 +18014,9 @@
       <c r="EC14" s="41"/>
     </row>
     <row r="15" spans="1:133" ht="45" x14ac:dyDescent="0.2">
-      <c r="A15" s="415"/>
-      <c r="B15" s="417"/>
-      <c r="C15" s="420"/>
+      <c r="A15" s="396"/>
+      <c r="B15" s="398"/>
+      <c r="C15" s="401"/>
       <c r="D15" s="73" t="s">
         <v>94</v>
       </c>
@@ -18036,13 +18036,13 @@
       </c>
     </row>
     <row r="16" spans="1:133" ht="36" x14ac:dyDescent="0.2">
-      <c r="A16" s="406" t="s">
+      <c r="A16" s="402" t="s">
         <v>97</v>
       </c>
-      <c r="B16" s="407" t="s">
+      <c r="B16" s="403" t="s">
         <v>98</v>
       </c>
-      <c r="C16" s="421" t="s">
+      <c r="C16" s="404" t="s">
         <v>99</v>
       </c>
       <c r="D16" s="73" t="s">
@@ -18064,9 +18064,9 @@
       </c>
     </row>
     <row r="17" spans="1:133" ht="30" x14ac:dyDescent="0.2">
-      <c r="A17" s="406"/>
-      <c r="B17" s="407"/>
-      <c r="C17" s="422"/>
+      <c r="A17" s="402"/>
+      <c r="B17" s="403"/>
+      <c r="C17" s="405"/>
       <c r="D17" s="73" t="s">
         <v>56</v>
       </c>
@@ -18088,9 +18088,9 @@
       </c>
     </row>
     <row r="18" spans="1:133" ht="24" x14ac:dyDescent="0.2">
-      <c r="A18" s="406"/>
-      <c r="B18" s="407"/>
-      <c r="C18" s="422"/>
+      <c r="A18" s="402"/>
+      <c r="B18" s="403"/>
+      <c r="C18" s="405"/>
       <c r="D18" s="237" t="s">
         <v>61</v>
       </c>
@@ -18110,13 +18110,13 @@
       </c>
     </row>
     <row r="19" spans="1:133" ht="15" x14ac:dyDescent="0.2">
-      <c r="A19" s="406"/>
-      <c r="B19" s="407"/>
-      <c r="C19" s="422"/>
-      <c r="D19" s="423" t="s">
+      <c r="A19" s="402"/>
+      <c r="B19" s="403"/>
+      <c r="C19" s="405"/>
+      <c r="D19" s="406" t="s">
         <v>76</v>
       </c>
-      <c r="E19" s="404" t="s">
+      <c r="E19" s="408" t="s">
         <v>77</v>
       </c>
       <c r="F19" s="73" t="s">
@@ -18132,11 +18132,11 @@
       </c>
     </row>
     <row r="20" spans="1:133" s="47" customFormat="1" ht="45" x14ac:dyDescent="0.2">
-      <c r="A20" s="406"/>
-      <c r="B20" s="407"/>
-      <c r="C20" s="422"/>
-      <c r="D20" s="424"/>
-      <c r="E20" s="405"/>
+      <c r="A20" s="402"/>
+      <c r="B20" s="403"/>
+      <c r="C20" s="405"/>
+      <c r="D20" s="407"/>
+      <c r="E20" s="409"/>
       <c r="F20" s="73" t="s">
         <v>103</v>
       </c>
@@ -18273,9 +18273,9 @@
       <c r="EC20" s="36"/>
     </row>
     <row r="21" spans="1:133" s="47" customFormat="1" ht="75" x14ac:dyDescent="0.2">
-      <c r="A21" s="406"/>
-      <c r="B21" s="407"/>
-      <c r="C21" s="422"/>
+      <c r="A21" s="402"/>
+      <c r="B21" s="403"/>
+      <c r="C21" s="405"/>
       <c r="D21" s="237" t="s">
         <v>79</v>
       </c>
@@ -18420,9 +18420,9 @@
       <c r="EC21" s="36"/>
     </row>
     <row r="22" spans="1:133" ht="60" x14ac:dyDescent="0.2">
-      <c r="A22" s="406"/>
-      <c r="B22" s="407"/>
-      <c r="C22" s="422"/>
+      <c r="A22" s="402"/>
+      <c r="B22" s="403"/>
+      <c r="C22" s="405"/>
       <c r="D22" s="237" t="s">
         <v>83</v>
       </c>
@@ -18444,9 +18444,9 @@
       </c>
     </row>
     <row r="23" spans="1:133" ht="48" x14ac:dyDescent="0.2">
-      <c r="A23" s="406"/>
-      <c r="B23" s="407"/>
-      <c r="C23" s="422"/>
+      <c r="A23" s="402"/>
+      <c r="B23" s="403"/>
+      <c r="C23" s="405"/>
       <c r="D23" s="73" t="s">
         <v>106</v>
       </c>
@@ -18468,9 +18468,9 @@
       </c>
     </row>
     <row r="24" spans="1:133" ht="30" x14ac:dyDescent="0.2">
-      <c r="A24" s="406"/>
-      <c r="B24" s="407"/>
-      <c r="C24" s="422"/>
+      <c r="A24" s="402"/>
+      <c r="B24" s="403"/>
+      <c r="C24" s="405"/>
       <c r="D24" s="73" t="s">
         <v>92</v>
       </c>
@@ -18492,9 +18492,9 @@
       </c>
     </row>
     <row r="25" spans="1:133" ht="45" x14ac:dyDescent="0.2">
-      <c r="A25" s="414"/>
-      <c r="B25" s="416"/>
-      <c r="C25" s="422"/>
+      <c r="A25" s="395"/>
+      <c r="B25" s="397"/>
+      <c r="C25" s="405"/>
       <c r="D25" s="73" t="s">
         <v>94</v>
       </c>
@@ -18514,13 +18514,13 @@
       </c>
     </row>
     <row r="26" spans="1:133" ht="36" x14ac:dyDescent="0.2">
-      <c r="A26" s="393" t="s">
+      <c r="A26" s="413" t="s">
         <v>108</v>
       </c>
-      <c r="B26" s="396" t="s">
+      <c r="B26" s="416" t="s">
         <v>109</v>
       </c>
-      <c r="C26" s="399" t="s">
+      <c r="C26" s="422" t="s">
         <v>110</v>
       </c>
       <c r="D26" s="73" t="s">
@@ -18542,9 +18542,9 @@
       </c>
     </row>
     <row r="27" spans="1:133" ht="36" x14ac:dyDescent="0.2">
-      <c r="A27" s="394"/>
-      <c r="B27" s="397"/>
-      <c r="C27" s="400"/>
+      <c r="A27" s="414"/>
+      <c r="B27" s="417"/>
+      <c r="C27" s="423"/>
       <c r="D27" s="73" t="s">
         <v>56</v>
       </c>
@@ -18566,9 +18566,9 @@
       </c>
     </row>
     <row r="28" spans="1:133" ht="30" x14ac:dyDescent="0.2">
-      <c r="A28" s="394"/>
-      <c r="B28" s="397"/>
-      <c r="C28" s="400"/>
+      <c r="A28" s="414"/>
+      <c r="B28" s="417"/>
+      <c r="C28" s="423"/>
       <c r="D28" s="237" t="s">
         <v>61</v>
       </c>
@@ -18590,13 +18590,13 @@
       </c>
     </row>
     <row r="29" spans="1:133" ht="15" x14ac:dyDescent="0.2">
-      <c r="A29" s="394"/>
-      <c r="B29" s="397"/>
-      <c r="C29" s="400"/>
-      <c r="D29" s="402" t="s">
+      <c r="A29" s="414"/>
+      <c r="B29" s="417"/>
+      <c r="C29" s="423"/>
+      <c r="D29" s="425" t="s">
         <v>76</v>
       </c>
-      <c r="E29" s="404" t="s">
+      <c r="E29" s="408" t="s">
         <v>77</v>
       </c>
       <c r="F29" s="73" t="s">
@@ -18612,11 +18612,11 @@
       </c>
     </row>
     <row r="30" spans="1:133" ht="30" x14ac:dyDescent="0.2">
-      <c r="A30" s="394"/>
-      <c r="B30" s="397"/>
-      <c r="C30" s="400"/>
-      <c r="D30" s="403"/>
-      <c r="E30" s="405"/>
+      <c r="A30" s="414"/>
+      <c r="B30" s="417"/>
+      <c r="C30" s="423"/>
+      <c r="D30" s="426"/>
+      <c r="E30" s="409"/>
       <c r="F30" s="73" t="s">
         <v>113</v>
       </c>
@@ -18632,9 +18632,9 @@
       </c>
     </row>
     <row r="31" spans="1:133" ht="75" x14ac:dyDescent="0.2">
-      <c r="A31" s="394"/>
-      <c r="B31" s="397"/>
-      <c r="C31" s="400"/>
+      <c r="A31" s="414"/>
+      <c r="B31" s="417"/>
+      <c r="C31" s="423"/>
       <c r="D31" s="237" t="s">
         <v>79</v>
       </c>
@@ -18656,9 +18656,9 @@
       </c>
     </row>
     <row r="32" spans="1:133" ht="60" x14ac:dyDescent="0.2">
-      <c r="A32" s="394"/>
-      <c r="B32" s="397"/>
-      <c r="C32" s="400"/>
+      <c r="A32" s="414"/>
+      <c r="B32" s="417"/>
+      <c r="C32" s="423"/>
       <c r="D32" s="237" t="s">
         <v>83</v>
       </c>
@@ -18680,9 +18680,9 @@
       </c>
     </row>
     <row r="33" spans="1:133" s="47" customFormat="1" ht="48" x14ac:dyDescent="0.2">
-      <c r="A33" s="394"/>
-      <c r="B33" s="397"/>
-      <c r="C33" s="400"/>
+      <c r="A33" s="414"/>
+      <c r="B33" s="417"/>
+      <c r="C33" s="423"/>
       <c r="D33" s="264" t="s">
         <v>114</v>
       </c>
@@ -18827,9 +18827,9 @@
       <c r="EC33" s="36"/>
     </row>
     <row r="34" spans="1:133" s="47" customFormat="1" ht="30" x14ac:dyDescent="0.2">
-      <c r="A34" s="394"/>
-      <c r="B34" s="397"/>
-      <c r="C34" s="400"/>
+      <c r="A34" s="414"/>
+      <c r="B34" s="417"/>
+      <c r="C34" s="423"/>
       <c r="D34" s="272" t="s">
         <v>92</v>
       </c>
@@ -18974,9 +18974,9 @@
       <c r="EC34" s="36"/>
     </row>
     <row r="35" spans="1:133" ht="45" x14ac:dyDescent="0.2">
-      <c r="A35" s="395"/>
-      <c r="B35" s="398"/>
-      <c r="C35" s="401"/>
+      <c r="A35" s="415"/>
+      <c r="B35" s="418"/>
+      <c r="C35" s="424"/>
       <c r="D35" s="73" t="s">
         <v>94</v>
       </c>
@@ -18996,13 +18996,13 @@
       </c>
     </row>
     <row r="36" spans="1:133" ht="60" x14ac:dyDescent="0.2">
-      <c r="A36" s="393" t="s">
+      <c r="A36" s="413" t="s">
         <v>115</v>
       </c>
-      <c r="B36" s="396" t="s">
+      <c r="B36" s="416" t="s">
         <v>116</v>
       </c>
-      <c r="C36" s="410" t="s">
+      <c r="C36" s="419" t="s">
         <v>117</v>
       </c>
       <c r="D36" s="37" t="s">
@@ -19026,9 +19026,9 @@
       </c>
     </row>
     <row r="37" spans="1:133" ht="60" x14ac:dyDescent="0.2">
-      <c r="A37" s="394"/>
-      <c r="B37" s="397"/>
-      <c r="C37" s="411"/>
+      <c r="A37" s="414"/>
+      <c r="B37" s="417"/>
+      <c r="C37" s="420"/>
       <c r="D37" s="189" t="s">
         <v>122</v>
       </c>
@@ -19050,9 +19050,9 @@
       </c>
     </row>
     <row r="38" spans="1:133" ht="60" x14ac:dyDescent="0.2">
-      <c r="A38" s="394"/>
-      <c r="B38" s="397"/>
-      <c r="C38" s="411"/>
+      <c r="A38" s="414"/>
+      <c r="B38" s="417"/>
+      <c r="C38" s="420"/>
       <c r="D38" s="37" t="s">
         <v>126</v>
       </c>
@@ -19074,9 +19074,9 @@
       </c>
     </row>
     <row r="39" spans="1:133" ht="84" x14ac:dyDescent="0.2">
-      <c r="A39" s="394"/>
-      <c r="B39" s="397"/>
-      <c r="C39" s="411"/>
+      <c r="A39" s="414"/>
+      <c r="B39" s="417"/>
+      <c r="C39" s="420"/>
       <c r="D39" s="73" t="s">
         <v>130</v>
       </c>
@@ -19098,9 +19098,9 @@
       </c>
     </row>
     <row r="40" spans="1:133" ht="36" x14ac:dyDescent="0.2">
-      <c r="A40" s="394"/>
-      <c r="B40" s="397"/>
-      <c r="C40" s="411"/>
+      <c r="A40" s="414"/>
+      <c r="B40" s="417"/>
+      <c r="C40" s="420"/>
       <c r="D40" s="189" t="s">
         <v>134</v>
       </c>
@@ -19120,9 +19120,9 @@
       </c>
     </row>
     <row r="41" spans="1:133" ht="30" x14ac:dyDescent="0.2">
-      <c r="A41" s="394"/>
-      <c r="B41" s="397"/>
-      <c r="C41" s="411"/>
+      <c r="A41" s="414"/>
+      <c r="B41" s="417"/>
+      <c r="C41" s="420"/>
       <c r="D41" s="237" t="s">
         <v>61</v>
       </c>
@@ -19144,9 +19144,9 @@
       </c>
     </row>
     <row r="42" spans="1:133" ht="72" x14ac:dyDescent="0.2">
-      <c r="A42" s="394"/>
-      <c r="B42" s="397"/>
-      <c r="C42" s="411"/>
+      <c r="A42" s="414"/>
+      <c r="B42" s="417"/>
+      <c r="C42" s="420"/>
       <c r="D42" s="73" t="s">
         <v>76</v>
       </c>
@@ -19168,9 +19168,9 @@
       </c>
     </row>
     <row r="43" spans="1:133" ht="48" x14ac:dyDescent="0.2">
-      <c r="A43" s="394"/>
-      <c r="B43" s="397"/>
-      <c r="C43" s="411"/>
+      <c r="A43" s="414"/>
+      <c r="B43" s="417"/>
+      <c r="C43" s="420"/>
       <c r="D43" s="73" t="s">
         <v>138</v>
       </c>
@@ -19192,9 +19192,9 @@
       </c>
     </row>
     <row r="44" spans="1:133" ht="30" x14ac:dyDescent="0.2">
-      <c r="A44" s="394"/>
-      <c r="B44" s="397"/>
-      <c r="C44" s="411"/>
+      <c r="A44" s="414"/>
+      <c r="B44" s="417"/>
+      <c r="C44" s="420"/>
       <c r="D44" s="332" t="s">
         <v>92</v>
       </c>
@@ -19216,9 +19216,9 @@
       </c>
     </row>
     <row r="45" spans="1:133" ht="45" x14ac:dyDescent="0.2">
-      <c r="A45" s="395"/>
-      <c r="B45" s="398"/>
-      <c r="C45" s="412"/>
+      <c r="A45" s="415"/>
+      <c r="B45" s="418"/>
+      <c r="C45" s="421"/>
       <c r="D45" s="73" t="s">
         <v>94</v>
       </c>
@@ -19254,13 +19254,13 @@
       <c r="J46" s="71"/>
     </row>
     <row r="47" spans="1:133" ht="36" x14ac:dyDescent="0.2">
-      <c r="A47" s="406" t="s">
+      <c r="A47" s="402" t="s">
         <v>141</v>
       </c>
-      <c r="B47" s="407" t="s">
+      <c r="B47" s="403" t="s">
         <v>50</v>
       </c>
-      <c r="C47" s="408" t="s">
+      <c r="C47" s="411" t="s">
         <v>142</v>
       </c>
       <c r="D47" s="73" t="s">
@@ -19282,9 +19282,9 @@
       </c>
     </row>
     <row r="48" spans="1:133" ht="24" x14ac:dyDescent="0.2">
-      <c r="A48" s="406"/>
-      <c r="B48" s="407"/>
-      <c r="C48" s="409"/>
+      <c r="A48" s="402"/>
+      <c r="B48" s="403"/>
+      <c r="C48" s="412"/>
       <c r="D48" s="73" t="s">
         <v>56</v>
       </c>
@@ -19304,9 +19304,9 @@
       </c>
     </row>
     <row r="49" spans="1:10" ht="24" x14ac:dyDescent="0.2">
-      <c r="A49" s="406"/>
-      <c r="B49" s="407"/>
-      <c r="C49" s="409"/>
+      <c r="A49" s="402"/>
+      <c r="B49" s="403"/>
+      <c r="C49" s="412"/>
       <c r="D49" s="237" t="s">
         <v>61</v>
       </c>
@@ -19326,9 +19326,9 @@
       </c>
     </row>
     <row r="50" spans="1:10" ht="117.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A50" s="406"/>
-      <c r="B50" s="407"/>
-      <c r="C50" s="409"/>
+      <c r="A50" s="402"/>
+      <c r="B50" s="403"/>
+      <c r="C50" s="412"/>
       <c r="D50" s="73" t="s">
         <v>63</v>
       </c>
@@ -19348,9 +19348,9 @@
       </c>
     </row>
     <row r="51" spans="1:10" ht="108" x14ac:dyDescent="0.2">
-      <c r="A51" s="406"/>
-      <c r="B51" s="407"/>
-      <c r="C51" s="409"/>
+      <c r="A51" s="402"/>
+      <c r="B51" s="403"/>
+      <c r="C51" s="412"/>
       <c r="D51" s="73" t="s">
         <v>68</v>
       </c>
@@ -19370,9 +19370,9 @@
       </c>
     </row>
     <row r="52" spans="1:10" ht="36" x14ac:dyDescent="0.2">
-      <c r="A52" s="406"/>
-      <c r="B52" s="407"/>
-      <c r="C52" s="409"/>
+      <c r="A52" s="402"/>
+      <c r="B52" s="403"/>
+      <c r="C52" s="412"/>
       <c r="D52" s="73" t="s">
         <v>143</v>
       </c>
@@ -19392,9 +19392,9 @@
       </c>
     </row>
     <row r="53" spans="1:10" ht="30" x14ac:dyDescent="0.2">
-      <c r="A53" s="406"/>
-      <c r="B53" s="407"/>
-      <c r="C53" s="409"/>
+      <c r="A53" s="402"/>
+      <c r="B53" s="403"/>
+      <c r="C53" s="412"/>
       <c r="D53" s="237" t="s">
         <v>76</v>
       </c>
@@ -19414,9 +19414,9 @@
       </c>
     </row>
     <row r="54" spans="1:10" ht="75" x14ac:dyDescent="0.2">
-      <c r="A54" s="406"/>
-      <c r="B54" s="407"/>
-      <c r="C54" s="409"/>
+      <c r="A54" s="402"/>
+      <c r="B54" s="403"/>
+      <c r="C54" s="412"/>
       <c r="D54" s="237" t="s">
         <v>79</v>
       </c>
@@ -19438,9 +19438,9 @@
       </c>
     </row>
     <row r="55" spans="1:10" ht="60" x14ac:dyDescent="0.2">
-      <c r="A55" s="406"/>
-      <c r="B55" s="407"/>
-      <c r="C55" s="409"/>
+      <c r="A55" s="402"/>
+      <c r="B55" s="403"/>
+      <c r="C55" s="412"/>
       <c r="D55" s="237" t="s">
         <v>83</v>
       </c>
@@ -19462,9 +19462,9 @@
       </c>
     </row>
     <row r="56" spans="1:10" ht="60" x14ac:dyDescent="0.2">
-      <c r="A56" s="406"/>
-      <c r="B56" s="407"/>
-      <c r="C56" s="409"/>
+      <c r="A56" s="402"/>
+      <c r="B56" s="403"/>
+      <c r="C56" s="412"/>
       <c r="D56" s="73" t="s">
         <v>106</v>
       </c>
@@ -19486,9 +19486,9 @@
       </c>
     </row>
     <row r="57" spans="1:10" ht="30" x14ac:dyDescent="0.2">
-      <c r="A57" s="406"/>
-      <c r="B57" s="407"/>
-      <c r="C57" s="409"/>
+      <c r="A57" s="402"/>
+      <c r="B57" s="403"/>
+      <c r="C57" s="412"/>
       <c r="D57" s="73" t="s">
         <v>92</v>
       </c>
@@ -19510,9 +19510,9 @@
       </c>
     </row>
     <row r="58" spans="1:10" ht="45" x14ac:dyDescent="0.2">
-      <c r="A58" s="406"/>
-      <c r="B58" s="407"/>
-      <c r="C58" s="409"/>
+      <c r="A58" s="402"/>
+      <c r="B58" s="403"/>
+      <c r="C58" s="412"/>
       <c r="D58" s="73" t="s">
         <v>94</v>
       </c>
@@ -19534,6 +19534,17 @@
   </sheetData>
   <autoFilter ref="A2:EC43" xr:uid="{92218EDD-6442-41B5-9565-D949ECDDA5BC}"/>
   <mergeCells count="21">
+    <mergeCell ref="A26:A35"/>
+    <mergeCell ref="B26:B35"/>
+    <mergeCell ref="C26:C35"/>
+    <mergeCell ref="D29:D30"/>
+    <mergeCell ref="E29:E30"/>
+    <mergeCell ref="A47:A58"/>
+    <mergeCell ref="B47:B58"/>
+    <mergeCell ref="C47:C58"/>
+    <mergeCell ref="A36:A45"/>
+    <mergeCell ref="B36:B45"/>
+    <mergeCell ref="C36:C45"/>
     <mergeCell ref="I1:J1"/>
     <mergeCell ref="A4:A15"/>
     <mergeCell ref="B4:B15"/>
@@ -19544,17 +19555,6 @@
     <mergeCell ref="D19:D20"/>
     <mergeCell ref="E19:E20"/>
     <mergeCell ref="A1:G1"/>
-    <mergeCell ref="A47:A58"/>
-    <mergeCell ref="B47:B58"/>
-    <mergeCell ref="C47:C58"/>
-    <mergeCell ref="A36:A45"/>
-    <mergeCell ref="B36:B45"/>
-    <mergeCell ref="C36:C45"/>
-    <mergeCell ref="A26:A35"/>
-    <mergeCell ref="B26:B35"/>
-    <mergeCell ref="C26:C35"/>
-    <mergeCell ref="D29:D30"/>
-    <mergeCell ref="E29:E30"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait"/>
@@ -19593,11 +19593,11 @@
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A4" s="4"/>
-      <c r="B4" s="452" t="s">
+      <c r="B4" s="453" t="s">
         <v>157</v>
       </c>
-      <c r="C4" s="453"/>
-      <c r="D4" s="454"/>
+      <c r="C4" s="454"/>
+      <c r="D4" s="455"/>
       <c r="E4" s="153" t="s">
         <v>383</v>
       </c>
@@ -19858,46 +19858,46 @@
       </c>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="C31" s="512" t="s">
+      <c r="C31" s="513" t="s">
         <v>265</v>
       </c>
-      <c r="D31" s="512" t="s">
+      <c r="D31" s="513" t="s">
         <v>389</v>
       </c>
-      <c r="E31" s="512" t="s">
+      <c r="E31" s="513" t="s">
         <v>205</v>
       </c>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="C32" s="513"/>
-      <c r="D32" s="513"/>
-      <c r="E32" s="513"/>
+      <c r="C32" s="514"/>
+      <c r="D32" s="514"/>
+      <c r="E32" s="514"/>
     </row>
     <row r="33" spans="3:6" x14ac:dyDescent="0.2">
-      <c r="C33" s="514"/>
-      <c r="D33" s="514"/>
-      <c r="E33" s="514"/>
+      <c r="C33" s="515"/>
+      <c r="D33" s="515"/>
+      <c r="E33" s="515"/>
     </row>
     <row r="34" spans="3:6" x14ac:dyDescent="0.2">
-      <c r="C34" s="515" t="s">
+      <c r="C34" s="516" t="s">
         <v>266</v>
       </c>
-      <c r="D34" s="515" t="s">
+      <c r="D34" s="516" t="s">
         <v>206</v>
       </c>
-      <c r="E34" s="515" t="s">
+      <c r="E34" s="516" t="s">
         <v>205</v>
       </c>
     </row>
     <row r="35" spans="3:6" x14ac:dyDescent="0.2">
-      <c r="C35" s="516"/>
-      <c r="D35" s="516"/>
-      <c r="E35" s="516"/>
+      <c r="C35" s="517"/>
+      <c r="D35" s="517"/>
+      <c r="E35" s="517"/>
     </row>
     <row r="36" spans="3:6" x14ac:dyDescent="0.2">
-      <c r="C36" s="517"/>
-      <c r="D36" s="517"/>
-      <c r="E36" s="517"/>
+      <c r="C36" s="518"/>
+      <c r="D36" s="518"/>
+      <c r="E36" s="518"/>
     </row>
     <row r="37" spans="3:6" x14ac:dyDescent="0.2">
       <c r="C37" s="124" t="s">
@@ -20014,32 +20014,32 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:138" s="31" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="518"/>
-      <c r="B1" s="518"/>
-      <c r="C1" s="518"/>
-      <c r="D1" s="518"/>
-      <c r="E1" s="518"/>
-      <c r="F1" s="518"/>
-      <c r="G1" s="518"/>
+      <c r="A1" s="520"/>
+      <c r="B1" s="520"/>
+      <c r="C1" s="520"/>
+      <c r="D1" s="520"/>
+      <c r="E1" s="520"/>
+      <c r="F1" s="520"/>
+      <c r="G1" s="520"/>
       <c r="H1" s="104"/>
       <c r="I1" s="101"/>
       <c r="J1" s="102"/>
     </row>
     <row r="2" spans="1:138" s="31" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="519" t="s">
+      <c r="A2" s="521" t="s">
         <v>393</v>
       </c>
-      <c r="B2" s="519"/>
-      <c r="C2" s="519"/>
-      <c r="D2" s="519"/>
-      <c r="E2" s="519"/>
-      <c r="F2" s="519"/>
-      <c r="G2" s="519"/>
+      <c r="B2" s="521"/>
+      <c r="C2" s="521"/>
+      <c r="D2" s="521"/>
+      <c r="E2" s="521"/>
+      <c r="F2" s="521"/>
+      <c r="G2" s="521"/>
       <c r="H2" s="105"/>
-      <c r="I2" s="413" t="s">
+      <c r="I2" s="394" t="s">
         <v>376</v>
       </c>
-      <c r="J2" s="413"/>
+      <c r="J2" s="394"/>
     </row>
     <row r="3" spans="1:138" s="31" customFormat="1" ht="9.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="64"/>
@@ -20083,13 +20083,13 @@
       </c>
     </row>
     <row r="5" spans="1:138" ht="72.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="481">
+      <c r="A5" s="468">
         <v>1</v>
       </c>
-      <c r="B5" s="416" t="s">
+      <c r="B5" s="397" t="s">
         <v>394</v>
       </c>
-      <c r="C5" s="421" t="s">
+      <c r="C5" s="404" t="s">
         <v>395</v>
       </c>
       <c r="D5" s="73" t="s">
@@ -20111,9 +20111,9 @@
       </c>
     </row>
     <row r="6" spans="1:138" ht="72.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="482"/>
-      <c r="B6" s="417"/>
-      <c r="C6" s="422"/>
+      <c r="A6" s="469"/>
+      <c r="B6" s="398"/>
+      <c r="C6" s="405"/>
       <c r="D6" s="73" t="s">
         <v>56</v>
       </c>
@@ -20133,9 +20133,9 @@
       </c>
     </row>
     <row r="7" spans="1:138" ht="60" x14ac:dyDescent="0.2">
-      <c r="A7" s="482"/>
-      <c r="B7" s="417"/>
-      <c r="C7" s="422"/>
+      <c r="A7" s="469"/>
+      <c r="B7" s="398"/>
+      <c r="C7" s="405"/>
       <c r="D7" s="73" t="s">
         <v>55</v>
       </c>
@@ -20155,9 +20155,9 @@
       </c>
     </row>
     <row r="8" spans="1:138" ht="210" x14ac:dyDescent="0.2">
-      <c r="A8" s="482"/>
-      <c r="B8" s="417"/>
-      <c r="C8" s="422"/>
+      <c r="A8" s="469"/>
+      <c r="B8" s="398"/>
+      <c r="C8" s="405"/>
       <c r="D8" s="73" t="s">
         <v>63</v>
       </c>
@@ -20178,9 +20178,9 @@
       <c r="K8" s="38"/>
     </row>
     <row r="9" spans="1:138" ht="150" x14ac:dyDescent="0.2">
-      <c r="A9" s="482"/>
-      <c r="B9" s="417"/>
-      <c r="C9" s="422"/>
+      <c r="A9" s="469"/>
+      <c r="B9" s="398"/>
+      <c r="C9" s="405"/>
       <c r="D9" s="73" t="s">
         <v>68</v>
       </c>
@@ -20200,9 +20200,9 @@
       </c>
     </row>
     <row r="10" spans="1:138" ht="60" x14ac:dyDescent="0.2">
-      <c r="A10" s="482"/>
-      <c r="B10" s="417"/>
-      <c r="C10" s="422"/>
+      <c r="A10" s="469"/>
+      <c r="B10" s="398"/>
+      <c r="C10" s="405"/>
       <c r="D10" s="73" t="s">
         <v>72</v>
       </c>
@@ -20222,9 +20222,9 @@
       </c>
     </row>
     <row r="11" spans="1:138" ht="409.6" x14ac:dyDescent="0.2">
-      <c r="A11" s="482"/>
-      <c r="B11" s="417"/>
-      <c r="C11" s="422"/>
+      <c r="A11" s="469"/>
+      <c r="B11" s="398"/>
+      <c r="C11" s="405"/>
       <c r="D11" s="73" t="s">
         <v>86</v>
       </c>
@@ -20246,9 +20246,9 @@
       </c>
     </row>
     <row r="12" spans="1:138" s="42" customFormat="1" ht="347.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A12" s="482"/>
-      <c r="B12" s="417"/>
-      <c r="C12" s="422"/>
+      <c r="A12" s="469"/>
+      <c r="B12" s="398"/>
+      <c r="C12" s="405"/>
       <c r="D12" s="73" t="s">
         <v>92</v>
       </c>
@@ -20398,9 +20398,9 @@
       <c r="EH12" s="41"/>
     </row>
     <row r="13" spans="1:138" ht="45" x14ac:dyDescent="0.2">
-      <c r="A13" s="482"/>
-      <c r="B13" s="417"/>
-      <c r="C13" s="422"/>
+      <c r="A13" s="469"/>
+      <c r="B13" s="398"/>
+      <c r="C13" s="405"/>
       <c r="D13" s="73" t="s">
         <v>277</v>
       </c>
@@ -20420,13 +20420,13 @@
       </c>
     </row>
     <row r="14" spans="1:138" ht="45" x14ac:dyDescent="0.2">
-      <c r="A14" s="486">
+      <c r="A14" s="473">
         <v>1.1000000000000001</v>
       </c>
-      <c r="B14" s="487" t="s">
+      <c r="B14" s="474" t="s">
         <v>98</v>
       </c>
-      <c r="C14" s="421" t="s">
+      <c r="C14" s="404" t="s">
         <v>396</v>
       </c>
       <c r="D14" s="73" t="s">
@@ -20448,9 +20448,9 @@
       </c>
     </row>
     <row r="15" spans="1:138" ht="40.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A15" s="486"/>
-      <c r="B15" s="487"/>
-      <c r="C15" s="520"/>
+      <c r="A15" s="473"/>
+      <c r="B15" s="474"/>
+      <c r="C15" s="519"/>
       <c r="D15" s="73" t="s">
         <v>56</v>
       </c>
@@ -20472,9 +20472,9 @@
       </c>
     </row>
     <row r="16" spans="1:138" ht="140.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A16" s="486"/>
-      <c r="B16" s="487"/>
-      <c r="C16" s="520"/>
+      <c r="A16" s="473"/>
+      <c r="B16" s="474"/>
+      <c r="C16" s="519"/>
       <c r="D16" s="73" t="s">
         <v>55</v>
       </c>
@@ -20497,9 +20497,9 @@
       <c r="K16" s="38"/>
     </row>
     <row r="17" spans="1:138" s="47" customFormat="1" ht="126" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A17" s="486"/>
-      <c r="B17" s="487"/>
-      <c r="C17" s="520"/>
+      <c r="A17" s="473"/>
+      <c r="B17" s="474"/>
+      <c r="C17" s="519"/>
       <c r="D17" s="76" t="s">
         <v>106</v>
       </c>
@@ -20649,9 +20649,9 @@
       <c r="EH17" s="36"/>
     </row>
     <row r="18" spans="1:138" s="47" customFormat="1" ht="129.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A18" s="486"/>
-      <c r="B18" s="487"/>
-      <c r="C18" s="520"/>
+      <c r="A18" s="473"/>
+      <c r="B18" s="474"/>
+      <c r="C18" s="519"/>
       <c r="D18" s="76" t="s">
         <v>92</v>
       </c>
@@ -20801,9 +20801,9 @@
       <c r="EH18" s="36"/>
     </row>
     <row r="19" spans="1:138" ht="45" x14ac:dyDescent="0.2">
-      <c r="A19" s="481"/>
-      <c r="B19" s="488"/>
-      <c r="C19" s="520"/>
+      <c r="A19" s="468"/>
+      <c r="B19" s="475"/>
+      <c r="C19" s="519"/>
       <c r="D19" s="78" t="s">
         <v>277</v>
       </c>
@@ -20823,10 +20823,10 @@
       </c>
     </row>
     <row r="20" spans="1:138" ht="45" x14ac:dyDescent="0.2">
-      <c r="A20" s="467">
+      <c r="A20" s="476">
         <v>2</v>
       </c>
-      <c r="B20" s="468" t="s">
+      <c r="B20" s="477" t="s">
         <v>109</v>
       </c>
       <c r="C20" s="461" t="s">
@@ -20851,9 +20851,9 @@
       </c>
     </row>
     <row r="21" spans="1:138" ht="45" x14ac:dyDescent="0.2">
-      <c r="A21" s="467"/>
-      <c r="B21" s="468"/>
-      <c r="C21" s="510"/>
+      <c r="A21" s="476"/>
+      <c r="B21" s="477"/>
+      <c r="C21" s="511"/>
       <c r="D21" s="73" t="s">
         <v>56</v>
       </c>
@@ -20875,9 +20875,9 @@
       </c>
     </row>
     <row r="22" spans="1:138" ht="60" x14ac:dyDescent="0.2">
-      <c r="A22" s="467"/>
-      <c r="B22" s="468"/>
-      <c r="C22" s="510"/>
+      <c r="A22" s="476"/>
+      <c r="B22" s="477"/>
+      <c r="C22" s="511"/>
       <c r="D22" s="73" t="s">
         <v>55</v>
       </c>
@@ -20899,9 +20899,9 @@
       </c>
     </row>
     <row r="23" spans="1:138" s="47" customFormat="1" ht="60" x14ac:dyDescent="0.2">
-      <c r="A23" s="467"/>
-      <c r="B23" s="468"/>
-      <c r="C23" s="510"/>
+      <c r="A23" s="476"/>
+      <c r="B23" s="477"/>
+      <c r="C23" s="511"/>
       <c r="D23" s="61" t="s">
         <v>114</v>
       </c>
@@ -21051,9 +21051,9 @@
       <c r="EH23" s="36"/>
     </row>
     <row r="24" spans="1:138" s="47" customFormat="1" ht="60" x14ac:dyDescent="0.2">
-      <c r="A24" s="467"/>
-      <c r="B24" s="468"/>
-      <c r="C24" s="510"/>
+      <c r="A24" s="476"/>
+      <c r="B24" s="477"/>
+      <c r="C24" s="511"/>
       <c r="D24" s="86" t="s">
         <v>92</v>
       </c>
@@ -21203,9 +21203,9 @@
       <c r="EH24" s="36"/>
     </row>
     <row r="25" spans="1:138" ht="30" x14ac:dyDescent="0.2">
-      <c r="A25" s="467"/>
-      <c r="B25" s="468"/>
-      <c r="C25" s="511"/>
+      <c r="A25" s="476"/>
+      <c r="B25" s="477"/>
+      <c r="C25" s="512"/>
       <c r="D25" s="76" t="s">
         <v>94</v>
       </c>
@@ -21225,13 +21225,13 @@
       </c>
     </row>
     <row r="26" spans="1:138" ht="60" x14ac:dyDescent="0.2">
-      <c r="A26" s="472">
+      <c r="A26" s="481">
         <v>2.1</v>
       </c>
-      <c r="B26" s="475" t="s">
+      <c r="B26" s="484" t="s">
         <v>116</v>
       </c>
-      <c r="C26" s="478" t="s">
+      <c r="C26" s="487" t="s">
         <v>117</v>
       </c>
       <c r="D26" s="83" t="s">
@@ -21253,9 +21253,9 @@
       </c>
     </row>
     <row r="27" spans="1:138" ht="105" x14ac:dyDescent="0.2">
-      <c r="A27" s="473"/>
-      <c r="B27" s="476"/>
-      <c r="C27" s="479"/>
+      <c r="A27" s="482"/>
+      <c r="B27" s="485"/>
+      <c r="C27" s="488"/>
       <c r="D27" s="83" t="s">
         <v>130</v>
       </c>
@@ -21275,9 +21275,9 @@
       </c>
     </row>
     <row r="28" spans="1:138" ht="60" x14ac:dyDescent="0.2">
-      <c r="A28" s="473"/>
-      <c r="B28" s="476"/>
-      <c r="C28" s="479"/>
+      <c r="A28" s="482"/>
+      <c r="B28" s="485"/>
+      <c r="C28" s="488"/>
       <c r="D28" s="73" t="s">
         <v>55</v>
       </c>
@@ -21299,9 +21299,9 @@
       </c>
     </row>
     <row r="29" spans="1:138" ht="60" x14ac:dyDescent="0.2">
-      <c r="A29" s="473"/>
-      <c r="B29" s="476"/>
-      <c r="C29" s="479"/>
+      <c r="A29" s="482"/>
+      <c r="B29" s="485"/>
+      <c r="C29" s="488"/>
       <c r="D29" s="61" t="s">
         <v>114</v>
       </c>
@@ -21323,9 +21323,9 @@
       </c>
     </row>
     <row r="30" spans="1:138" ht="30" x14ac:dyDescent="0.2">
-      <c r="A30" s="473"/>
-      <c r="B30" s="476"/>
-      <c r="C30" s="479"/>
+      <c r="A30" s="482"/>
+      <c r="B30" s="485"/>
+      <c r="C30" s="488"/>
       <c r="D30" s="86" t="s">
         <v>92</v>
       </c>
@@ -21347,9 +21347,9 @@
       </c>
     </row>
     <row r="31" spans="1:138" ht="30" x14ac:dyDescent="0.2">
-      <c r="A31" s="474"/>
-      <c r="B31" s="477"/>
-      <c r="C31" s="480"/>
+      <c r="A31" s="483"/>
+      <c r="B31" s="486"/>
+      <c r="C31" s="489"/>
       <c r="D31" s="76" t="s">
         <v>94</v>
       </c>
@@ -21369,13 +21369,13 @@
       </c>
     </row>
     <row r="32" spans="1:138" ht="60" x14ac:dyDescent="0.2">
-      <c r="A32" s="507">
+      <c r="A32" s="508">
         <v>3</v>
       </c>
-      <c r="B32" s="504" t="s">
+      <c r="B32" s="505" t="s">
         <v>336</v>
       </c>
-      <c r="C32" s="501" t="s">
+      <c r="C32" s="502" t="s">
         <v>337</v>
       </c>
       <c r="D32" s="157" t="s">
@@ -21397,9 +21397,9 @@
       </c>
     </row>
     <row r="33" spans="1:10" ht="105" x14ac:dyDescent="0.2">
-      <c r="A33" s="508"/>
-      <c r="B33" s="505"/>
-      <c r="C33" s="502"/>
+      <c r="A33" s="509"/>
+      <c r="B33" s="506"/>
+      <c r="C33" s="503"/>
       <c r="D33" s="157" t="s">
         <v>341</v>
       </c>
@@ -21419,9 +21419,9 @@
       </c>
     </row>
     <row r="34" spans="1:10" ht="90" x14ac:dyDescent="0.2">
-      <c r="A34" s="508"/>
-      <c r="B34" s="505"/>
-      <c r="C34" s="502"/>
+      <c r="A34" s="509"/>
+      <c r="B34" s="506"/>
+      <c r="C34" s="503"/>
       <c r="D34" s="80" t="s">
         <v>114</v>
       </c>
@@ -21443,9 +21443,9 @@
       </c>
     </row>
     <row r="35" spans="1:10" ht="90" x14ac:dyDescent="0.2">
-      <c r="A35" s="508"/>
-      <c r="B35" s="505"/>
-      <c r="C35" s="502"/>
+      <c r="A35" s="509"/>
+      <c r="B35" s="506"/>
+      <c r="C35" s="503"/>
       <c r="D35" s="91" t="s">
         <v>92</v>
       </c>
@@ -21467,9 +21467,9 @@
       </c>
     </row>
     <row r="36" spans="1:10" ht="90" x14ac:dyDescent="0.2">
-      <c r="A36" s="509"/>
-      <c r="B36" s="506"/>
-      <c r="C36" s="503"/>
+      <c r="A36" s="510"/>
+      <c r="B36" s="507"/>
+      <c r="C36" s="504"/>
       <c r="D36" s="83" t="s">
         <v>94</v>
       </c>
@@ -21491,24 +21491,24 @@
   </sheetData>
   <autoFilter ref="A4:EH32" xr:uid="{92218EDD-6442-41B5-9565-D949ECDDA5BC}"/>
   <mergeCells count="18">
+    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="A2:G2"/>
+    <mergeCell ref="I2:J2"/>
+    <mergeCell ref="A5:A13"/>
+    <mergeCell ref="B5:B13"/>
+    <mergeCell ref="C5:C13"/>
+    <mergeCell ref="A14:A19"/>
+    <mergeCell ref="B14:B19"/>
+    <mergeCell ref="C14:C19"/>
+    <mergeCell ref="A20:A25"/>
+    <mergeCell ref="B20:B25"/>
+    <mergeCell ref="C20:C25"/>
     <mergeCell ref="A26:A31"/>
     <mergeCell ref="B26:B31"/>
     <mergeCell ref="C26:C31"/>
     <mergeCell ref="A32:A36"/>
     <mergeCell ref="B32:B36"/>
     <mergeCell ref="C32:C36"/>
-    <mergeCell ref="A14:A19"/>
-    <mergeCell ref="B14:B19"/>
-    <mergeCell ref="C14:C19"/>
-    <mergeCell ref="A20:A25"/>
-    <mergeCell ref="B20:B25"/>
-    <mergeCell ref="C20:C25"/>
-    <mergeCell ref="A1:G1"/>
-    <mergeCell ref="A2:G2"/>
-    <mergeCell ref="I2:J2"/>
-    <mergeCell ref="A5:A13"/>
-    <mergeCell ref="B5:B13"/>
-    <mergeCell ref="C5:C13"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait"/>
@@ -21536,33 +21536,33 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:139" s="31" customFormat="1" ht="20" x14ac:dyDescent="0.2">
-      <c r="A1" s="518"/>
-      <c r="B1" s="518"/>
-      <c r="C1" s="518"/>
-      <c r="D1" s="518"/>
-      <c r="E1" s="518"/>
-      <c r="F1" s="518"/>
-      <c r="G1" s="518"/>
+      <c r="A1" s="520"/>
+      <c r="B1" s="520"/>
+      <c r="C1" s="520"/>
+      <c r="D1" s="520"/>
+      <c r="E1" s="520"/>
+      <c r="F1" s="520"/>
+      <c r="G1" s="520"/>
       <c r="H1" s="104"/>
       <c r="I1" s="101"/>
       <c r="J1" s="102"/>
       <c r="K1" s="102"/>
     </row>
     <row r="2" spans="1:139" s="31" customFormat="1" ht="25" x14ac:dyDescent="0.2">
-      <c r="A2" s="519" t="s">
+      <c r="A2" s="521" t="s">
         <v>375</v>
       </c>
-      <c r="B2" s="519"/>
-      <c r="C2" s="519"/>
-      <c r="D2" s="519"/>
-      <c r="E2" s="519"/>
-      <c r="F2" s="519"/>
-      <c r="G2" s="519"/>
+      <c r="B2" s="521"/>
+      <c r="C2" s="521"/>
+      <c r="D2" s="521"/>
+      <c r="E2" s="521"/>
+      <c r="F2" s="521"/>
+      <c r="G2" s="521"/>
       <c r="H2" s="105"/>
-      <c r="I2" s="413" t="s">
+      <c r="I2" s="394" t="s">
         <v>376</v>
       </c>
-      <c r="J2" s="413"/>
+      <c r="J2" s="394"/>
       <c r="K2" s="103"/>
     </row>
     <row r="3" spans="1:139" s="31" customFormat="1" ht="20" x14ac:dyDescent="0.2">
@@ -21611,13 +21611,13 @@
       </c>
     </row>
     <row r="5" spans="1:139" ht="45" x14ac:dyDescent="0.2">
-      <c r="A5" s="481">
+      <c r="A5" s="468">
         <v>1</v>
       </c>
-      <c r="B5" s="416" t="s">
+      <c r="B5" s="397" t="s">
         <v>394</v>
       </c>
-      <c r="C5" s="500" t="s">
+      <c r="C5" s="501" t="s">
         <v>401</v>
       </c>
       <c r="D5" s="73" t="s">
@@ -21642,8 +21642,8 @@
       </c>
     </row>
     <row r="6" spans="1:139" ht="45" x14ac:dyDescent="0.2">
-      <c r="A6" s="482"/>
-      <c r="B6" s="417"/>
+      <c r="A6" s="469"/>
+      <c r="B6" s="398"/>
       <c r="C6" s="464"/>
       <c r="D6" s="73" t="s">
         <v>56</v>
@@ -21665,8 +21665,8 @@
       <c r="K6" s="35"/>
     </row>
     <row r="7" spans="1:139" ht="60" x14ac:dyDescent="0.2">
-      <c r="A7" s="482"/>
-      <c r="B7" s="417"/>
+      <c r="A7" s="469"/>
+      <c r="B7" s="398"/>
       <c r="C7" s="464"/>
       <c r="D7" s="73" t="s">
         <v>55</v>
@@ -21688,8 +21688,8 @@
       <c r="K7" s="35"/>
     </row>
     <row r="8" spans="1:139" ht="210" x14ac:dyDescent="0.2">
-      <c r="A8" s="482"/>
-      <c r="B8" s="417"/>
+      <c r="A8" s="469"/>
+      <c r="B8" s="398"/>
       <c r="C8" s="464"/>
       <c r="D8" s="73" t="s">
         <v>63</v>
@@ -21712,8 +21712,8 @@
       <c r="L8" s="38"/>
     </row>
     <row r="9" spans="1:139" ht="150" x14ac:dyDescent="0.2">
-      <c r="A9" s="482"/>
-      <c r="B9" s="417"/>
+      <c r="A9" s="469"/>
+      <c r="B9" s="398"/>
       <c r="C9" s="464"/>
       <c r="D9" s="73" t="s">
         <v>68</v>
@@ -21735,8 +21735,8 @@
       <c r="K9" s="35"/>
     </row>
     <row r="10" spans="1:139" ht="60" x14ac:dyDescent="0.2">
-      <c r="A10" s="482"/>
-      <c r="B10" s="417"/>
+      <c r="A10" s="469"/>
+      <c r="B10" s="398"/>
       <c r="C10" s="464"/>
       <c r="D10" s="73" t="s">
         <v>72</v>
@@ -21758,8 +21758,8 @@
       <c r="K10" s="35"/>
     </row>
     <row r="11" spans="1:139" ht="409.6" x14ac:dyDescent="0.2">
-      <c r="A11" s="482"/>
-      <c r="B11" s="417"/>
+      <c r="A11" s="469"/>
+      <c r="B11" s="398"/>
       <c r="C11" s="464"/>
       <c r="D11" s="73" t="s">
         <v>86</v>
@@ -21797,8 +21797,8 @@
       </c>
     </row>
     <row r="12" spans="1:139" s="42" customFormat="1" ht="409.6" x14ac:dyDescent="0.2">
-      <c r="A12" s="482"/>
-      <c r="B12" s="417"/>
+      <c r="A12" s="469"/>
+      <c r="B12" s="398"/>
       <c r="C12" s="464"/>
       <c r="D12" s="73" t="s">
         <v>92</v>
@@ -21964,8 +21964,8 @@
       <c r="EI12" s="41"/>
     </row>
     <row r="13" spans="1:139" ht="45" x14ac:dyDescent="0.2">
-      <c r="A13" s="482"/>
-      <c r="B13" s="417"/>
+      <c r="A13" s="469"/>
+      <c r="B13" s="398"/>
       <c r="C13" s="464"/>
       <c r="D13" s="73" t="s">
         <v>277</v>
@@ -21989,13 +21989,13 @@
       </c>
     </row>
     <row r="14" spans="1:139" ht="45" x14ac:dyDescent="0.2">
-      <c r="A14" s="486">
+      <c r="A14" s="473">
         <v>1.1000000000000001</v>
       </c>
-      <c r="B14" s="487" t="s">
+      <c r="B14" s="474" t="s">
         <v>98</v>
       </c>
-      <c r="C14" s="500" t="s">
+      <c r="C14" s="501" t="s">
         <v>402</v>
       </c>
       <c r="D14" s="73" t="s">
@@ -22020,9 +22020,9 @@
       </c>
     </row>
     <row r="15" spans="1:139" ht="45" x14ac:dyDescent="0.2">
-      <c r="A15" s="486"/>
-      <c r="B15" s="487"/>
-      <c r="C15" s="521"/>
+      <c r="A15" s="473"/>
+      <c r="B15" s="474"/>
+      <c r="C15" s="522"/>
       <c r="D15" s="73" t="s">
         <v>56</v>
       </c>
@@ -22045,9 +22045,9 @@
       <c r="K15" s="35"/>
     </row>
     <row r="16" spans="1:139" ht="409.6" x14ac:dyDescent="0.2">
-      <c r="A16" s="486"/>
-      <c r="B16" s="487"/>
-      <c r="C16" s="521"/>
+      <c r="A16" s="473"/>
+      <c r="B16" s="474"/>
+      <c r="C16" s="522"/>
       <c r="D16" s="73" t="s">
         <v>55</v>
       </c>
@@ -22085,9 +22085,9 @@
       <c r="L16" s="38"/>
     </row>
     <row r="17" spans="1:139" s="47" customFormat="1" ht="409.6" x14ac:dyDescent="0.2">
-      <c r="A17" s="486"/>
-      <c r="B17" s="487"/>
-      <c r="C17" s="521"/>
+      <c r="A17" s="473"/>
+      <c r="B17" s="474"/>
+      <c r="C17" s="522"/>
       <c r="D17" s="76" t="s">
         <v>106</v>
       </c>
@@ -22252,9 +22252,9 @@
       <c r="EI17" s="36"/>
     </row>
     <row r="18" spans="1:139" s="47" customFormat="1" ht="409.6" x14ac:dyDescent="0.2">
-      <c r="A18" s="486"/>
-      <c r="B18" s="487"/>
-      <c r="C18" s="521"/>
+      <c r="A18" s="473"/>
+      <c r="B18" s="474"/>
+      <c r="C18" s="522"/>
       <c r="D18" s="76" t="s">
         <v>92</v>
       </c>
@@ -22417,9 +22417,9 @@
       <c r="EI18" s="36"/>
     </row>
     <row r="19" spans="1:139" ht="45" x14ac:dyDescent="0.2">
-      <c r="A19" s="481"/>
-      <c r="B19" s="488"/>
-      <c r="C19" s="521"/>
+      <c r="A19" s="468"/>
+      <c r="B19" s="475"/>
+      <c r="C19" s="522"/>
       <c r="D19" s="78" t="s">
         <v>277</v>
       </c>
@@ -22442,10 +22442,10 @@
       </c>
     </row>
     <row r="20" spans="1:139" ht="45" x14ac:dyDescent="0.2">
-      <c r="A20" s="467">
+      <c r="A20" s="476">
         <v>2</v>
       </c>
-      <c r="B20" s="468" t="s">
+      <c r="B20" s="477" t="s">
         <v>109</v>
       </c>
       <c r="C20" s="461" t="s">
@@ -22471,9 +22471,9 @@
       <c r="K20" s="54"/>
     </row>
     <row r="21" spans="1:139" ht="45" x14ac:dyDescent="0.2">
-      <c r="A21" s="467"/>
-      <c r="B21" s="468"/>
-      <c r="C21" s="510"/>
+      <c r="A21" s="476"/>
+      <c r="B21" s="477"/>
+      <c r="C21" s="511"/>
       <c r="D21" s="73" t="s">
         <v>56</v>
       </c>
@@ -22496,9 +22496,9 @@
       <c r="K21" s="54"/>
     </row>
     <row r="22" spans="1:139" ht="75" x14ac:dyDescent="0.2">
-      <c r="A22" s="467"/>
-      <c r="B22" s="468"/>
-      <c r="C22" s="510"/>
+      <c r="A22" s="476"/>
+      <c r="B22" s="477"/>
+      <c r="C22" s="511"/>
       <c r="D22" s="73" t="s">
         <v>55</v>
       </c>
@@ -22523,9 +22523,9 @@
       </c>
     </row>
     <row r="23" spans="1:139" s="47" customFormat="1" ht="75" x14ac:dyDescent="0.2">
-      <c r="A23" s="467"/>
-      <c r="B23" s="468"/>
-      <c r="C23" s="510"/>
+      <c r="A23" s="476"/>
+      <c r="B23" s="477"/>
+      <c r="C23" s="511"/>
       <c r="D23" s="61" t="s">
         <v>114</v>
       </c>
@@ -22678,9 +22678,9 @@
       <c r="EI23" s="36"/>
     </row>
     <row r="24" spans="1:139" s="47" customFormat="1" ht="75" x14ac:dyDescent="0.2">
-      <c r="A24" s="467"/>
-      <c r="B24" s="468"/>
-      <c r="C24" s="510"/>
+      <c r="A24" s="476"/>
+      <c r="B24" s="477"/>
+      <c r="C24" s="511"/>
       <c r="D24" s="86" t="s">
         <v>92</v>
       </c>
@@ -22833,9 +22833,9 @@
       <c r="EI24" s="36"/>
     </row>
     <row r="25" spans="1:139" ht="30" x14ac:dyDescent="0.2">
-      <c r="A25" s="467"/>
-      <c r="B25" s="468"/>
-      <c r="C25" s="511"/>
+      <c r="A25" s="476"/>
+      <c r="B25" s="477"/>
+      <c r="C25" s="512"/>
       <c r="D25" s="76" t="s">
         <v>94</v>
       </c>
@@ -22858,13 +22858,13 @@
       </c>
     </row>
     <row r="26" spans="1:139" ht="90" x14ac:dyDescent="0.2">
-      <c r="A26" s="472">
+      <c r="A26" s="481">
         <v>2.1</v>
       </c>
-      <c r="B26" s="475" t="s">
+      <c r="B26" s="484" t="s">
         <v>116</v>
       </c>
-      <c r="C26" s="478" t="s">
+      <c r="C26" s="487" t="s">
         <v>117</v>
       </c>
       <c r="D26" s="76" t="s">
@@ -22887,9 +22887,9 @@
       <c r="K26" s="35"/>
     </row>
     <row r="27" spans="1:139" ht="75" x14ac:dyDescent="0.2">
-      <c r="A27" s="473"/>
-      <c r="B27" s="476"/>
-      <c r="C27" s="479"/>
+      <c r="A27" s="482"/>
+      <c r="B27" s="485"/>
+      <c r="C27" s="488"/>
       <c r="D27" s="73" t="s">
         <v>55</v>
       </c>
@@ -22912,9 +22912,9 @@
       <c r="K27" s="35"/>
     </row>
     <row r="28" spans="1:139" ht="75" x14ac:dyDescent="0.2">
-      <c r="A28" s="473"/>
-      <c r="B28" s="476"/>
-      <c r="C28" s="479"/>
+      <c r="A28" s="482"/>
+      <c r="B28" s="485"/>
+      <c r="C28" s="488"/>
       <c r="D28" s="61" t="s">
         <v>114</v>
       </c>
@@ -22937,9 +22937,9 @@
       <c r="K28" s="35"/>
     </row>
     <row r="29" spans="1:139" ht="75" x14ac:dyDescent="0.2">
-      <c r="A29" s="473"/>
-      <c r="B29" s="476"/>
-      <c r="C29" s="479"/>
+      <c r="A29" s="482"/>
+      <c r="B29" s="485"/>
+      <c r="C29" s="488"/>
       <c r="D29" s="86" t="s">
         <v>92</v>
       </c>
@@ -22962,9 +22962,9 @@
       <c r="K29" s="35"/>
     </row>
     <row r="30" spans="1:139" ht="30" x14ac:dyDescent="0.2">
-      <c r="A30" s="474"/>
-      <c r="B30" s="477"/>
-      <c r="C30" s="480"/>
+      <c r="A30" s="483"/>
+      <c r="B30" s="486"/>
+      <c r="C30" s="489"/>
       <c r="D30" s="76" t="s">
         <v>94</v>
       </c>
@@ -24177,6 +24177,12 @@
   </sheetData>
   <autoFilter ref="A4:EI31" xr:uid="{92218EDD-6442-41B5-9565-D949ECDDA5BC}"/>
   <mergeCells count="15">
+    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="A2:G2"/>
+    <mergeCell ref="I2:J2"/>
+    <mergeCell ref="A5:A13"/>
+    <mergeCell ref="B5:B13"/>
+    <mergeCell ref="C5:C13"/>
     <mergeCell ref="A26:A30"/>
     <mergeCell ref="B26:B30"/>
     <mergeCell ref="C26:C30"/>
@@ -24186,12 +24192,6 @@
     <mergeCell ref="A20:A25"/>
     <mergeCell ref="B20:B25"/>
     <mergeCell ref="C20:C25"/>
-    <mergeCell ref="A1:G1"/>
-    <mergeCell ref="A2:G2"/>
-    <mergeCell ref="I2:J2"/>
-    <mergeCell ref="A5:A13"/>
-    <mergeCell ref="B5:B13"/>
-    <mergeCell ref="C5:C13"/>
   </mergeCells>
   <dataValidations count="1">
     <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="K6:K7 K26" xr:uid="{71B7DFEE-6548-4738-BBF7-B2A60C74FD01}"/>
@@ -24232,11 +24232,11 @@
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A4" s="4"/>
-      <c r="B4" s="452" t="s">
+      <c r="B4" s="453" t="s">
         <v>157</v>
       </c>
-      <c r="C4" s="453"/>
-      <c r="D4" s="454"/>
+      <c r="C4" s="454"/>
+      <c r="D4" s="455"/>
       <c r="E4" s="153" t="s">
         <v>383</v>
       </c>
@@ -24498,15 +24498,15 @@
   <sheetData>
     <row r="1" spans="1:10" s="132" customFormat="1" ht="21" x14ac:dyDescent="0.25">
       <c r="A1" s="131"/>
-      <c r="B1" s="522" t="s">
+      <c r="B1" s="523" t="s">
         <v>412</v>
       </c>
-      <c r="C1" s="522"/>
-      <c r="E1" s="523" t="s">
+      <c r="C1" s="523"/>
+      <c r="E1" s="524" t="s">
         <v>413</v>
       </c>
-      <c r="F1" s="523"/>
-      <c r="G1" s="523"/>
+      <c r="F1" s="524"/>
+      <c r="G1" s="524"/>
     </row>
     <row r="2" spans="1:10" s="129" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="130" t="s">
@@ -24538,13 +24538,13 @@
       <c r="C3" s="133" t="s">
         <v>415</v>
       </c>
-      <c r="E3" s="512" t="s">
+      <c r="E3" s="513" t="s">
         <v>265</v>
       </c>
-      <c r="F3" s="512" t="s">
+      <c r="F3" s="513" t="s">
         <v>389</v>
       </c>
-      <c r="G3" s="512" t="s">
+      <c r="G3" s="513" t="s">
         <v>205</v>
       </c>
       <c r="J3" t="s">
@@ -24561,9 +24561,9 @@
       <c r="C4" s="133" t="s">
         <v>418</v>
       </c>
-      <c r="E4" s="513"/>
-      <c r="F4" s="513"/>
-      <c r="G4" s="513"/>
+      <c r="E4" s="514"/>
+      <c r="F4" s="514"/>
+      <c r="G4" s="514"/>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A5" s="125">
@@ -24575,9 +24575,9 @@
       <c r="C5" s="133" t="s">
         <v>420</v>
       </c>
-      <c r="E5" s="514"/>
-      <c r="F5" s="514"/>
-      <c r="G5" s="514"/>
+      <c r="E5" s="515"/>
+      <c r="F5" s="515"/>
+      <c r="G5" s="515"/>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A6" s="126">
@@ -24589,13 +24589,13 @@
       <c r="C6" s="134" t="s">
         <v>422</v>
       </c>
-      <c r="E6" s="515" t="s">
+      <c r="E6" s="516" t="s">
         <v>266</v>
       </c>
-      <c r="F6" s="515" t="s">
+      <c r="F6" s="516" t="s">
         <v>206</v>
       </c>
-      <c r="G6" s="515" t="s">
+      <c r="G6" s="516" t="s">
         <v>205</v>
       </c>
       <c r="I6" t="s">
@@ -24615,9 +24615,9 @@
       <c r="C7" s="134" t="s">
         <v>425</v>
       </c>
-      <c r="E7" s="516"/>
-      <c r="F7" s="516"/>
-      <c r="G7" s="516"/>
+      <c r="E7" s="517"/>
+      <c r="F7" s="517"/>
+      <c r="G7" s="517"/>
       <c r="I7" t="s">
         <v>426</v>
       </c>
@@ -24635,9 +24635,9 @@
       <c r="C8" s="134" t="s">
         <v>428</v>
       </c>
-      <c r="E8" s="517"/>
-      <c r="F8" s="517"/>
-      <c r="G8" s="517"/>
+      <c r="E8" s="518"/>
+      <c r="F8" s="518"/>
+      <c r="G8" s="518"/>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A9" s="127">
@@ -24801,33 +24801,33 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:139" s="31" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="518"/>
-      <c r="B1" s="518"/>
-      <c r="C1" s="518"/>
-      <c r="D1" s="518"/>
-      <c r="E1" s="518"/>
-      <c r="F1" s="518"/>
-      <c r="G1" s="518"/>
+      <c r="A1" s="520"/>
+      <c r="B1" s="520"/>
+      <c r="C1" s="520"/>
+      <c r="D1" s="520"/>
+      <c r="E1" s="520"/>
+      <c r="F1" s="520"/>
+      <c r="G1" s="520"/>
       <c r="H1" s="104"/>
       <c r="I1" s="101"/>
       <c r="J1" s="102"/>
       <c r="K1" s="102"/>
     </row>
     <row r="2" spans="1:139" s="31" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="519" t="s">
+      <c r="A2" s="521" t="s">
         <v>393</v>
       </c>
-      <c r="B2" s="519"/>
-      <c r="C2" s="519"/>
-      <c r="D2" s="519"/>
-      <c r="E2" s="519"/>
-      <c r="F2" s="519"/>
-      <c r="G2" s="519"/>
+      <c r="B2" s="521"/>
+      <c r="C2" s="521"/>
+      <c r="D2" s="521"/>
+      <c r="E2" s="521"/>
+      <c r="F2" s="521"/>
+      <c r="G2" s="521"/>
       <c r="H2" s="105"/>
-      <c r="I2" s="413" t="s">
+      <c r="I2" s="394" t="s">
         <v>376</v>
       </c>
-      <c r="J2" s="413"/>
+      <c r="J2" s="394"/>
       <c r="K2" s="103"/>
     </row>
     <row r="3" spans="1:139" s="31" customFormat="1" ht="9.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -24876,13 +24876,13 @@
       </c>
     </row>
     <row r="5" spans="1:139" ht="72.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="481">
+      <c r="A5" s="468">
         <v>1</v>
       </c>
-      <c r="B5" s="416" t="s">
+      <c r="B5" s="397" t="s">
         <v>394</v>
       </c>
-      <c r="C5" s="421" t="s">
+      <c r="C5" s="404" t="s">
         <v>395</v>
       </c>
       <c r="D5" s="73" t="s">
@@ -24907,9 +24907,9 @@
       </c>
     </row>
     <row r="6" spans="1:139" ht="72.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="482"/>
-      <c r="B6" s="417"/>
-      <c r="C6" s="422"/>
+      <c r="A6" s="469"/>
+      <c r="B6" s="398"/>
+      <c r="C6" s="405"/>
       <c r="D6" s="73" t="s">
         <v>56</v>
       </c>
@@ -24930,9 +24930,9 @@
       <c r="K6" s="35"/>
     </row>
     <row r="7" spans="1:139" ht="60" x14ac:dyDescent="0.2">
-      <c r="A7" s="482"/>
-      <c r="B7" s="417"/>
-      <c r="C7" s="422"/>
+      <c r="A7" s="469"/>
+      <c r="B7" s="398"/>
+      <c r="C7" s="405"/>
       <c r="D7" s="73" t="s">
         <v>55</v>
       </c>
@@ -24953,9 +24953,9 @@
       <c r="K7" s="35"/>
     </row>
     <row r="8" spans="1:139" ht="210" x14ac:dyDescent="0.2">
-      <c r="A8" s="482"/>
-      <c r="B8" s="417"/>
-      <c r="C8" s="422"/>
+      <c r="A8" s="469"/>
+      <c r="B8" s="398"/>
+      <c r="C8" s="405"/>
       <c r="D8" s="73" t="s">
         <v>63</v>
       </c>
@@ -24977,9 +24977,9 @@
       <c r="L8" s="38"/>
     </row>
     <row r="9" spans="1:139" ht="150" x14ac:dyDescent="0.2">
-      <c r="A9" s="482"/>
-      <c r="B9" s="417"/>
-      <c r="C9" s="422"/>
+      <c r="A9" s="469"/>
+      <c r="B9" s="398"/>
+      <c r="C9" s="405"/>
       <c r="D9" s="73" t="s">
         <v>68</v>
       </c>
@@ -25000,9 +25000,9 @@
       <c r="K9" s="35"/>
     </row>
     <row r="10" spans="1:139" ht="60" x14ac:dyDescent="0.2">
-      <c r="A10" s="482"/>
-      <c r="B10" s="417"/>
-      <c r="C10" s="422"/>
+      <c r="A10" s="469"/>
+      <c r="B10" s="398"/>
+      <c r="C10" s="405"/>
       <c r="D10" s="73" t="s">
         <v>72</v>
       </c>
@@ -25023,9 +25023,9 @@
       <c r="K10" s="35"/>
     </row>
     <row r="11" spans="1:139" ht="409.6" x14ac:dyDescent="0.2">
-      <c r="A11" s="482"/>
-      <c r="B11" s="417"/>
-      <c r="C11" s="422"/>
+      <c r="A11" s="469"/>
+      <c r="B11" s="398"/>
+      <c r="C11" s="405"/>
       <c r="D11" s="73" t="s">
         <v>86</v>
       </c>
@@ -25050,9 +25050,9 @@
       </c>
     </row>
     <row r="12" spans="1:139" s="42" customFormat="1" ht="347.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A12" s="482"/>
-      <c r="B12" s="417"/>
-      <c r="C12" s="422"/>
+      <c r="A12" s="469"/>
+      <c r="B12" s="398"/>
+      <c r="C12" s="405"/>
       <c r="D12" s="73" t="s">
         <v>92</v>
       </c>
@@ -25205,9 +25205,9 @@
       <c r="EI12" s="41"/>
     </row>
     <row r="13" spans="1:139" ht="45" x14ac:dyDescent="0.2">
-      <c r="A13" s="482"/>
-      <c r="B13" s="417"/>
-      <c r="C13" s="422"/>
+      <c r="A13" s="469"/>
+      <c r="B13" s="398"/>
+      <c r="C13" s="405"/>
       <c r="D13" s="73" t="s">
         <v>277</v>
       </c>
@@ -25230,13 +25230,13 @@
       </c>
     </row>
     <row r="14" spans="1:139" ht="45" x14ac:dyDescent="0.2">
-      <c r="A14" s="486">
+      <c r="A14" s="473">
         <v>1.1000000000000001</v>
       </c>
-      <c r="B14" s="487" t="s">
+      <c r="B14" s="474" t="s">
         <v>98</v>
       </c>
-      <c r="C14" s="421" t="s">
+      <c r="C14" s="404" t="s">
         <v>396</v>
       </c>
       <c r="D14" s="73" t="s">
@@ -25261,9 +25261,9 @@
       </c>
     </row>
     <row r="15" spans="1:139" ht="40.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A15" s="486"/>
-      <c r="B15" s="487"/>
-      <c r="C15" s="520"/>
+      <c r="A15" s="473"/>
+      <c r="B15" s="474"/>
+      <c r="C15" s="519"/>
       <c r="D15" s="73" t="s">
         <v>56</v>
       </c>
@@ -25286,9 +25286,9 @@
       <c r="K15" s="35"/>
     </row>
     <row r="16" spans="1:139" ht="140.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A16" s="486"/>
-      <c r="B16" s="487"/>
-      <c r="C16" s="520"/>
+      <c r="A16" s="473"/>
+      <c r="B16" s="474"/>
+      <c r="C16" s="519"/>
       <c r="D16" s="73" t="s">
         <v>55</v>
       </c>
@@ -25314,9 +25314,9 @@
       <c r="L16" s="38"/>
     </row>
     <row r="17" spans="1:139" s="47" customFormat="1" ht="126" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A17" s="486"/>
-      <c r="B17" s="487"/>
-      <c r="C17" s="520"/>
+      <c r="A17" s="473"/>
+      <c r="B17" s="474"/>
+      <c r="C17" s="519"/>
       <c r="D17" s="76" t="s">
         <v>106</v>
       </c>
@@ -25469,9 +25469,9 @@
       <c r="EI17" s="36"/>
     </row>
     <row r="18" spans="1:139" s="47" customFormat="1" ht="129.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A18" s="486"/>
-      <c r="B18" s="487"/>
-      <c r="C18" s="520"/>
+      <c r="A18" s="473"/>
+      <c r="B18" s="474"/>
+      <c r="C18" s="519"/>
       <c r="D18" s="76" t="s">
         <v>92</v>
       </c>
@@ -25622,9 +25622,9 @@
       <c r="EI18" s="36"/>
     </row>
     <row r="19" spans="1:139" ht="45" x14ac:dyDescent="0.2">
-      <c r="A19" s="481"/>
-      <c r="B19" s="488"/>
-      <c r="C19" s="520"/>
+      <c r="A19" s="468"/>
+      <c r="B19" s="475"/>
+      <c r="C19" s="519"/>
       <c r="D19" s="78" t="s">
         <v>277</v>
       </c>
@@ -25647,10 +25647,10 @@
       </c>
     </row>
     <row r="20" spans="1:139" ht="45" x14ac:dyDescent="0.2">
-      <c r="A20" s="467">
+      <c r="A20" s="476">
         <v>2</v>
       </c>
-      <c r="B20" s="468" t="s">
+      <c r="B20" s="477" t="s">
         <v>109</v>
       </c>
       <c r="C20" s="461" t="s">
@@ -25676,9 +25676,9 @@
       <c r="K20" s="54"/>
     </row>
     <row r="21" spans="1:139" ht="45" x14ac:dyDescent="0.2">
-      <c r="A21" s="467"/>
-      <c r="B21" s="468"/>
-      <c r="C21" s="510"/>
+      <c r="A21" s="476"/>
+      <c r="B21" s="477"/>
+      <c r="C21" s="511"/>
       <c r="D21" s="73" t="s">
         <v>56</v>
       </c>
@@ -25701,9 +25701,9 @@
       <c r="K21" s="54"/>
     </row>
     <row r="22" spans="1:139" ht="75" x14ac:dyDescent="0.2">
-      <c r="A22" s="467"/>
-      <c r="B22" s="468"/>
-      <c r="C22" s="510"/>
+      <c r="A22" s="476"/>
+      <c r="B22" s="477"/>
+      <c r="C22" s="511"/>
       <c r="D22" s="73" t="s">
         <v>55</v>
       </c>
@@ -25728,9 +25728,9 @@
       </c>
     </row>
     <row r="23" spans="1:139" s="47" customFormat="1" ht="75" x14ac:dyDescent="0.2">
-      <c r="A23" s="467"/>
-      <c r="B23" s="468"/>
-      <c r="C23" s="510"/>
+      <c r="A23" s="476"/>
+      <c r="B23" s="477"/>
+      <c r="C23" s="511"/>
       <c r="D23" s="61" t="s">
         <v>114</v>
       </c>
@@ -25883,9 +25883,9 @@
       <c r="EI23" s="36"/>
     </row>
     <row r="24" spans="1:139" s="47" customFormat="1" ht="75" x14ac:dyDescent="0.2">
-      <c r="A24" s="467"/>
-      <c r="B24" s="468"/>
-      <c r="C24" s="510"/>
+      <c r="A24" s="476"/>
+      <c r="B24" s="477"/>
+      <c r="C24" s="511"/>
       <c r="D24" s="86" t="s">
         <v>92</v>
       </c>
@@ -26038,9 +26038,9 @@
       <c r="EI24" s="36"/>
     </row>
     <row r="25" spans="1:139" ht="30" x14ac:dyDescent="0.2">
-      <c r="A25" s="467"/>
-      <c r="B25" s="468"/>
-      <c r="C25" s="511"/>
+      <c r="A25" s="476"/>
+      <c r="B25" s="477"/>
+      <c r="C25" s="512"/>
       <c r="D25" s="76" t="s">
         <v>94</v>
       </c>
@@ -26063,13 +26063,13 @@
       </c>
     </row>
     <row r="26" spans="1:139" ht="90" x14ac:dyDescent="0.2">
-      <c r="A26" s="472">
+      <c r="A26" s="481">
         <v>2.1</v>
       </c>
-      <c r="B26" s="475" t="s">
+      <c r="B26" s="484" t="s">
         <v>116</v>
       </c>
-      <c r="C26" s="478" t="s">
+      <c r="C26" s="487" t="s">
         <v>117</v>
       </c>
       <c r="D26" s="76" t="s">
@@ -26092,9 +26092,9 @@
       <c r="K26" s="35"/>
     </row>
     <row r="27" spans="1:139" ht="75" x14ac:dyDescent="0.2">
-      <c r="A27" s="473"/>
-      <c r="B27" s="476"/>
-      <c r="C27" s="479"/>
+      <c r="A27" s="482"/>
+      <c r="B27" s="485"/>
+      <c r="C27" s="488"/>
       <c r="D27" s="73" t="s">
         <v>55</v>
       </c>
@@ -26117,9 +26117,9 @@
       <c r="K27" s="35"/>
     </row>
     <row r="28" spans="1:139" ht="75" x14ac:dyDescent="0.2">
-      <c r="A28" s="473"/>
-      <c r="B28" s="476"/>
-      <c r="C28" s="479"/>
+      <c r="A28" s="482"/>
+      <c r="B28" s="485"/>
+      <c r="C28" s="488"/>
       <c r="D28" s="61" t="s">
         <v>114</v>
       </c>
@@ -26142,9 +26142,9 @@
       <c r="K28" s="35"/>
     </row>
     <row r="29" spans="1:139" ht="75" x14ac:dyDescent="0.2">
-      <c r="A29" s="473"/>
-      <c r="B29" s="476"/>
-      <c r="C29" s="479"/>
+      <c r="A29" s="482"/>
+      <c r="B29" s="485"/>
+      <c r="C29" s="488"/>
       <c r="D29" s="86" t="s">
         <v>92</v>
       </c>
@@ -26167,9 +26167,9 @@
       <c r="K29" s="35"/>
     </row>
     <row r="30" spans="1:139" ht="30" x14ac:dyDescent="0.2">
-      <c r="A30" s="474"/>
-      <c r="B30" s="477"/>
-      <c r="C30" s="480"/>
+      <c r="A30" s="483"/>
+      <c r="B30" s="486"/>
+      <c r="C30" s="489"/>
       <c r="D30" s="76" t="s">
         <v>94</v>
       </c>
@@ -27382,6 +27382,12 @@
   </sheetData>
   <autoFilter ref="A4:EI31" xr:uid="{92218EDD-6442-41B5-9565-D949ECDDA5BC}"/>
   <mergeCells count="15">
+    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="A2:G2"/>
+    <mergeCell ref="I2:J2"/>
+    <mergeCell ref="A5:A13"/>
+    <mergeCell ref="B5:B13"/>
+    <mergeCell ref="C5:C13"/>
     <mergeCell ref="A26:A30"/>
     <mergeCell ref="B26:B30"/>
     <mergeCell ref="C26:C30"/>
@@ -27391,12 +27397,6 @@
     <mergeCell ref="A20:A25"/>
     <mergeCell ref="B20:B25"/>
     <mergeCell ref="C20:C25"/>
-    <mergeCell ref="A1:G1"/>
-    <mergeCell ref="A2:G2"/>
-    <mergeCell ref="I2:J2"/>
-    <mergeCell ref="A5:A13"/>
-    <mergeCell ref="B5:B13"/>
-    <mergeCell ref="C5:C13"/>
   </mergeCells>
   <dataValidations count="1">
     <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="K6:K7 K26" xr:uid="{EC1EB0C9-7584-409C-B7C9-CE8A33BC2994}"/>
@@ -27438,11 +27438,11 @@
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A4" s="4"/>
-      <c r="B4" s="452" t="s">
+      <c r="B4" s="453" t="s">
         <v>157</v>
       </c>
-      <c r="C4" s="453"/>
-      <c r="D4" s="454"/>
+      <c r="C4" s="454"/>
+      <c r="D4" s="455"/>
       <c r="E4" s="153" t="s">
         <v>158</v>
       </c>
@@ -27708,46 +27708,46 @@
       </c>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="C32" s="512" t="s">
+      <c r="C32" s="513" t="s">
         <v>125</v>
       </c>
-      <c r="D32" s="512" t="s">
+      <c r="D32" s="513" t="s">
         <v>389</v>
       </c>
-      <c r="E32" s="512" t="s">
+      <c r="E32" s="513" t="s">
         <v>205</v>
       </c>
     </row>
     <row r="33" spans="3:5" x14ac:dyDescent="0.2">
-      <c r="C33" s="513"/>
-      <c r="D33" s="513"/>
-      <c r="E33" s="513"/>
+      <c r="C33" s="514"/>
+      <c r="D33" s="514"/>
+      <c r="E33" s="514"/>
     </row>
     <row r="34" spans="3:5" x14ac:dyDescent="0.2">
-      <c r="C34" s="514"/>
-      <c r="D34" s="514"/>
-      <c r="E34" s="514"/>
+      <c r="C34" s="515"/>
+      <c r="D34" s="515"/>
+      <c r="E34" s="515"/>
     </row>
     <row r="35" spans="3:5" x14ac:dyDescent="0.2">
-      <c r="C35" s="515" t="s">
+      <c r="C35" s="516" t="s">
         <v>133</v>
       </c>
-      <c r="D35" s="515" t="s">
+      <c r="D35" s="516" t="s">
         <v>206</v>
       </c>
-      <c r="E35" s="515" t="s">
+      <c r="E35" s="516" t="s">
         <v>205</v>
       </c>
     </row>
     <row r="36" spans="3:5" x14ac:dyDescent="0.2">
-      <c r="C36" s="516"/>
-      <c r="D36" s="516"/>
-      <c r="E36" s="516"/>
+      <c r="C36" s="517"/>
+      <c r="D36" s="517"/>
+      <c r="E36" s="517"/>
     </row>
     <row r="37" spans="3:5" x14ac:dyDescent="0.2">
-      <c r="C37" s="517"/>
-      <c r="D37" s="517"/>
-      <c r="E37" s="517"/>
+      <c r="C37" s="518"/>
+      <c r="D37" s="518"/>
+      <c r="E37" s="518"/>
     </row>
     <row r="38" spans="3:5" x14ac:dyDescent="0.2">
       <c r="C38" s="124" t="s">
@@ -27848,46 +27848,46 @@
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A2" s="512" t="s">
+      <c r="A2" s="513" t="s">
         <v>125</v>
       </c>
-      <c r="B2" s="512" t="s">
+      <c r="B2" s="513" t="s">
         <v>389</v>
       </c>
-      <c r="C2" s="512" t="s">
+      <c r="C2" s="513" t="s">
         <v>205</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A3" s="513"/>
-      <c r="B3" s="513"/>
-      <c r="C3" s="513"/>
+      <c r="A3" s="514"/>
+      <c r="B3" s="514"/>
+      <c r="C3" s="514"/>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A4" s="514"/>
-      <c r="B4" s="514"/>
-      <c r="C4" s="514"/>
+      <c r="A4" s="515"/>
+      <c r="B4" s="515"/>
+      <c r="C4" s="515"/>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A5" s="515" t="s">
+      <c r="A5" s="516" t="s">
         <v>133</v>
       </c>
-      <c r="B5" s="515" t="s">
+      <c r="B5" s="516" t="s">
         <v>206</v>
       </c>
-      <c r="C5" s="515" t="s">
+      <c r="C5" s="516" t="s">
         <v>205</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A6" s="516"/>
-      <c r="B6" s="516"/>
-      <c r="C6" s="516"/>
+      <c r="A6" s="517"/>
+      <c r="B6" s="517"/>
+      <c r="C6" s="517"/>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A7" s="517"/>
-      <c r="B7" s="517"/>
-      <c r="C7" s="517"/>
+      <c r="A7" s="518"/>
+      <c r="B7" s="518"/>
+      <c r="C7" s="518"/>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A8" s="124" t="s">
@@ -27986,33 +27986,33 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:139" s="31" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="518"/>
-      <c r="B1" s="518"/>
-      <c r="C1" s="518"/>
-      <c r="D1" s="518"/>
-      <c r="E1" s="518"/>
-      <c r="F1" s="518"/>
-      <c r="G1" s="518"/>
+      <c r="A1" s="520"/>
+      <c r="B1" s="520"/>
+      <c r="C1" s="520"/>
+      <c r="D1" s="520"/>
+      <c r="E1" s="520"/>
+      <c r="F1" s="520"/>
+      <c r="G1" s="520"/>
       <c r="H1" s="104"/>
       <c r="I1" s="101"/>
       <c r="J1" s="102"/>
       <c r="K1" s="102"/>
     </row>
     <row r="2" spans="1:139" s="31" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="519" t="s">
+      <c r="A2" s="521" t="s">
         <v>429</v>
       </c>
-      <c r="B2" s="519"/>
-      <c r="C2" s="519"/>
-      <c r="D2" s="519"/>
-      <c r="E2" s="519"/>
-      <c r="F2" s="519"/>
-      <c r="G2" s="519"/>
+      <c r="B2" s="521"/>
+      <c r="C2" s="521"/>
+      <c r="D2" s="521"/>
+      <c r="E2" s="521"/>
+      <c r="F2" s="521"/>
+      <c r="G2" s="521"/>
       <c r="H2" s="105"/>
-      <c r="I2" s="413" t="s">
+      <c r="I2" s="394" t="s">
         <v>376</v>
       </c>
-      <c r="J2" s="413"/>
+      <c r="J2" s="394"/>
       <c r="K2" s="103"/>
     </row>
     <row r="3" spans="1:139" s="31" customFormat="1" ht="9.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -28061,13 +28061,13 @@
       </c>
     </row>
     <row r="5" spans="1:139" ht="72.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="481">
+      <c r="A5" s="468">
         <v>1</v>
       </c>
-      <c r="B5" s="416" t="s">
+      <c r="B5" s="397" t="s">
         <v>394</v>
       </c>
-      <c r="C5" s="500" t="s">
+      <c r="C5" s="501" t="s">
         <v>377</v>
       </c>
       <c r="D5" s="73" t="s">
@@ -28092,8 +28092,8 @@
       </c>
     </row>
     <row r="6" spans="1:139" ht="72.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="482"/>
-      <c r="B6" s="417"/>
+      <c r="A6" s="469"/>
+      <c r="B6" s="398"/>
       <c r="C6" s="464"/>
       <c r="D6" s="73" t="s">
         <v>56</v>
@@ -28115,8 +28115,8 @@
       <c r="K6" s="35"/>
     </row>
     <row r="7" spans="1:139" ht="60" x14ac:dyDescent="0.2">
-      <c r="A7" s="482"/>
-      <c r="B7" s="417"/>
+      <c r="A7" s="469"/>
+      <c r="B7" s="398"/>
       <c r="C7" s="464"/>
       <c r="D7" s="73" t="s">
         <v>55</v>
@@ -28138,8 +28138,8 @@
       <c r="K7" s="35"/>
     </row>
     <row r="8" spans="1:139" ht="210" x14ac:dyDescent="0.2">
-      <c r="A8" s="482"/>
-      <c r="B8" s="417"/>
+      <c r="A8" s="469"/>
+      <c r="B8" s="398"/>
       <c r="C8" s="464"/>
       <c r="D8" s="73" t="s">
         <v>63</v>
@@ -28162,8 +28162,8 @@
       <c r="L8" s="38"/>
     </row>
     <row r="9" spans="1:139" ht="150" x14ac:dyDescent="0.2">
-      <c r="A9" s="482"/>
-      <c r="B9" s="417"/>
+      <c r="A9" s="469"/>
+      <c r="B9" s="398"/>
       <c r="C9" s="464"/>
       <c r="D9" s="73" t="s">
         <v>68</v>
@@ -28185,8 +28185,8 @@
       <c r="K9" s="35"/>
     </row>
     <row r="10" spans="1:139" ht="60" x14ac:dyDescent="0.2">
-      <c r="A10" s="482"/>
-      <c r="B10" s="417"/>
+      <c r="A10" s="469"/>
+      <c r="B10" s="398"/>
       <c r="C10" s="464"/>
       <c r="D10" s="73" t="s">
         <v>72</v>
@@ -28208,8 +28208,8 @@
       <c r="K10" s="35"/>
     </row>
     <row r="11" spans="1:139" ht="409.6" x14ac:dyDescent="0.2">
-      <c r="A11" s="482"/>
-      <c r="B11" s="417"/>
+      <c r="A11" s="469"/>
+      <c r="B11" s="398"/>
       <c r="C11" s="464"/>
       <c r="D11" s="73" t="s">
         <v>86</v>
@@ -28235,8 +28235,8 @@
       </c>
     </row>
     <row r="12" spans="1:139" s="42" customFormat="1" ht="347.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A12" s="482"/>
-      <c r="B12" s="417"/>
+      <c r="A12" s="469"/>
+      <c r="B12" s="398"/>
       <c r="C12" s="464"/>
       <c r="D12" s="73" t="s">
         <v>92</v>
@@ -28390,8 +28390,8 @@
       <c r="EI12" s="41"/>
     </row>
     <row r="13" spans="1:139" ht="45" x14ac:dyDescent="0.2">
-      <c r="A13" s="482"/>
-      <c r="B13" s="417"/>
+      <c r="A13" s="469"/>
+      <c r="B13" s="398"/>
       <c r="C13" s="464"/>
       <c r="D13" s="73" t="s">
         <v>277</v>
@@ -28415,13 +28415,13 @@
       </c>
     </row>
     <row r="14" spans="1:139" ht="45" x14ac:dyDescent="0.2">
-      <c r="A14" s="486">
+      <c r="A14" s="473">
         <v>1.1000000000000001</v>
       </c>
-      <c r="B14" s="487" t="s">
+      <c r="B14" s="474" t="s">
         <v>98</v>
       </c>
-      <c r="C14" s="500" t="s">
+      <c r="C14" s="501" t="s">
         <v>378</v>
       </c>
       <c r="D14" s="73" t="s">
@@ -28446,9 +28446,9 @@
       </c>
     </row>
     <row r="15" spans="1:139" ht="40.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A15" s="486"/>
-      <c r="B15" s="487"/>
-      <c r="C15" s="521"/>
+      <c r="A15" s="473"/>
+      <c r="B15" s="474"/>
+      <c r="C15" s="522"/>
       <c r="D15" s="73" t="s">
         <v>56</v>
       </c>
@@ -28471,9 +28471,9 @@
       <c r="K15" s="35"/>
     </row>
     <row r="16" spans="1:139" ht="140.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A16" s="486"/>
-      <c r="B16" s="487"/>
-      <c r="C16" s="521"/>
+      <c r="A16" s="473"/>
+      <c r="B16" s="474"/>
+      <c r="C16" s="522"/>
       <c r="D16" s="73" t="s">
         <v>55</v>
       </c>
@@ -28499,9 +28499,9 @@
       <c r="L16" s="38"/>
     </row>
     <row r="17" spans="1:139" s="47" customFormat="1" ht="126" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A17" s="486"/>
-      <c r="B17" s="487"/>
-      <c r="C17" s="521"/>
+      <c r="A17" s="473"/>
+      <c r="B17" s="474"/>
+      <c r="C17" s="522"/>
       <c r="D17" s="76" t="s">
         <v>106</v>
       </c>
@@ -28654,9 +28654,9 @@
       <c r="EI17" s="36"/>
     </row>
     <row r="18" spans="1:139" s="47" customFormat="1" ht="129.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A18" s="486"/>
-      <c r="B18" s="487"/>
-      <c r="C18" s="521"/>
+      <c r="A18" s="473"/>
+      <c r="B18" s="474"/>
+      <c r="C18" s="522"/>
       <c r="D18" s="76" t="s">
         <v>92</v>
       </c>
@@ -28807,9 +28807,9 @@
       <c r="EI18" s="36"/>
     </row>
     <row r="19" spans="1:139" ht="45" x14ac:dyDescent="0.2">
-      <c r="A19" s="481"/>
-      <c r="B19" s="488"/>
-      <c r="C19" s="521"/>
+      <c r="A19" s="468"/>
+      <c r="B19" s="475"/>
+      <c r="C19" s="522"/>
       <c r="D19" s="78" t="s">
         <v>277</v>
       </c>
@@ -28832,10 +28832,10 @@
       </c>
     </row>
     <row r="20" spans="1:139" ht="45" x14ac:dyDescent="0.2">
-      <c r="A20" s="467">
+      <c r="A20" s="476">
         <v>2</v>
       </c>
-      <c r="B20" s="468" t="s">
+      <c r="B20" s="477" t="s">
         <v>109</v>
       </c>
       <c r="C20" s="461" t="s">
@@ -28861,9 +28861,9 @@
       <c r="K20" s="54"/>
     </row>
     <row r="21" spans="1:139" ht="45" x14ac:dyDescent="0.2">
-      <c r="A21" s="467"/>
-      <c r="B21" s="468"/>
-      <c r="C21" s="510"/>
+      <c r="A21" s="476"/>
+      <c r="B21" s="477"/>
+      <c r="C21" s="511"/>
       <c r="D21" s="73" t="s">
         <v>56</v>
       </c>
@@ -28886,9 +28886,9 @@
       <c r="K21" s="54"/>
     </row>
     <row r="22" spans="1:139" ht="75" x14ac:dyDescent="0.2">
-      <c r="A22" s="467"/>
-      <c r="B22" s="468"/>
-      <c r="C22" s="510"/>
+      <c r="A22" s="476"/>
+      <c r="B22" s="477"/>
+      <c r="C22" s="511"/>
       <c r="D22" s="73" t="s">
         <v>55</v>
       </c>
@@ -28913,9 +28913,9 @@
       </c>
     </row>
     <row r="23" spans="1:139" s="47" customFormat="1" ht="75" x14ac:dyDescent="0.2">
-      <c r="A23" s="467"/>
-      <c r="B23" s="468"/>
-      <c r="C23" s="510"/>
+      <c r="A23" s="476"/>
+      <c r="B23" s="477"/>
+      <c r="C23" s="511"/>
       <c r="D23" s="61" t="s">
         <v>114</v>
       </c>
@@ -29068,9 +29068,9 @@
       <c r="EI23" s="36"/>
     </row>
     <row r="24" spans="1:139" s="47" customFormat="1" ht="75" x14ac:dyDescent="0.2">
-      <c r="A24" s="467"/>
-      <c r="B24" s="468"/>
-      <c r="C24" s="510"/>
+      <c r="A24" s="476"/>
+      <c r="B24" s="477"/>
+      <c r="C24" s="511"/>
       <c r="D24" s="86" t="s">
         <v>92</v>
       </c>
@@ -29223,9 +29223,9 @@
       <c r="EI24" s="36"/>
     </row>
     <row r="25" spans="1:139" ht="30" x14ac:dyDescent="0.2">
-      <c r="A25" s="467"/>
-      <c r="B25" s="468"/>
-      <c r="C25" s="511"/>
+      <c r="A25" s="476"/>
+      <c r="B25" s="477"/>
+      <c r="C25" s="512"/>
       <c r="D25" s="76" t="s">
         <v>94</v>
       </c>
@@ -29248,13 +29248,13 @@
       </c>
     </row>
     <row r="26" spans="1:139" ht="90" x14ac:dyDescent="0.2">
-      <c r="A26" s="472">
+      <c r="A26" s="481">
         <v>2.1</v>
       </c>
-      <c r="B26" s="475" t="s">
+      <c r="B26" s="484" t="s">
         <v>116</v>
       </c>
-      <c r="C26" s="478" t="s">
+      <c r="C26" s="487" t="s">
         <v>117</v>
       </c>
       <c r="D26" s="76" t="s">
@@ -29277,9 +29277,9 @@
       <c r="K26" s="35"/>
     </row>
     <row r="27" spans="1:139" ht="75" x14ac:dyDescent="0.2">
-      <c r="A27" s="473"/>
-      <c r="B27" s="476"/>
-      <c r="C27" s="479"/>
+      <c r="A27" s="482"/>
+      <c r="B27" s="485"/>
+      <c r="C27" s="488"/>
       <c r="D27" s="73" t="s">
         <v>55</v>
       </c>
@@ -29302,9 +29302,9 @@
       <c r="K27" s="35"/>
     </row>
     <row r="28" spans="1:139" ht="75" x14ac:dyDescent="0.2">
-      <c r="A28" s="473"/>
-      <c r="B28" s="476"/>
-      <c r="C28" s="479"/>
+      <c r="A28" s="482"/>
+      <c r="B28" s="485"/>
+      <c r="C28" s="488"/>
       <c r="D28" s="61" t="s">
         <v>114</v>
       </c>
@@ -29327,9 +29327,9 @@
       <c r="K28" s="35"/>
     </row>
     <row r="29" spans="1:139" ht="75" x14ac:dyDescent="0.2">
-      <c r="A29" s="473"/>
-      <c r="B29" s="476"/>
-      <c r="C29" s="479"/>
+      <c r="A29" s="482"/>
+      <c r="B29" s="485"/>
+      <c r="C29" s="488"/>
       <c r="D29" s="86" t="s">
         <v>92</v>
       </c>
@@ -29352,9 +29352,9 @@
       <c r="K29" s="35"/>
     </row>
     <row r="30" spans="1:139" ht="30" x14ac:dyDescent="0.2">
-      <c r="A30" s="474"/>
-      <c r="B30" s="477"/>
-      <c r="C30" s="480"/>
+      <c r="A30" s="483"/>
+      <c r="B30" s="486"/>
+      <c r="C30" s="489"/>
       <c r="D30" s="76" t="s">
         <v>94</v>
       </c>
@@ -30567,6 +30567,12 @@
   </sheetData>
   <autoFilter ref="A4:EI31" xr:uid="{92218EDD-6442-41B5-9565-D949ECDDA5BC}"/>
   <mergeCells count="15">
+    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="A2:G2"/>
+    <mergeCell ref="I2:J2"/>
+    <mergeCell ref="A5:A13"/>
+    <mergeCell ref="B5:B13"/>
+    <mergeCell ref="C5:C13"/>
     <mergeCell ref="A26:A30"/>
     <mergeCell ref="B26:B30"/>
     <mergeCell ref="C26:C30"/>
@@ -30576,12 +30582,6 @@
     <mergeCell ref="A20:A25"/>
     <mergeCell ref="B20:B25"/>
     <mergeCell ref="C20:C25"/>
-    <mergeCell ref="A1:G1"/>
-    <mergeCell ref="A2:G2"/>
-    <mergeCell ref="I2:J2"/>
-    <mergeCell ref="A5:A13"/>
-    <mergeCell ref="B5:B13"/>
-    <mergeCell ref="C5:C13"/>
   </mergeCells>
   <dataValidations count="1">
     <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="K6:K7 K26" xr:uid="{F4C3080E-55C9-4ABE-B0CD-E6276EC6EDFB}"/>
@@ -30773,7 +30773,8 @@
     <col min="3" max="4" width="34.1640625" style="61" customWidth="1"/>
     <col min="5" max="5" width="27.83203125" style="61" customWidth="1"/>
     <col min="6" max="6" width="23" style="55" customWidth="1"/>
-    <col min="7" max="16384" width="8.83203125" style="36"/>
+    <col min="7" max="7" width="8.83203125" style="36" customWidth="1"/>
+    <col min="8" max="16384" width="8.83203125" style="36"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:129" s="29" customFormat="1" ht="50" customHeight="1" x14ac:dyDescent="0.2">
@@ -31936,7 +31937,7 @@
       <c r="E9" s="264" t="s">
         <v>496</v>
       </c>
-      <c r="F9" s="537" t="s">
+      <c r="F9" s="393" t="s">
         <v>511</v>
       </c>
       <c r="G9" s="381"/>
@@ -33652,7 +33653,7 @@
       <c r="E21" s="264" t="s">
         <v>496</v>
       </c>
-      <c r="F21" s="537" t="s">
+      <c r="F21" s="393" t="s">
         <v>511</v>
       </c>
       <c r="G21" s="381"/>
@@ -35225,7 +35226,7 @@
       <c r="E32" s="264" t="s">
         <v>496</v>
       </c>
-      <c r="F32" s="537" t="s">
+      <c r="F32" s="393" t="s">
         <v>511</v>
       </c>
       <c r="G32" s="381"/>
@@ -40370,27 +40371,27 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:138" s="31" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="518"/>
-      <c r="B1" s="518"/>
-      <c r="C1" s="518"/>
-      <c r="D1" s="518"/>
-      <c r="E1" s="518"/>
-      <c r="F1" s="518"/>
-      <c r="G1" s="518"/>
+      <c r="A1" s="520"/>
+      <c r="B1" s="520"/>
+      <c r="C1" s="520"/>
+      <c r="D1" s="520"/>
+      <c r="E1" s="520"/>
+      <c r="F1" s="520"/>
+      <c r="G1" s="520"/>
       <c r="H1" s="24"/>
       <c r="I1" s="25"/>
       <c r="J1" s="25"/>
     </row>
     <row r="2" spans="1:138" s="31" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="519" t="s">
+      <c r="A2" s="521" t="s">
         <v>434</v>
       </c>
-      <c r="B2" s="519"/>
-      <c r="C2" s="519"/>
-      <c r="D2" s="519"/>
-      <c r="E2" s="519"/>
-      <c r="F2" s="519"/>
-      <c r="G2" s="519"/>
+      <c r="B2" s="521"/>
+      <c r="C2" s="521"/>
+      <c r="D2" s="521"/>
+      <c r="E2" s="521"/>
+      <c r="F2" s="521"/>
+      <c r="G2" s="521"/>
       <c r="H2" s="24"/>
       <c r="I2" s="25"/>
       <c r="J2" s="25"/>
@@ -40439,13 +40440,13 @@
       </c>
     </row>
     <row r="5" spans="1:138" ht="72.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="481">
+      <c r="A5" s="468">
         <v>1</v>
       </c>
-      <c r="B5" s="416" t="s">
+      <c r="B5" s="397" t="s">
         <v>394</v>
       </c>
-      <c r="C5" s="421" t="s">
+      <c r="C5" s="404" t="s">
         <v>435</v>
       </c>
       <c r="D5" s="73" t="s">
@@ -40469,9 +40470,9 @@
       </c>
     </row>
     <row r="6" spans="1:138" ht="72.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="482"/>
-      <c r="B6" s="417"/>
-      <c r="C6" s="422"/>
+      <c r="A6" s="469"/>
+      <c r="B6" s="398"/>
+      <c r="C6" s="405"/>
       <c r="D6" s="73" t="s">
         <v>56</v>
       </c>
@@ -40491,9 +40492,9 @@
       <c r="J6" s="35"/>
     </row>
     <row r="7" spans="1:138" ht="60" x14ac:dyDescent="0.2">
-      <c r="A7" s="482"/>
-      <c r="B7" s="417"/>
-      <c r="C7" s="422"/>
+      <c r="A7" s="469"/>
+      <c r="B7" s="398"/>
+      <c r="C7" s="405"/>
       <c r="D7" s="73" t="s">
         <v>55</v>
       </c>
@@ -40513,9 +40514,9 @@
       <c r="J7" s="35"/>
     </row>
     <row r="8" spans="1:138" ht="210" x14ac:dyDescent="0.2">
-      <c r="A8" s="482"/>
-      <c r="B8" s="417"/>
-      <c r="C8" s="422"/>
+      <c r="A8" s="469"/>
+      <c r="B8" s="398"/>
+      <c r="C8" s="405"/>
       <c r="D8" s="73" t="s">
         <v>63</v>
       </c>
@@ -40536,9 +40537,9 @@
       <c r="K8" s="38"/>
     </row>
     <row r="9" spans="1:138" ht="150" x14ac:dyDescent="0.2">
-      <c r="A9" s="482"/>
-      <c r="B9" s="417"/>
-      <c r="C9" s="422"/>
+      <c r="A9" s="469"/>
+      <c r="B9" s="398"/>
+      <c r="C9" s="405"/>
       <c r="D9" s="73" t="s">
         <v>68</v>
       </c>
@@ -40558,9 +40559,9 @@
       <c r="J9" s="35"/>
     </row>
     <row r="10" spans="1:138" ht="60" x14ac:dyDescent="0.2">
-      <c r="A10" s="482"/>
-      <c r="B10" s="417"/>
-      <c r="C10" s="422"/>
+      <c r="A10" s="469"/>
+      <c r="B10" s="398"/>
+      <c r="C10" s="405"/>
       <c r="D10" s="73" t="s">
         <v>72</v>
       </c>
@@ -40580,9 +40581,9 @@
       <c r="J10" s="35"/>
     </row>
     <row r="11" spans="1:138" ht="409.6" x14ac:dyDescent="0.2">
-      <c r="A11" s="482"/>
-      <c r="B11" s="417"/>
-      <c r="C11" s="422"/>
+      <c r="A11" s="469"/>
+      <c r="B11" s="398"/>
+      <c r="C11" s="405"/>
       <c r="D11" s="73" t="s">
         <v>86</v>
       </c>
@@ -40606,9 +40607,9 @@
       </c>
     </row>
     <row r="12" spans="1:138" s="42" customFormat="1" ht="347.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A12" s="482"/>
-      <c r="B12" s="417"/>
-      <c r="C12" s="422"/>
+      <c r="A12" s="469"/>
+      <c r="B12" s="398"/>
+      <c r="C12" s="405"/>
       <c r="D12" s="73" t="s">
         <v>92</v>
       </c>
@@ -40758,9 +40759,9 @@
       <c r="EH12" s="41"/>
     </row>
     <row r="13" spans="1:138" ht="409.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A13" s="482"/>
-      <c r="B13" s="417"/>
-      <c r="C13" s="422"/>
+      <c r="A13" s="469"/>
+      <c r="B13" s="398"/>
+      <c r="C13" s="405"/>
       <c r="D13" s="73" t="s">
         <v>277</v>
       </c>
@@ -40780,13 +40781,13 @@
       </c>
     </row>
     <row r="14" spans="1:138" ht="45" x14ac:dyDescent="0.2">
-      <c r="A14" s="486">
+      <c r="A14" s="473">
         <v>1.1000000000000001</v>
       </c>
-      <c r="B14" s="487" t="s">
+      <c r="B14" s="474" t="s">
         <v>98</v>
       </c>
-      <c r="C14" s="421" t="s">
+      <c r="C14" s="404" t="s">
         <v>436</v>
       </c>
       <c r="D14" s="73" t="s">
@@ -40810,9 +40811,9 @@
       </c>
     </row>
     <row r="15" spans="1:138" ht="40.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A15" s="486"/>
-      <c r="B15" s="487"/>
-      <c r="C15" s="520"/>
+      <c r="A15" s="473"/>
+      <c r="B15" s="474"/>
+      <c r="C15" s="519"/>
       <c r="D15" s="73" t="s">
         <v>56</v>
       </c>
@@ -40834,9 +40835,9 @@
       <c r="J15" s="35"/>
     </row>
     <row r="16" spans="1:138" ht="140.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A16" s="486"/>
-      <c r="B16" s="487"/>
-      <c r="C16" s="520"/>
+      <c r="A16" s="473"/>
+      <c r="B16" s="474"/>
+      <c r="C16" s="519"/>
       <c r="D16" s="73" t="s">
         <v>55</v>
       </c>
@@ -40861,9 +40862,9 @@
       <c r="K16" s="38"/>
     </row>
     <row r="17" spans="1:138" s="47" customFormat="1" ht="126" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A17" s="486"/>
-      <c r="B17" s="487"/>
-      <c r="C17" s="520"/>
+      <c r="A17" s="473"/>
+      <c r="B17" s="474"/>
+      <c r="C17" s="519"/>
       <c r="D17" s="76" t="s">
         <v>106</v>
       </c>
@@ -41015,9 +41016,9 @@
       <c r="EH17" s="36"/>
     </row>
     <row r="18" spans="1:138" s="47" customFormat="1" ht="129.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A18" s="486"/>
-      <c r="B18" s="487"/>
-      <c r="C18" s="520"/>
+      <c r="A18" s="473"/>
+      <c r="B18" s="474"/>
+      <c r="C18" s="519"/>
       <c r="D18" s="76" t="s">
         <v>92</v>
       </c>
@@ -41165,9 +41166,9 @@
       <c r="EH18" s="36"/>
     </row>
     <row r="19" spans="1:138" ht="45" x14ac:dyDescent="0.2">
-      <c r="A19" s="481"/>
-      <c r="B19" s="488"/>
-      <c r="C19" s="520"/>
+      <c r="A19" s="468"/>
+      <c r="B19" s="475"/>
+      <c r="C19" s="519"/>
       <c r="D19" s="78" t="s">
         <v>277</v>
       </c>
@@ -41187,10 +41188,10 @@
       </c>
     </row>
     <row r="20" spans="1:138" ht="45" x14ac:dyDescent="0.2">
-      <c r="A20" s="467">
+      <c r="A20" s="476">
         <v>2</v>
       </c>
-      <c r="B20" s="468" t="s">
+      <c r="B20" s="477" t="s">
         <v>437</v>
       </c>
       <c r="C20" s="461" t="s">
@@ -41215,9 +41216,9 @@
       <c r="J20" s="54"/>
     </row>
     <row r="21" spans="1:138" ht="45" x14ac:dyDescent="0.2">
-      <c r="A21" s="467"/>
-      <c r="B21" s="468"/>
-      <c r="C21" s="510"/>
+      <c r="A21" s="476"/>
+      <c r="B21" s="477"/>
+      <c r="C21" s="511"/>
       <c r="D21" s="73" t="s">
         <v>56</v>
       </c>
@@ -41239,9 +41240,9 @@
       <c r="J21" s="54"/>
     </row>
     <row r="22" spans="1:138" ht="165" x14ac:dyDescent="0.2">
-      <c r="A22" s="467"/>
-      <c r="B22" s="468"/>
-      <c r="C22" s="510"/>
+      <c r="A22" s="476"/>
+      <c r="B22" s="477"/>
+      <c r="C22" s="511"/>
       <c r="D22" s="73" t="s">
         <v>55</v>
       </c>
@@ -41265,9 +41266,9 @@
       </c>
     </row>
     <row r="23" spans="1:138" s="47" customFormat="1" ht="165" x14ac:dyDescent="0.2">
-      <c r="A23" s="467"/>
-      <c r="B23" s="468"/>
-      <c r="C23" s="510"/>
+      <c r="A23" s="476"/>
+      <c r="B23" s="477"/>
+      <c r="C23" s="511"/>
       <c r="D23" s="61" t="s">
         <v>114</v>
       </c>
@@ -41419,9 +41420,9 @@
       <c r="EH23" s="36"/>
     </row>
     <row r="24" spans="1:138" s="47" customFormat="1" ht="165" x14ac:dyDescent="0.2">
-      <c r="A24" s="467"/>
-      <c r="B24" s="468"/>
-      <c r="C24" s="510"/>
+      <c r="A24" s="476"/>
+      <c r="B24" s="477"/>
+      <c r="C24" s="511"/>
       <c r="D24" s="86" t="s">
         <v>92</v>
       </c>
@@ -41571,9 +41572,9 @@
       <c r="EH24" s="36"/>
     </row>
     <row r="25" spans="1:138" ht="30" x14ac:dyDescent="0.2">
-      <c r="A25" s="467"/>
-      <c r="B25" s="468"/>
-      <c r="C25" s="511"/>
+      <c r="A25" s="476"/>
+      <c r="B25" s="477"/>
+      <c r="C25" s="512"/>
       <c r="D25" s="76" t="s">
         <v>94</v>
       </c>
@@ -41593,13 +41594,13 @@
       </c>
     </row>
     <row r="26" spans="1:138" ht="90" x14ac:dyDescent="0.2">
-      <c r="A26" s="507">
+      <c r="A26" s="508">
         <v>2.1</v>
       </c>
-      <c r="B26" s="504" t="s">
+      <c r="B26" s="505" t="s">
         <v>116</v>
       </c>
-      <c r="C26" s="501" t="s">
+      <c r="C26" s="502" t="s">
         <v>117</v>
       </c>
       <c r="D26" s="83" t="s">
@@ -41621,9 +41622,9 @@
       <c r="J26" s="82"/>
     </row>
     <row r="27" spans="1:138" ht="165" x14ac:dyDescent="0.2">
-      <c r="A27" s="508"/>
-      <c r="B27" s="505"/>
-      <c r="C27" s="502"/>
+      <c r="A27" s="509"/>
+      <c r="B27" s="506"/>
+      <c r="C27" s="503"/>
       <c r="D27" s="37" t="s">
         <v>55</v>
       </c>
@@ -41647,9 +41648,9 @@
       </c>
     </row>
     <row r="28" spans="1:138" ht="165" x14ac:dyDescent="0.2">
-      <c r="A28" s="508"/>
-      <c r="B28" s="505"/>
-      <c r="C28" s="502"/>
+      <c r="A28" s="509"/>
+      <c r="B28" s="506"/>
+      <c r="C28" s="503"/>
       <c r="D28" s="80" t="s">
         <v>114</v>
       </c>
@@ -41673,9 +41674,9 @@
       </c>
     </row>
     <row r="29" spans="1:138" ht="165" x14ac:dyDescent="0.2">
-      <c r="A29" s="508"/>
-      <c r="B29" s="505"/>
-      <c r="C29" s="502"/>
+      <c r="A29" s="509"/>
+      <c r="B29" s="506"/>
+      <c r="C29" s="503"/>
       <c r="D29" s="91" t="s">
         <v>92</v>
       </c>
@@ -41697,9 +41698,9 @@
       </c>
     </row>
     <row r="30" spans="1:138" ht="30" x14ac:dyDescent="0.2">
-      <c r="A30" s="509"/>
-      <c r="B30" s="506"/>
-      <c r="C30" s="503"/>
+      <c r="A30" s="510"/>
+      <c r="B30" s="507"/>
+      <c r="C30" s="504"/>
       <c r="D30" s="83" t="s">
         <v>94</v>
       </c>
@@ -43078,26 +43079,26 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:138" s="31" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="518"/>
-      <c r="B1" s="518"/>
-      <c r="C1" s="518"/>
-      <c r="D1" s="518"/>
-      <c r="E1" s="518"/>
-      <c r="F1" s="518"/>
+      <c r="A1" s="520"/>
+      <c r="B1" s="520"/>
+      <c r="C1" s="520"/>
+      <c r="D1" s="520"/>
+      <c r="E1" s="520"/>
+      <c r="F1" s="520"/>
       <c r="G1" s="23"/>
       <c r="H1" s="24"/>
       <c r="I1" s="25"/>
       <c r="J1" s="25"/>
     </row>
     <row r="2" spans="1:138" s="31" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="518" t="s">
+      <c r="A2" s="520" t="s">
         <v>20</v>
       </c>
-      <c r="B2" s="518"/>
-      <c r="C2" s="518"/>
-      <c r="D2" s="518"/>
-      <c r="E2" s="518"/>
-      <c r="F2" s="518"/>
+      <c r="B2" s="520"/>
+      <c r="C2" s="520"/>
+      <c r="D2" s="520"/>
+      <c r="E2" s="520"/>
+      <c r="F2" s="520"/>
       <c r="G2" s="23"/>
       <c r="H2" s="24"/>
       <c r="I2" s="25"/>
@@ -43147,13 +43148,13 @@
       </c>
     </row>
     <row r="5" spans="1:138" ht="72.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="481">
+      <c r="A5" s="468">
         <v>1</v>
       </c>
-      <c r="B5" s="531" t="s">
+      <c r="B5" s="525" t="s">
         <v>394</v>
       </c>
-      <c r="C5" s="529" t="s">
+      <c r="C5" s="527" t="s">
         <v>435</v>
       </c>
       <c r="D5" s="32" t="s">
@@ -43175,9 +43176,9 @@
       <c r="J5" s="35"/>
     </row>
     <row r="6" spans="1:138" ht="72.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="482"/>
-      <c r="B6" s="532"/>
-      <c r="C6" s="533"/>
+      <c r="A6" s="469"/>
+      <c r="B6" s="526"/>
+      <c r="C6" s="528"/>
       <c r="D6" s="32" t="s">
         <v>56</v>
       </c>
@@ -43197,9 +43198,9 @@
       <c r="J6" s="35"/>
     </row>
     <row r="7" spans="1:138" ht="45" x14ac:dyDescent="0.2">
-      <c r="A7" s="482"/>
-      <c r="B7" s="532"/>
-      <c r="C7" s="533"/>
+      <c r="A7" s="469"/>
+      <c r="B7" s="526"/>
+      <c r="C7" s="528"/>
       <c r="D7" s="32" t="s">
         <v>55</v>
       </c>
@@ -43219,9 +43220,9 @@
       <c r="J7" s="35"/>
     </row>
     <row r="8" spans="1:138" ht="120" x14ac:dyDescent="0.2">
-      <c r="A8" s="482"/>
-      <c r="B8" s="532"/>
-      <c r="C8" s="533"/>
+      <c r="A8" s="469"/>
+      <c r="B8" s="526"/>
+      <c r="C8" s="528"/>
       <c r="D8" s="32" t="s">
         <v>63</v>
       </c>
@@ -43242,9 +43243,9 @@
       <c r="K8" s="38"/>
     </row>
     <row r="9" spans="1:138" ht="105" x14ac:dyDescent="0.2">
-      <c r="A9" s="482"/>
-      <c r="B9" s="532"/>
-      <c r="C9" s="533"/>
+      <c r="A9" s="469"/>
+      <c r="B9" s="526"/>
+      <c r="C9" s="528"/>
       <c r="D9" s="32" t="s">
         <v>68</v>
       </c>
@@ -43264,9 +43265,9 @@
       <c r="J9" s="35"/>
     </row>
     <row r="10" spans="1:138" ht="45" x14ac:dyDescent="0.2">
-      <c r="A10" s="482"/>
-      <c r="B10" s="532"/>
-      <c r="C10" s="533"/>
+      <c r="A10" s="469"/>
+      <c r="B10" s="526"/>
+      <c r="C10" s="528"/>
       <c r="D10" s="32" t="s">
         <v>72</v>
       </c>
@@ -43286,9 +43287,9 @@
       <c r="J10" s="35"/>
     </row>
     <row r="11" spans="1:138" ht="409.6" x14ac:dyDescent="0.2">
-      <c r="A11" s="482"/>
-      <c r="B11" s="532"/>
-      <c r="C11" s="533"/>
+      <c r="A11" s="469"/>
+      <c r="B11" s="526"/>
+      <c r="C11" s="528"/>
       <c r="D11" s="32" t="s">
         <v>86</v>
       </c>
@@ -43312,9 +43313,9 @@
       </c>
     </row>
     <row r="12" spans="1:138" s="42" customFormat="1" ht="347.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A12" s="482"/>
-      <c r="B12" s="532"/>
-      <c r="C12" s="533"/>
+      <c r="A12" s="469"/>
+      <c r="B12" s="526"/>
+      <c r="C12" s="528"/>
       <c r="D12" s="32" t="s">
         <v>92</v>
       </c>
@@ -43464,9 +43465,9 @@
       <c r="EH12" s="41"/>
     </row>
     <row r="13" spans="1:138" ht="409.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A13" s="482"/>
-      <c r="B13" s="532"/>
-      <c r="C13" s="533"/>
+      <c r="A13" s="469"/>
+      <c r="B13" s="526"/>
+      <c r="C13" s="528"/>
       <c r="D13" s="32" t="s">
         <v>277</v>
       </c>
@@ -43486,13 +43487,13 @@
       </c>
     </row>
     <row r="14" spans="1:138" ht="60" x14ac:dyDescent="0.2">
-      <c r="A14" s="486">
+      <c r="A14" s="473">
         <v>1.1000000000000001</v>
       </c>
-      <c r="B14" s="527" t="s">
+      <c r="B14" s="532" t="s">
         <v>98</v>
       </c>
-      <c r="C14" s="529" t="s">
+      <c r="C14" s="527" t="s">
         <v>436</v>
       </c>
       <c r="D14" s="32" t="s">
@@ -43516,9 +43517,9 @@
       <c r="J14" s="44"/>
     </row>
     <row r="15" spans="1:138" ht="40.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A15" s="486"/>
-      <c r="B15" s="527"/>
-      <c r="C15" s="530"/>
+      <c r="A15" s="473"/>
+      <c r="B15" s="532"/>
+      <c r="C15" s="534"/>
       <c r="D15" s="32" t="s">
         <v>56</v>
       </c>
@@ -43540,9 +43541,9 @@
       <c r="J15" s="35"/>
     </row>
     <row r="16" spans="1:138" ht="140.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A16" s="486"/>
-      <c r="B16" s="527"/>
-      <c r="C16" s="530"/>
+      <c r="A16" s="473"/>
+      <c r="B16" s="532"/>
+      <c r="C16" s="534"/>
       <c r="D16" s="32" t="s">
         <v>55</v>
       </c>
@@ -43567,9 +43568,9 @@
       <c r="K16" s="38"/>
     </row>
     <row r="17" spans="1:138" s="47" customFormat="1" ht="126" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A17" s="486"/>
-      <c r="B17" s="527"/>
-      <c r="C17" s="530"/>
+      <c r="A17" s="473"/>
+      <c r="B17" s="532"/>
+      <c r="C17" s="534"/>
       <c r="D17" s="46" t="s">
         <v>106</v>
       </c>
@@ -43721,9 +43722,9 @@
       <c r="EH17" s="36"/>
     </row>
     <row r="18" spans="1:138" s="47" customFormat="1" ht="129.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A18" s="486"/>
-      <c r="B18" s="527"/>
-      <c r="C18" s="530"/>
+      <c r="A18" s="473"/>
+      <c r="B18" s="532"/>
+      <c r="C18" s="534"/>
       <c r="D18" s="46" t="s">
         <v>92</v>
       </c>
@@ -43871,9 +43872,9 @@
       <c r="EH18" s="36"/>
     </row>
     <row r="19" spans="1:138" ht="45" x14ac:dyDescent="0.2">
-      <c r="A19" s="481"/>
-      <c r="B19" s="528"/>
-      <c r="C19" s="530"/>
+      <c r="A19" s="468"/>
+      <c r="B19" s="533"/>
+      <c r="C19" s="534"/>
       <c r="D19" s="49" t="s">
         <v>277</v>
       </c>
@@ -43893,13 +43894,13 @@
       </c>
     </row>
     <row r="20" spans="1:138" ht="45" x14ac:dyDescent="0.2">
-      <c r="A20" s="467">
+      <c r="A20" s="476">
         <v>2</v>
       </c>
-      <c r="B20" s="524" t="s">
+      <c r="B20" s="529" t="s">
         <v>437</v>
       </c>
-      <c r="C20" s="525" t="s">
+      <c r="C20" s="530" t="s">
         <v>438</v>
       </c>
       <c r="D20" s="32" t="s">
@@ -43921,9 +43922,9 @@
       <c r="J20" s="54"/>
     </row>
     <row r="21" spans="1:138" ht="30" x14ac:dyDescent="0.2">
-      <c r="A21" s="467"/>
-      <c r="B21" s="524"/>
-      <c r="C21" s="526"/>
+      <c r="A21" s="476"/>
+      <c r="B21" s="529"/>
+      <c r="C21" s="531"/>
       <c r="D21" s="32" t="s">
         <v>56</v>
       </c>
@@ -43945,9 +43946,9 @@
       <c r="J21" s="54"/>
     </row>
     <row r="22" spans="1:138" ht="210" x14ac:dyDescent="0.2">
-      <c r="A22" s="467"/>
-      <c r="B22" s="524"/>
-      <c r="C22" s="526"/>
+      <c r="A22" s="476"/>
+      <c r="B22" s="529"/>
+      <c r="C22" s="531"/>
       <c r="D22" s="32" t="s">
         <v>55</v>
       </c>
@@ -43971,9 +43972,9 @@
       </c>
     </row>
     <row r="23" spans="1:138" s="47" customFormat="1" ht="210" x14ac:dyDescent="0.2">
-      <c r="A23" s="467"/>
-      <c r="B23" s="524"/>
-      <c r="C23" s="526"/>
+      <c r="A23" s="476"/>
+      <c r="B23" s="529"/>
+      <c r="C23" s="531"/>
       <c r="D23" s="52" t="s">
         <v>114</v>
       </c>
@@ -44125,9 +44126,9 @@
       <c r="EH23" s="36"/>
     </row>
     <row r="24" spans="1:138" s="47" customFormat="1" ht="210" x14ac:dyDescent="0.2">
-      <c r="A24" s="467"/>
-      <c r="B24" s="524"/>
-      <c r="C24" s="526"/>
+      <c r="A24" s="476"/>
+      <c r="B24" s="529"/>
+      <c r="C24" s="531"/>
       <c r="D24" s="52" t="s">
         <v>92</v>
       </c>
@@ -44277,9 +44278,9 @@
       <c r="EH24" s="36"/>
     </row>
     <row r="25" spans="1:138" ht="30" x14ac:dyDescent="0.2">
-      <c r="A25" s="467"/>
-      <c r="B25" s="524"/>
-      <c r="C25" s="526"/>
+      <c r="A25" s="476"/>
+      <c r="B25" s="529"/>
+      <c r="C25" s="531"/>
       <c r="D25" s="52" t="s">
         <v>94</v>
       </c>
@@ -45489,17 +45490,17 @@
     </row>
   </sheetData>
   <mergeCells count="11">
-    <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A2:F2"/>
-    <mergeCell ref="A5:A13"/>
-    <mergeCell ref="B5:B13"/>
-    <mergeCell ref="C5:C13"/>
     <mergeCell ref="A20:A25"/>
     <mergeCell ref="B20:B25"/>
     <mergeCell ref="C20:C25"/>
     <mergeCell ref="A14:A19"/>
     <mergeCell ref="B14:B19"/>
     <mergeCell ref="C14:C19"/>
+    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A2:F2"/>
+    <mergeCell ref="A5:A13"/>
+    <mergeCell ref="B5:B13"/>
+    <mergeCell ref="C5:C13"/>
   </mergeCells>
   <dataValidations count="1">
     <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="J5:J7" xr:uid="{D5870D16-9B64-40FF-B604-4C6EAE214F81}"/>
@@ -45566,18 +45567,18 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:133" s="31" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="425" t="s">
+      <c r="A1" s="410" t="s">
         <v>38</v>
       </c>
-      <c r="B1" s="425"/>
-      <c r="C1" s="425"/>
-      <c r="D1" s="425"/>
-      <c r="E1" s="425"/>
-      <c r="F1" s="425"/>
-      <c r="G1" s="425"/>
+      <c r="B1" s="410"/>
+      <c r="C1" s="410"/>
+      <c r="D1" s="410"/>
+      <c r="E1" s="410"/>
+      <c r="F1" s="410"/>
+      <c r="G1" s="410"/>
       <c r="H1" s="334"/>
-      <c r="I1" s="413"/>
-      <c r="J1" s="413"/>
+      <c r="I1" s="394"/>
+      <c r="J1" s="394"/>
     </row>
     <row r="2" spans="1:133" s="29" customFormat="1" ht="30" x14ac:dyDescent="0.2">
       <c r="A2" s="27" t="s">
@@ -45749,13 +45750,13 @@
       <c r="EC3" s="36"/>
     </row>
     <row r="4" spans="1:133" ht="36" x14ac:dyDescent="0.2">
-      <c r="A4" s="414">
+      <c r="A4" s="395">
         <v>1</v>
       </c>
-      <c r="B4" s="416" t="s">
+      <c r="B4" s="397" t="s">
         <v>50</v>
       </c>
-      <c r="C4" s="534" t="s">
+      <c r="C4" s="535" t="s">
         <v>445</v>
       </c>
       <c r="D4" s="73" t="s">
@@ -45777,9 +45778,9 @@
       </c>
     </row>
     <row r="5" spans="1:133" ht="24" x14ac:dyDescent="0.2">
-      <c r="A5" s="415"/>
-      <c r="B5" s="417"/>
-      <c r="C5" s="535"/>
+      <c r="A5" s="396"/>
+      <c r="B5" s="398"/>
+      <c r="C5" s="536"/>
       <c r="D5" s="73" t="s">
         <v>56</v>
       </c>
@@ -45799,9 +45800,9 @@
       </c>
     </row>
     <row r="6" spans="1:133" ht="24" x14ac:dyDescent="0.2">
-      <c r="A6" s="415"/>
-      <c r="B6" s="417"/>
-      <c r="C6" s="535"/>
+      <c r="A6" s="396"/>
+      <c r="B6" s="398"/>
+      <c r="C6" s="536"/>
       <c r="D6" s="73" t="s">
         <v>61</v>
       </c>
@@ -45821,9 +45822,9 @@
       </c>
     </row>
     <row r="7" spans="1:133" ht="72" x14ac:dyDescent="0.2">
-      <c r="A7" s="415"/>
-      <c r="B7" s="417"/>
-      <c r="C7" s="535"/>
+      <c r="A7" s="396"/>
+      <c r="B7" s="398"/>
+      <c r="C7" s="536"/>
       <c r="D7" s="73" t="s">
         <v>63</v>
       </c>
@@ -45843,9 +45844,9 @@
       </c>
     </row>
     <row r="8" spans="1:133" ht="108" x14ac:dyDescent="0.2">
-      <c r="A8" s="415"/>
-      <c r="B8" s="417"/>
-      <c r="C8" s="535"/>
+      <c r="A8" s="396"/>
+      <c r="B8" s="398"/>
+      <c r="C8" s="536"/>
       <c r="D8" s="73" t="s">
         <v>68</v>
       </c>
@@ -45865,9 +45866,9 @@
       </c>
     </row>
     <row r="9" spans="1:133" ht="36" x14ac:dyDescent="0.2">
-      <c r="A9" s="415"/>
-      <c r="B9" s="417"/>
-      <c r="C9" s="535"/>
+      <c r="A9" s="396"/>
+      <c r="B9" s="398"/>
+      <c r="C9" s="536"/>
       <c r="D9" s="73" t="s">
         <v>72</v>
       </c>
@@ -45887,9 +45888,9 @@
       </c>
     </row>
     <row r="10" spans="1:133" ht="30" x14ac:dyDescent="0.2">
-      <c r="A10" s="415"/>
-      <c r="B10" s="417"/>
-      <c r="C10" s="535"/>
+      <c r="A10" s="396"/>
+      <c r="B10" s="398"/>
+      <c r="C10" s="536"/>
       <c r="D10" s="73" t="s">
         <v>76</v>
       </c>
@@ -45909,9 +45910,9 @@
       </c>
     </row>
     <row r="11" spans="1:133" ht="75" x14ac:dyDescent="0.2">
-      <c r="A11" s="415"/>
-      <c r="B11" s="417"/>
-      <c r="C11" s="535"/>
+      <c r="A11" s="396"/>
+      <c r="B11" s="398"/>
+      <c r="C11" s="536"/>
       <c r="D11" s="73" t="s">
         <v>79</v>
       </c>
@@ -45933,9 +45934,9 @@
       </c>
     </row>
     <row r="12" spans="1:133" ht="60" x14ac:dyDescent="0.2">
-      <c r="A12" s="415"/>
-      <c r="B12" s="417"/>
-      <c r="C12" s="535"/>
+      <c r="A12" s="396"/>
+      <c r="B12" s="398"/>
+      <c r="C12" s="536"/>
       <c r="D12" s="73" t="s">
         <v>83</v>
       </c>
@@ -45957,9 +45958,9 @@
       </c>
     </row>
     <row r="13" spans="1:133" ht="48" x14ac:dyDescent="0.2">
-      <c r="A13" s="415"/>
-      <c r="B13" s="417"/>
-      <c r="C13" s="535"/>
+      <c r="A13" s="396"/>
+      <c r="B13" s="398"/>
+      <c r="C13" s="536"/>
       <c r="D13" s="73" t="s">
         <v>86</v>
       </c>
@@ -45981,9 +45982,9 @@
       </c>
     </row>
     <row r="14" spans="1:133" s="42" customFormat="1" ht="150" x14ac:dyDescent="0.2">
-      <c r="A14" s="415"/>
-      <c r="B14" s="417"/>
-      <c r="C14" s="535"/>
+      <c r="A14" s="396"/>
+      <c r="B14" s="398"/>
+      <c r="C14" s="536"/>
       <c r="D14" s="73" t="s">
         <v>92</v>
       </c>
@@ -46128,9 +46129,9 @@
       <c r="EC14" s="41"/>
     </row>
     <row r="15" spans="1:133" ht="30" x14ac:dyDescent="0.2">
-      <c r="A15" s="415"/>
-      <c r="B15" s="417"/>
-      <c r="C15" s="536"/>
+      <c r="A15" s="396"/>
+      <c r="B15" s="398"/>
+      <c r="C15" s="537"/>
       <c r="D15" s="73" t="s">
         <v>94</v>
       </c>
@@ -46150,13 +46151,13 @@
       </c>
     </row>
     <row r="16" spans="1:133" ht="36" x14ac:dyDescent="0.2">
-      <c r="A16" s="406" t="s">
+      <c r="A16" s="402" t="s">
         <v>97</v>
       </c>
-      <c r="B16" s="407" t="s">
+      <c r="B16" s="403" t="s">
         <v>98</v>
       </c>
-      <c r="C16" s="421" t="s">
+      <c r="C16" s="404" t="s">
         <v>99</v>
       </c>
       <c r="D16" s="73" t="s">
@@ -46178,9 +46179,9 @@
       </c>
     </row>
     <row r="17" spans="1:133" ht="30" x14ac:dyDescent="0.2">
-      <c r="A17" s="406"/>
-      <c r="B17" s="407"/>
-      <c r="C17" s="422"/>
+      <c r="A17" s="402"/>
+      <c r="B17" s="403"/>
+      <c r="C17" s="405"/>
       <c r="D17" s="73" t="s">
         <v>56</v>
       </c>
@@ -46202,9 +46203,9 @@
       </c>
     </row>
     <row r="18" spans="1:133" ht="24" x14ac:dyDescent="0.2">
-      <c r="A18" s="406"/>
-      <c r="B18" s="407"/>
-      <c r="C18" s="422"/>
+      <c r="A18" s="402"/>
+      <c r="B18" s="403"/>
+      <c r="C18" s="405"/>
       <c r="D18" s="73" t="s">
         <v>61</v>
       </c>
@@ -46224,13 +46225,13 @@
       </c>
     </row>
     <row r="19" spans="1:133" ht="15" x14ac:dyDescent="0.2">
-      <c r="A19" s="406"/>
-      <c r="B19" s="407"/>
-      <c r="C19" s="422"/>
-      <c r="D19" s="421" t="s">
+      <c r="A19" s="402"/>
+      <c r="B19" s="403"/>
+      <c r="C19" s="405"/>
+      <c r="D19" s="404" t="s">
         <v>76</v>
       </c>
-      <c r="E19" s="437" t="s">
+      <c r="E19" s="436" t="s">
         <v>77</v>
       </c>
       <c r="F19" s="73" t="s">
@@ -46246,11 +46247,11 @@
       </c>
     </row>
     <row r="20" spans="1:133" s="47" customFormat="1" ht="30" x14ac:dyDescent="0.2">
-      <c r="A20" s="406"/>
-      <c r="B20" s="407"/>
-      <c r="C20" s="422"/>
-      <c r="D20" s="436"/>
-      <c r="E20" s="438"/>
+      <c r="A20" s="402"/>
+      <c r="B20" s="403"/>
+      <c r="C20" s="405"/>
+      <c r="D20" s="435"/>
+      <c r="E20" s="437"/>
       <c r="F20" s="73" t="s">
         <v>103</v>
       </c>
@@ -46387,9 +46388,9 @@
       <c r="EC20" s="36"/>
     </row>
     <row r="21" spans="1:133" s="47" customFormat="1" ht="75" x14ac:dyDescent="0.2">
-      <c r="A21" s="406"/>
-      <c r="B21" s="407"/>
-      <c r="C21" s="422"/>
+      <c r="A21" s="402"/>
+      <c r="B21" s="403"/>
+      <c r="C21" s="405"/>
       <c r="D21" s="73" t="s">
         <v>79</v>
       </c>
@@ -46534,9 +46535,9 @@
       <c r="EC21" s="36"/>
     </row>
     <row r="22" spans="1:133" ht="60" x14ac:dyDescent="0.2">
-      <c r="A22" s="406"/>
-      <c r="B22" s="407"/>
-      <c r="C22" s="422"/>
+      <c r="A22" s="402"/>
+      <c r="B22" s="403"/>
+      <c r="C22" s="405"/>
       <c r="D22" s="73" t="s">
         <v>83</v>
       </c>
@@ -46558,9 +46559,9 @@
       </c>
     </row>
     <row r="23" spans="1:133" ht="48" x14ac:dyDescent="0.2">
-      <c r="A23" s="406"/>
-      <c r="B23" s="407"/>
-      <c r="C23" s="422"/>
+      <c r="A23" s="402"/>
+      <c r="B23" s="403"/>
+      <c r="C23" s="405"/>
       <c r="D23" s="73" t="s">
         <v>106</v>
       </c>
@@ -46582,9 +46583,9 @@
       </c>
     </row>
     <row r="24" spans="1:133" ht="30" x14ac:dyDescent="0.2">
-      <c r="A24" s="406"/>
-      <c r="B24" s="407"/>
-      <c r="C24" s="422"/>
+      <c r="A24" s="402"/>
+      <c r="B24" s="403"/>
+      <c r="C24" s="405"/>
       <c r="D24" s="73" t="s">
         <v>92</v>
       </c>
@@ -46606,9 +46607,9 @@
       </c>
     </row>
     <row r="25" spans="1:133" ht="30" x14ac:dyDescent="0.2">
-      <c r="A25" s="414"/>
-      <c r="B25" s="416"/>
-      <c r="C25" s="422"/>
+      <c r="A25" s="395"/>
+      <c r="B25" s="397"/>
+      <c r="C25" s="405"/>
       <c r="D25" s="189" t="s">
         <v>94</v>
       </c>
@@ -46628,13 +46629,13 @@
       </c>
     </row>
     <row r="26" spans="1:133" ht="36" x14ac:dyDescent="0.2">
-      <c r="A26" s="393" t="s">
+      <c r="A26" s="413" t="s">
         <v>108</v>
       </c>
-      <c r="B26" s="428" t="s">
+      <c r="B26" s="427" t="s">
         <v>109</v>
       </c>
-      <c r="C26" s="426" t="s">
+      <c r="C26" s="441" t="s">
         <v>110</v>
       </c>
       <c r="D26" s="73" t="s">
@@ -46656,9 +46657,9 @@
       </c>
     </row>
     <row r="27" spans="1:133" ht="36" x14ac:dyDescent="0.2">
-      <c r="A27" s="394"/>
-      <c r="B27" s="429"/>
-      <c r="C27" s="426"/>
+      <c r="A27" s="414"/>
+      <c r="B27" s="428"/>
+      <c r="C27" s="441"/>
       <c r="D27" s="73" t="s">
         <v>56</v>
       </c>
@@ -46680,9 +46681,9 @@
       </c>
     </row>
     <row r="28" spans="1:133" ht="30" x14ac:dyDescent="0.2">
-      <c r="A28" s="394"/>
-      <c r="B28" s="429"/>
-      <c r="C28" s="426"/>
+      <c r="A28" s="414"/>
+      <c r="B28" s="428"/>
+      <c r="C28" s="441"/>
       <c r="D28" s="73" t="s">
         <v>61</v>
       </c>
@@ -46704,13 +46705,13 @@
       </c>
     </row>
     <row r="29" spans="1:133" ht="15" x14ac:dyDescent="0.2">
-      <c r="A29" s="394"/>
-      <c r="B29" s="429"/>
-      <c r="C29" s="426"/>
-      <c r="D29" s="427" t="s">
+      <c r="A29" s="414"/>
+      <c r="B29" s="428"/>
+      <c r="C29" s="441"/>
+      <c r="D29" s="432" t="s">
         <v>76</v>
       </c>
-      <c r="E29" s="431" t="s">
+      <c r="E29" s="433" t="s">
         <v>77</v>
       </c>
       <c r="F29" s="73" t="s">
@@ -46726,11 +46727,11 @@
       </c>
     </row>
     <row r="30" spans="1:133" ht="30" x14ac:dyDescent="0.2">
-      <c r="A30" s="394"/>
-      <c r="B30" s="429"/>
-      <c r="C30" s="426"/>
-      <c r="D30" s="427"/>
-      <c r="E30" s="432"/>
+      <c r="A30" s="414"/>
+      <c r="B30" s="428"/>
+      <c r="C30" s="441"/>
+      <c r="D30" s="432"/>
+      <c r="E30" s="434"/>
       <c r="F30" s="73" t="s">
         <v>113</v>
       </c>
@@ -46746,9 +46747,9 @@
       </c>
     </row>
     <row r="31" spans="1:133" ht="75" x14ac:dyDescent="0.2">
-      <c r="A31" s="394"/>
-      <c r="B31" s="429"/>
-      <c r="C31" s="426"/>
+      <c r="A31" s="414"/>
+      <c r="B31" s="428"/>
+      <c r="C31" s="441"/>
       <c r="D31" s="73" t="s">
         <v>79</v>
       </c>
@@ -46770,9 +46771,9 @@
       </c>
     </row>
     <row r="32" spans="1:133" ht="60" x14ac:dyDescent="0.2">
-      <c r="A32" s="394"/>
-      <c r="B32" s="429"/>
-      <c r="C32" s="426"/>
+      <c r="A32" s="414"/>
+      <c r="B32" s="428"/>
+      <c r="C32" s="441"/>
       <c r="D32" s="73" t="s">
         <v>83</v>
       </c>
@@ -46794,9 +46795,9 @@
       </c>
     </row>
     <row r="33" spans="1:133" s="47" customFormat="1" ht="48" x14ac:dyDescent="0.2">
-      <c r="A33" s="394"/>
-      <c r="B33" s="429"/>
-      <c r="C33" s="426"/>
+      <c r="A33" s="414"/>
+      <c r="B33" s="428"/>
+      <c r="C33" s="441"/>
       <c r="D33" s="73" t="s">
         <v>114</v>
       </c>
@@ -46941,9 +46942,9 @@
       <c r="EC33" s="36"/>
     </row>
     <row r="34" spans="1:133" s="47" customFormat="1" ht="45" x14ac:dyDescent="0.2">
-      <c r="A34" s="394"/>
-      <c r="B34" s="429"/>
-      <c r="C34" s="426"/>
+      <c r="A34" s="414"/>
+      <c r="B34" s="428"/>
+      <c r="C34" s="441"/>
       <c r="D34" s="73" t="s">
         <v>92</v>
       </c>
@@ -47088,9 +47089,9 @@
       <c r="EC34" s="36"/>
     </row>
     <row r="35" spans="1:133" ht="45" x14ac:dyDescent="0.2">
-      <c r="A35" s="395"/>
-      <c r="B35" s="430"/>
-      <c r="C35" s="426"/>
+      <c r="A35" s="415"/>
+      <c r="B35" s="429"/>
+      <c r="C35" s="441"/>
       <c r="D35" s="73" t="s">
         <v>94</v>
       </c>
@@ -47110,13 +47111,13 @@
       </c>
     </row>
     <row r="36" spans="1:133" ht="60" x14ac:dyDescent="0.2">
-      <c r="A36" s="393" t="s">
+      <c r="A36" s="413" t="s">
         <v>115</v>
       </c>
-      <c r="B36" s="396" t="s">
+      <c r="B36" s="416" t="s">
         <v>116</v>
       </c>
-      <c r="C36" s="411" t="s">
+      <c r="C36" s="420" t="s">
         <v>117</v>
       </c>
       <c r="D36" s="206" t="s">
@@ -47140,9 +47141,9 @@
       </c>
     </row>
     <row r="37" spans="1:133" ht="60" x14ac:dyDescent="0.2">
-      <c r="A37" s="394"/>
-      <c r="B37" s="397"/>
-      <c r="C37" s="411"/>
+      <c r="A37" s="414"/>
+      <c r="B37" s="417"/>
+      <c r="C37" s="420"/>
       <c r="D37" s="189" t="s">
         <v>122</v>
       </c>
@@ -47164,9 +47165,9 @@
       </c>
     </row>
     <row r="38" spans="1:133" ht="60" x14ac:dyDescent="0.2">
-      <c r="A38" s="394"/>
-      <c r="B38" s="397"/>
-      <c r="C38" s="411"/>
+      <c r="A38" s="414"/>
+      <c r="B38" s="417"/>
+      <c r="C38" s="420"/>
       <c r="D38" s="73" t="s">
         <v>126</v>
       </c>
@@ -47188,9 +47189,9 @@
       </c>
     </row>
     <row r="39" spans="1:133" ht="84" x14ac:dyDescent="0.2">
-      <c r="A39" s="394"/>
-      <c r="B39" s="397"/>
-      <c r="C39" s="411"/>
+      <c r="A39" s="414"/>
+      <c r="B39" s="417"/>
+      <c r="C39" s="420"/>
       <c r="D39" s="73" t="s">
         <v>130</v>
       </c>
@@ -47212,9 +47213,9 @@
       </c>
     </row>
     <row r="40" spans="1:133" ht="36" x14ac:dyDescent="0.2">
-      <c r="A40" s="394"/>
-      <c r="B40" s="397"/>
-      <c r="C40" s="411"/>
+      <c r="A40" s="414"/>
+      <c r="B40" s="417"/>
+      <c r="C40" s="420"/>
       <c r="D40" s="189" t="s">
         <v>134</v>
       </c>
@@ -47234,9 +47235,9 @@
       </c>
     </row>
     <row r="41" spans="1:133" ht="30" x14ac:dyDescent="0.2">
-      <c r="A41" s="394"/>
-      <c r="B41" s="397"/>
-      <c r="C41" s="411"/>
+      <c r="A41" s="414"/>
+      <c r="B41" s="417"/>
+      <c r="C41" s="420"/>
       <c r="D41" s="73" t="s">
         <v>61</v>
       </c>
@@ -47258,9 +47259,9 @@
       </c>
     </row>
     <row r="42" spans="1:133" ht="72" x14ac:dyDescent="0.2">
-      <c r="A42" s="394"/>
-      <c r="B42" s="397"/>
-      <c r="C42" s="411"/>
+      <c r="A42" s="414"/>
+      <c r="B42" s="417"/>
+      <c r="C42" s="420"/>
       <c r="D42" s="73" t="s">
         <v>76</v>
       </c>
@@ -47282,9 +47283,9 @@
       </c>
     </row>
     <row r="43" spans="1:133" ht="48" x14ac:dyDescent="0.2">
-      <c r="A43" s="394"/>
-      <c r="B43" s="397"/>
-      <c r="C43" s="411"/>
+      <c r="A43" s="414"/>
+      <c r="B43" s="417"/>
+      <c r="C43" s="420"/>
       <c r="D43" s="264" t="s">
         <v>114</v>
       </c>
@@ -47306,9 +47307,9 @@
       </c>
     </row>
     <row r="44" spans="1:133" ht="45" x14ac:dyDescent="0.2">
-      <c r="A44" s="394"/>
-      <c r="B44" s="397"/>
-      <c r="C44" s="411"/>
+      <c r="A44" s="414"/>
+      <c r="B44" s="417"/>
+      <c r="C44" s="420"/>
       <c r="D44" s="332" t="s">
         <v>92</v>
       </c>
@@ -47330,9 +47331,9 @@
       </c>
     </row>
     <row r="45" spans="1:133" ht="45" x14ac:dyDescent="0.2">
-      <c r="A45" s="395"/>
-      <c r="B45" s="398"/>
-      <c r="C45" s="412"/>
+      <c r="A45" s="415"/>
+      <c r="B45" s="418"/>
+      <c r="C45" s="421"/>
       <c r="D45" s="73" t="s">
         <v>94</v>
       </c>
@@ -47368,13 +47369,13 @@
       <c r="J46" s="108"/>
     </row>
     <row r="47" spans="1:133" ht="36" x14ac:dyDescent="0.2">
-      <c r="A47" s="406" t="s">
+      <c r="A47" s="402" t="s">
         <v>141</v>
       </c>
-      <c r="B47" s="407" t="s">
+      <c r="B47" s="403" t="s">
         <v>50</v>
       </c>
-      <c r="C47" s="426" t="s">
+      <c r="C47" s="441" t="s">
         <v>142</v>
       </c>
       <c r="D47" s="73" t="s">
@@ -47396,9 +47397,9 @@
       </c>
     </row>
     <row r="48" spans="1:133" ht="24" x14ac:dyDescent="0.2">
-      <c r="A48" s="406"/>
-      <c r="B48" s="407"/>
-      <c r="C48" s="427"/>
+      <c r="A48" s="402"/>
+      <c r="B48" s="403"/>
+      <c r="C48" s="432"/>
       <c r="D48" s="73" t="s">
         <v>56</v>
       </c>
@@ -47418,9 +47419,9 @@
       </c>
     </row>
     <row r="49" spans="1:10" ht="24" x14ac:dyDescent="0.2">
-      <c r="A49" s="406"/>
-      <c r="B49" s="407"/>
-      <c r="C49" s="427"/>
+      <c r="A49" s="402"/>
+      <c r="B49" s="403"/>
+      <c r="C49" s="432"/>
       <c r="D49" s="73" t="s">
         <v>61</v>
       </c>
@@ -47440,9 +47441,9 @@
       </c>
     </row>
     <row r="50" spans="1:10" ht="117.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A50" s="406"/>
-      <c r="B50" s="407"/>
-      <c r="C50" s="427"/>
+      <c r="A50" s="402"/>
+      <c r="B50" s="403"/>
+      <c r="C50" s="432"/>
       <c r="D50" s="73" t="s">
         <v>63</v>
       </c>
@@ -47462,9 +47463,9 @@
       </c>
     </row>
     <row r="51" spans="1:10" ht="108" x14ac:dyDescent="0.2">
-      <c r="A51" s="406"/>
-      <c r="B51" s="407"/>
-      <c r="C51" s="427"/>
+      <c r="A51" s="402"/>
+      <c r="B51" s="403"/>
+      <c r="C51" s="432"/>
       <c r="D51" s="73" t="s">
         <v>68</v>
       </c>
@@ -47484,9 +47485,9 @@
       </c>
     </row>
     <row r="52" spans="1:10" ht="36" x14ac:dyDescent="0.2">
-      <c r="A52" s="406"/>
-      <c r="B52" s="407"/>
-      <c r="C52" s="427"/>
+      <c r="A52" s="402"/>
+      <c r="B52" s="403"/>
+      <c r="C52" s="432"/>
       <c r="D52" s="73" t="s">
         <v>143</v>
       </c>
@@ -47506,9 +47507,9 @@
       </c>
     </row>
     <row r="53" spans="1:10" ht="30" x14ac:dyDescent="0.2">
-      <c r="A53" s="406"/>
-      <c r="B53" s="407"/>
-      <c r="C53" s="427"/>
+      <c r="A53" s="402"/>
+      <c r="B53" s="403"/>
+      <c r="C53" s="432"/>
       <c r="D53" s="73" t="s">
         <v>76</v>
       </c>
@@ -47528,9 +47529,9 @@
       </c>
     </row>
     <row r="54" spans="1:10" ht="75" x14ac:dyDescent="0.2">
-      <c r="A54" s="406"/>
-      <c r="B54" s="407"/>
-      <c r="C54" s="427"/>
+      <c r="A54" s="402"/>
+      <c r="B54" s="403"/>
+      <c r="C54" s="432"/>
       <c r="D54" s="73" t="s">
         <v>79</v>
       </c>
@@ -47552,9 +47553,9 @@
       </c>
     </row>
     <row r="55" spans="1:10" ht="60" x14ac:dyDescent="0.2">
-      <c r="A55" s="406"/>
-      <c r="B55" s="407"/>
-      <c r="C55" s="427"/>
+      <c r="A55" s="402"/>
+      <c r="B55" s="403"/>
+      <c r="C55" s="432"/>
       <c r="D55" s="73" t="s">
         <v>83</v>
       </c>
@@ -47576,9 +47577,9 @@
       </c>
     </row>
     <row r="56" spans="1:10" ht="60" x14ac:dyDescent="0.2">
-      <c r="A56" s="406"/>
-      <c r="B56" s="407"/>
-      <c r="C56" s="427"/>
+      <c r="A56" s="402"/>
+      <c r="B56" s="403"/>
+      <c r="C56" s="432"/>
       <c r="D56" s="73" t="s">
         <v>106</v>
       </c>
@@ -47600,9 +47601,9 @@
       </c>
     </row>
     <row r="57" spans="1:10" ht="30" x14ac:dyDescent="0.2">
-      <c r="A57" s="406"/>
-      <c r="B57" s="407"/>
-      <c r="C57" s="427"/>
+      <c r="A57" s="402"/>
+      <c r="B57" s="403"/>
+      <c r="C57" s="432"/>
       <c r="D57" s="73" t="s">
         <v>92</v>
       </c>
@@ -47624,9 +47625,9 @@
       </c>
     </row>
     <row r="58" spans="1:10" ht="30" x14ac:dyDescent="0.2">
-      <c r="A58" s="406"/>
-      <c r="B58" s="407"/>
-      <c r="C58" s="427"/>
+      <c r="A58" s="402"/>
+      <c r="B58" s="403"/>
+      <c r="C58" s="432"/>
       <c r="D58" s="73" t="s">
         <v>94</v>
       </c>
@@ -47648,27 +47649,27 @@
   </sheetData>
   <autoFilter ref="A2:EC43" xr:uid="{92218EDD-6442-41B5-9565-D949ECDDA5BC}"/>
   <mergeCells count="21">
+    <mergeCell ref="A16:A25"/>
+    <mergeCell ref="B16:B25"/>
+    <mergeCell ref="C16:C25"/>
+    <mergeCell ref="D19:D20"/>
+    <mergeCell ref="E19:E20"/>
+    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="I1:J1"/>
+    <mergeCell ref="A4:A15"/>
+    <mergeCell ref="B4:B15"/>
+    <mergeCell ref="C4:C15"/>
+    <mergeCell ref="D29:D30"/>
+    <mergeCell ref="E29:E30"/>
+    <mergeCell ref="A36:A45"/>
+    <mergeCell ref="B36:B45"/>
+    <mergeCell ref="C36:C45"/>
     <mergeCell ref="A47:A58"/>
     <mergeCell ref="B47:B58"/>
     <mergeCell ref="C47:C58"/>
     <mergeCell ref="A26:A35"/>
     <mergeCell ref="B26:B35"/>
     <mergeCell ref="C26:C35"/>
-    <mergeCell ref="D29:D30"/>
-    <mergeCell ref="E29:E30"/>
-    <mergeCell ref="A36:A45"/>
-    <mergeCell ref="B36:B45"/>
-    <mergeCell ref="C36:C45"/>
-    <mergeCell ref="A1:G1"/>
-    <mergeCell ref="I1:J1"/>
-    <mergeCell ref="A4:A15"/>
-    <mergeCell ref="B4:B15"/>
-    <mergeCell ref="C4:C15"/>
-    <mergeCell ref="A16:A25"/>
-    <mergeCell ref="B16:B25"/>
-    <mergeCell ref="C16:C25"/>
-    <mergeCell ref="D19:D20"/>
-    <mergeCell ref="E19:E20"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait"/>
@@ -47974,18 +47975,18 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:133" s="31" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="425" t="s">
+      <c r="A1" s="410" t="s">
         <v>38</v>
       </c>
-      <c r="B1" s="425"/>
-      <c r="C1" s="425"/>
-      <c r="D1" s="425"/>
-      <c r="E1" s="425"/>
-      <c r="F1" s="425"/>
-      <c r="G1" s="425"/>
+      <c r="B1" s="410"/>
+      <c r="C1" s="410"/>
+      <c r="D1" s="410"/>
+      <c r="E1" s="410"/>
+      <c r="F1" s="410"/>
+      <c r="G1" s="410"/>
       <c r="H1" s="334"/>
-      <c r="I1" s="413"/>
-      <c r="J1" s="413"/>
+      <c r="I1" s="394"/>
+      <c r="J1" s="394"/>
     </row>
     <row r="2" spans="1:133" s="29" customFormat="1" ht="30" x14ac:dyDescent="0.2">
       <c r="A2" s="27" t="s">
@@ -48157,13 +48158,13 @@
       <c r="EC3" s="36"/>
     </row>
     <row r="4" spans="1:133" ht="36" x14ac:dyDescent="0.2">
-      <c r="A4" s="414">
+      <c r="A4" s="395">
         <v>1</v>
       </c>
-      <c r="B4" s="416" t="s">
+      <c r="B4" s="397" t="s">
         <v>50</v>
       </c>
-      <c r="C4" s="433" t="s">
+      <c r="C4" s="438" t="s">
         <v>217</v>
       </c>
       <c r="D4" s="73" t="s">
@@ -48185,9 +48186,9 @@
       </c>
     </row>
     <row r="5" spans="1:133" ht="24" x14ac:dyDescent="0.2">
-      <c r="A5" s="415"/>
-      <c r="B5" s="417"/>
-      <c r="C5" s="434"/>
+      <c r="A5" s="396"/>
+      <c r="B5" s="398"/>
+      <c r="C5" s="439"/>
       <c r="D5" s="73" t="s">
         <v>56</v>
       </c>
@@ -48207,9 +48208,9 @@
       </c>
     </row>
     <row r="6" spans="1:133" ht="24" x14ac:dyDescent="0.2">
-      <c r="A6" s="415"/>
-      <c r="B6" s="417"/>
-      <c r="C6" s="434"/>
+      <c r="A6" s="396"/>
+      <c r="B6" s="398"/>
+      <c r="C6" s="439"/>
       <c r="D6" s="73" t="s">
         <v>61</v>
       </c>
@@ -48229,9 +48230,9 @@
       </c>
     </row>
     <row r="7" spans="1:133" ht="72" x14ac:dyDescent="0.2">
-      <c r="A7" s="415"/>
-      <c r="B7" s="417"/>
-      <c r="C7" s="434"/>
+      <c r="A7" s="396"/>
+      <c r="B7" s="398"/>
+      <c r="C7" s="439"/>
       <c r="D7" s="73" t="s">
         <v>63</v>
       </c>
@@ -48251,9 +48252,9 @@
       </c>
     </row>
     <row r="8" spans="1:133" ht="108" x14ac:dyDescent="0.2">
-      <c r="A8" s="415"/>
-      <c r="B8" s="417"/>
-      <c r="C8" s="434"/>
+      <c r="A8" s="396"/>
+      <c r="B8" s="398"/>
+      <c r="C8" s="439"/>
       <c r="D8" s="73" t="s">
         <v>68</v>
       </c>
@@ -48273,9 +48274,9 @@
       </c>
     </row>
     <row r="9" spans="1:133" ht="36" x14ac:dyDescent="0.2">
-      <c r="A9" s="415"/>
-      <c r="B9" s="417"/>
-      <c r="C9" s="434"/>
+      <c r="A9" s="396"/>
+      <c r="B9" s="398"/>
+      <c r="C9" s="439"/>
       <c r="D9" s="73" t="s">
         <v>72</v>
       </c>
@@ -48295,9 +48296,9 @@
       </c>
     </row>
     <row r="10" spans="1:133" ht="30" x14ac:dyDescent="0.2">
-      <c r="A10" s="415"/>
-      <c r="B10" s="417"/>
-      <c r="C10" s="434"/>
+      <c r="A10" s="396"/>
+      <c r="B10" s="398"/>
+      <c r="C10" s="439"/>
       <c r="D10" s="73" t="s">
         <v>76</v>
       </c>
@@ -48317,9 +48318,9 @@
       </c>
     </row>
     <row r="11" spans="1:133" ht="75" x14ac:dyDescent="0.2">
-      <c r="A11" s="415"/>
-      <c r="B11" s="417"/>
-      <c r="C11" s="434"/>
+      <c r="A11" s="396"/>
+      <c r="B11" s="398"/>
+      <c r="C11" s="439"/>
       <c r="D11" s="73" t="s">
         <v>79</v>
       </c>
@@ -48341,9 +48342,9 @@
       </c>
     </row>
     <row r="12" spans="1:133" ht="60" x14ac:dyDescent="0.2">
-      <c r="A12" s="415"/>
-      <c r="B12" s="417"/>
-      <c r="C12" s="434"/>
+      <c r="A12" s="396"/>
+      <c r="B12" s="398"/>
+      <c r="C12" s="439"/>
       <c r="D12" s="73" t="s">
         <v>83</v>
       </c>
@@ -48365,9 +48366,9 @@
       </c>
     </row>
     <row r="13" spans="1:133" ht="48" x14ac:dyDescent="0.2">
-      <c r="A13" s="415"/>
-      <c r="B13" s="417"/>
-      <c r="C13" s="434"/>
+      <c r="A13" s="396"/>
+      <c r="B13" s="398"/>
+      <c r="C13" s="439"/>
       <c r="D13" s="73" t="s">
         <v>86</v>
       </c>
@@ -48389,9 +48390,9 @@
       </c>
     </row>
     <row r="14" spans="1:133" s="42" customFormat="1" ht="30" x14ac:dyDescent="0.2">
-      <c r="A14" s="415"/>
-      <c r="B14" s="417"/>
-      <c r="C14" s="434"/>
+      <c r="A14" s="396"/>
+      <c r="B14" s="398"/>
+      <c r="C14" s="439"/>
       <c r="D14" s="73" t="s">
         <v>92</v>
       </c>
@@ -48536,9 +48537,9 @@
       <c r="EC14" s="41"/>
     </row>
     <row r="15" spans="1:133" ht="30" x14ac:dyDescent="0.2">
-      <c r="A15" s="415"/>
-      <c r="B15" s="417"/>
-      <c r="C15" s="435"/>
+      <c r="A15" s="396"/>
+      <c r="B15" s="398"/>
+      <c r="C15" s="440"/>
       <c r="D15" s="73" t="s">
         <v>94</v>
       </c>
@@ -48558,13 +48559,13 @@
       </c>
     </row>
     <row r="16" spans="1:133" ht="36" x14ac:dyDescent="0.2">
-      <c r="A16" s="406" t="s">
+      <c r="A16" s="402" t="s">
         <v>97</v>
       </c>
-      <c r="B16" s="407" t="s">
+      <c r="B16" s="403" t="s">
         <v>98</v>
       </c>
-      <c r="C16" s="421" t="s">
+      <c r="C16" s="404" t="s">
         <v>99</v>
       </c>
       <c r="D16" s="73" t="s">
@@ -48586,9 +48587,9 @@
       </c>
     </row>
     <row r="17" spans="1:133" ht="30" x14ac:dyDescent="0.2">
-      <c r="A17" s="406"/>
-      <c r="B17" s="407"/>
-      <c r="C17" s="422"/>
+      <c r="A17" s="402"/>
+      <c r="B17" s="403"/>
+      <c r="C17" s="405"/>
       <c r="D17" s="73" t="s">
         <v>56</v>
       </c>
@@ -48610,9 +48611,9 @@
       </c>
     </row>
     <row r="18" spans="1:133" ht="24" x14ac:dyDescent="0.2">
-      <c r="A18" s="406"/>
-      <c r="B18" s="407"/>
-      <c r="C18" s="422"/>
+      <c r="A18" s="402"/>
+      <c r="B18" s="403"/>
+      <c r="C18" s="405"/>
       <c r="D18" s="73" t="s">
         <v>61</v>
       </c>
@@ -48632,13 +48633,13 @@
       </c>
     </row>
     <row r="19" spans="1:133" ht="15" x14ac:dyDescent="0.2">
-      <c r="A19" s="406"/>
-      <c r="B19" s="407"/>
-      <c r="C19" s="422"/>
-      <c r="D19" s="421" t="s">
+      <c r="A19" s="402"/>
+      <c r="B19" s="403"/>
+      <c r="C19" s="405"/>
+      <c r="D19" s="404" t="s">
         <v>76</v>
       </c>
-      <c r="E19" s="437" t="s">
+      <c r="E19" s="436" t="s">
         <v>77</v>
       </c>
       <c r="F19" s="73" t="s">
@@ -48654,11 +48655,11 @@
       </c>
     </row>
     <row r="20" spans="1:133" s="47" customFormat="1" ht="30" x14ac:dyDescent="0.2">
-      <c r="A20" s="406"/>
-      <c r="B20" s="407"/>
-      <c r="C20" s="422"/>
-      <c r="D20" s="436"/>
-      <c r="E20" s="438"/>
+      <c r="A20" s="402"/>
+      <c r="B20" s="403"/>
+      <c r="C20" s="405"/>
+      <c r="D20" s="435"/>
+      <c r="E20" s="437"/>
       <c r="F20" s="73" t="s">
         <v>103</v>
       </c>
@@ -48795,9 +48796,9 @@
       <c r="EC20" s="36"/>
     </row>
     <row r="21" spans="1:133" s="47" customFormat="1" ht="75" x14ac:dyDescent="0.2">
-      <c r="A21" s="406"/>
-      <c r="B21" s="407"/>
-      <c r="C21" s="422"/>
+      <c r="A21" s="402"/>
+      <c r="B21" s="403"/>
+      <c r="C21" s="405"/>
       <c r="D21" s="73" t="s">
         <v>79</v>
       </c>
@@ -48942,9 +48943,9 @@
       <c r="EC21" s="36"/>
     </row>
     <row r="22" spans="1:133" ht="60" x14ac:dyDescent="0.2">
-      <c r="A22" s="406"/>
-      <c r="B22" s="407"/>
-      <c r="C22" s="422"/>
+      <c r="A22" s="402"/>
+      <c r="B22" s="403"/>
+      <c r="C22" s="405"/>
       <c r="D22" s="73" t="s">
         <v>83</v>
       </c>
@@ -48966,9 +48967,9 @@
       </c>
     </row>
     <row r="23" spans="1:133" ht="48" x14ac:dyDescent="0.2">
-      <c r="A23" s="406"/>
-      <c r="B23" s="407"/>
-      <c r="C23" s="422"/>
+      <c r="A23" s="402"/>
+      <c r="B23" s="403"/>
+      <c r="C23" s="405"/>
       <c r="D23" s="73" t="s">
         <v>106</v>
       </c>
@@ -48990,9 +48991,9 @@
       </c>
     </row>
     <row r="24" spans="1:133" ht="30" x14ac:dyDescent="0.2">
-      <c r="A24" s="406"/>
-      <c r="B24" s="407"/>
-      <c r="C24" s="422"/>
+      <c r="A24" s="402"/>
+      <c r="B24" s="403"/>
+      <c r="C24" s="405"/>
       <c r="D24" s="73" t="s">
         <v>92</v>
       </c>
@@ -49014,9 +49015,9 @@
       </c>
     </row>
     <row r="25" spans="1:133" ht="30" x14ac:dyDescent="0.2">
-      <c r="A25" s="414"/>
-      <c r="B25" s="416"/>
-      <c r="C25" s="422"/>
+      <c r="A25" s="395"/>
+      <c r="B25" s="397"/>
+      <c r="C25" s="405"/>
       <c r="D25" s="189" t="s">
         <v>94</v>
       </c>
@@ -49036,13 +49037,13 @@
       </c>
     </row>
     <row r="26" spans="1:133" ht="36" x14ac:dyDescent="0.2">
-      <c r="A26" s="393" t="s">
+      <c r="A26" s="413" t="s">
         <v>108</v>
       </c>
-      <c r="B26" s="428" t="s">
+      <c r="B26" s="427" t="s">
         <v>109</v>
       </c>
-      <c r="C26" s="426" t="s">
+      <c r="C26" s="441" t="s">
         <v>110</v>
       </c>
       <c r="D26" s="73" t="s">
@@ -49064,9 +49065,9 @@
       </c>
     </row>
     <row r="27" spans="1:133" ht="36" x14ac:dyDescent="0.2">
-      <c r="A27" s="394"/>
-      <c r="B27" s="429"/>
-      <c r="C27" s="426"/>
+      <c r="A27" s="414"/>
+      <c r="B27" s="428"/>
+      <c r="C27" s="441"/>
       <c r="D27" s="73" t="s">
         <v>56</v>
       </c>
@@ -49088,9 +49089,9 @@
       </c>
     </row>
     <row r="28" spans="1:133" ht="30" x14ac:dyDescent="0.2">
-      <c r="A28" s="394"/>
-      <c r="B28" s="429"/>
-      <c r="C28" s="426"/>
+      <c r="A28" s="414"/>
+      <c r="B28" s="428"/>
+      <c r="C28" s="441"/>
       <c r="D28" s="73" t="s">
         <v>61</v>
       </c>
@@ -49112,13 +49113,13 @@
       </c>
     </row>
     <row r="29" spans="1:133" ht="15" x14ac:dyDescent="0.2">
-      <c r="A29" s="394"/>
-      <c r="B29" s="429"/>
-      <c r="C29" s="426"/>
-      <c r="D29" s="427" t="s">
+      <c r="A29" s="414"/>
+      <c r="B29" s="428"/>
+      <c r="C29" s="441"/>
+      <c r="D29" s="432" t="s">
         <v>76</v>
       </c>
-      <c r="E29" s="431" t="s">
+      <c r="E29" s="433" t="s">
         <v>77</v>
       </c>
       <c r="F29" s="73" t="s">
@@ -49134,11 +49135,11 @@
       </c>
     </row>
     <row r="30" spans="1:133" ht="30" x14ac:dyDescent="0.2">
-      <c r="A30" s="394"/>
-      <c r="B30" s="429"/>
-      <c r="C30" s="426"/>
-      <c r="D30" s="427"/>
-      <c r="E30" s="432"/>
+      <c r="A30" s="414"/>
+      <c r="B30" s="428"/>
+      <c r="C30" s="441"/>
+      <c r="D30" s="432"/>
+      <c r="E30" s="434"/>
       <c r="F30" s="73" t="s">
         <v>113</v>
       </c>
@@ -49154,9 +49155,9 @@
       </c>
     </row>
     <row r="31" spans="1:133" ht="75" x14ac:dyDescent="0.2">
-      <c r="A31" s="394"/>
-      <c r="B31" s="429"/>
-      <c r="C31" s="426"/>
+      <c r="A31" s="414"/>
+      <c r="B31" s="428"/>
+      <c r="C31" s="441"/>
       <c r="D31" s="73" t="s">
         <v>79</v>
       </c>
@@ -49178,9 +49179,9 @@
       </c>
     </row>
     <row r="32" spans="1:133" ht="60" x14ac:dyDescent="0.2">
-      <c r="A32" s="394"/>
-      <c r="B32" s="429"/>
-      <c r="C32" s="426"/>
+      <c r="A32" s="414"/>
+      <c r="B32" s="428"/>
+      <c r="C32" s="441"/>
       <c r="D32" s="73" t="s">
         <v>83</v>
       </c>
@@ -49202,9 +49203,9 @@
       </c>
     </row>
     <row r="33" spans="1:133" s="47" customFormat="1" ht="48" x14ac:dyDescent="0.2">
-      <c r="A33" s="394"/>
-      <c r="B33" s="429"/>
-      <c r="C33" s="426"/>
+      <c r="A33" s="414"/>
+      <c r="B33" s="428"/>
+      <c r="C33" s="441"/>
       <c r="D33" s="73" t="s">
         <v>114</v>
       </c>
@@ -49349,9 +49350,9 @@
       <c r="EC33" s="36"/>
     </row>
     <row r="34" spans="1:133" s="47" customFormat="1" ht="30" x14ac:dyDescent="0.2">
-      <c r="A34" s="394"/>
-      <c r="B34" s="429"/>
-      <c r="C34" s="426"/>
+      <c r="A34" s="414"/>
+      <c r="B34" s="428"/>
+      <c r="C34" s="441"/>
       <c r="D34" s="73" t="s">
         <v>92</v>
       </c>
@@ -49496,9 +49497,9 @@
       <c r="EC34" s="36"/>
     </row>
     <row r="35" spans="1:133" ht="30" x14ac:dyDescent="0.2">
-      <c r="A35" s="395"/>
-      <c r="B35" s="430"/>
-      <c r="C35" s="426"/>
+      <c r="A35" s="415"/>
+      <c r="B35" s="429"/>
+      <c r="C35" s="441"/>
       <c r="D35" s="73" t="s">
         <v>94</v>
       </c>
@@ -49518,13 +49519,13 @@
       </c>
     </row>
     <row r="36" spans="1:133" ht="60" x14ac:dyDescent="0.2">
-      <c r="A36" s="393" t="s">
+      <c r="A36" s="413" t="s">
         <v>115</v>
       </c>
-      <c r="B36" s="396" t="s">
+      <c r="B36" s="416" t="s">
         <v>116</v>
       </c>
-      <c r="C36" s="411" t="s">
+      <c r="C36" s="420" t="s">
         <v>117</v>
       </c>
       <c r="D36" s="206" t="s">
@@ -49548,9 +49549,9 @@
       </c>
     </row>
     <row r="37" spans="1:133" ht="60" x14ac:dyDescent="0.2">
-      <c r="A37" s="394"/>
-      <c r="B37" s="397"/>
-      <c r="C37" s="411"/>
+      <c r="A37" s="414"/>
+      <c r="B37" s="417"/>
+      <c r="C37" s="420"/>
       <c r="D37" s="189" t="s">
         <v>122</v>
       </c>
@@ -49572,9 +49573,9 @@
       </c>
     </row>
     <row r="38" spans="1:133" ht="60" x14ac:dyDescent="0.2">
-      <c r="A38" s="394"/>
-      <c r="B38" s="397"/>
-      <c r="C38" s="411"/>
+      <c r="A38" s="414"/>
+      <c r="B38" s="417"/>
+      <c r="C38" s="420"/>
       <c r="D38" s="73" t="s">
         <v>126</v>
       </c>
@@ -49596,9 +49597,9 @@
       </c>
     </row>
     <row r="39" spans="1:133" ht="84" x14ac:dyDescent="0.2">
-      <c r="A39" s="394"/>
-      <c r="B39" s="397"/>
-      <c r="C39" s="411"/>
+      <c r="A39" s="414"/>
+      <c r="B39" s="417"/>
+      <c r="C39" s="420"/>
       <c r="D39" s="73" t="s">
         <v>130</v>
       </c>
@@ -49620,9 +49621,9 @@
       </c>
     </row>
     <row r="40" spans="1:133" ht="36" x14ac:dyDescent="0.2">
-      <c r="A40" s="394"/>
-      <c r="B40" s="397"/>
-      <c r="C40" s="411"/>
+      <c r="A40" s="414"/>
+      <c r="B40" s="417"/>
+      <c r="C40" s="420"/>
       <c r="D40" s="189" t="s">
         <v>134</v>
       </c>
@@ -49642,9 +49643,9 @@
       </c>
     </row>
     <row r="41" spans="1:133" ht="30" x14ac:dyDescent="0.2">
-      <c r="A41" s="394"/>
-      <c r="B41" s="397"/>
-      <c r="C41" s="411"/>
+      <c r="A41" s="414"/>
+      <c r="B41" s="417"/>
+      <c r="C41" s="420"/>
       <c r="D41" s="73" t="s">
         <v>61</v>
       </c>
@@ -49666,9 +49667,9 @@
       </c>
     </row>
     <row r="42" spans="1:133" ht="72" x14ac:dyDescent="0.2">
-      <c r="A42" s="394"/>
-      <c r="B42" s="397"/>
-      <c r="C42" s="411"/>
+      <c r="A42" s="414"/>
+      <c r="B42" s="417"/>
+      <c r="C42" s="420"/>
       <c r="D42" s="73" t="s">
         <v>76</v>
       </c>
@@ -49690,9 +49691,9 @@
       </c>
     </row>
     <row r="43" spans="1:133" ht="48" x14ac:dyDescent="0.2">
-      <c r="A43" s="394"/>
-      <c r="B43" s="397"/>
-      <c r="C43" s="411"/>
+      <c r="A43" s="414"/>
+      <c r="B43" s="417"/>
+      <c r="C43" s="420"/>
       <c r="D43" s="264" t="s">
         <v>114</v>
       </c>
@@ -49714,9 +49715,9 @@
       </c>
     </row>
     <row r="44" spans="1:133" ht="30" x14ac:dyDescent="0.2">
-      <c r="A44" s="394"/>
-      <c r="B44" s="397"/>
-      <c r="C44" s="411"/>
+      <c r="A44" s="414"/>
+      <c r="B44" s="417"/>
+      <c r="C44" s="420"/>
       <c r="D44" s="332" t="s">
         <v>92</v>
       </c>
@@ -49738,9 +49739,9 @@
       </c>
     </row>
     <row r="45" spans="1:133" ht="30" x14ac:dyDescent="0.2">
-      <c r="A45" s="395"/>
-      <c r="B45" s="398"/>
-      <c r="C45" s="412"/>
+      <c r="A45" s="415"/>
+      <c r="B45" s="418"/>
+      <c r="C45" s="421"/>
       <c r="D45" s="73" t="s">
         <v>94</v>
       </c>
@@ -49776,13 +49777,13 @@
       <c r="J46" s="108"/>
     </row>
     <row r="47" spans="1:133" ht="36" x14ac:dyDescent="0.2">
-      <c r="A47" s="406" t="s">
+      <c r="A47" s="402" t="s">
         <v>141</v>
       </c>
-      <c r="B47" s="407" t="s">
+      <c r="B47" s="403" t="s">
         <v>50</v>
       </c>
-      <c r="C47" s="426" t="s">
+      <c r="C47" s="441" t="s">
         <v>142</v>
       </c>
       <c r="D47" s="73" t="s">
@@ -49804,9 +49805,9 @@
       </c>
     </row>
     <row r="48" spans="1:133" ht="24" x14ac:dyDescent="0.2">
-      <c r="A48" s="406"/>
-      <c r="B48" s="407"/>
-      <c r="C48" s="427"/>
+      <c r="A48" s="402"/>
+      <c r="B48" s="403"/>
+      <c r="C48" s="432"/>
       <c r="D48" s="73" t="s">
         <v>56</v>
       </c>
@@ -49826,9 +49827,9 @@
       </c>
     </row>
     <row r="49" spans="1:10" ht="24" x14ac:dyDescent="0.2">
-      <c r="A49" s="406"/>
-      <c r="B49" s="407"/>
-      <c r="C49" s="427"/>
+      <c r="A49" s="402"/>
+      <c r="B49" s="403"/>
+      <c r="C49" s="432"/>
       <c r="D49" s="73" t="s">
         <v>61</v>
       </c>
@@ -49848,9 +49849,9 @@
       </c>
     </row>
     <row r="50" spans="1:10" ht="117.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A50" s="406"/>
-      <c r="B50" s="407"/>
-      <c r="C50" s="427"/>
+      <c r="A50" s="402"/>
+      <c r="B50" s="403"/>
+      <c r="C50" s="432"/>
       <c r="D50" s="73" t="s">
         <v>63</v>
       </c>
@@ -49870,9 +49871,9 @@
       </c>
     </row>
     <row r="51" spans="1:10" ht="108" x14ac:dyDescent="0.2">
-      <c r="A51" s="406"/>
-      <c r="B51" s="407"/>
-      <c r="C51" s="427"/>
+      <c r="A51" s="402"/>
+      <c r="B51" s="403"/>
+      <c r="C51" s="432"/>
       <c r="D51" s="73" t="s">
         <v>68</v>
       </c>
@@ -49892,9 +49893,9 @@
       </c>
     </row>
     <row r="52" spans="1:10" ht="36" x14ac:dyDescent="0.2">
-      <c r="A52" s="406"/>
-      <c r="B52" s="407"/>
-      <c r="C52" s="427"/>
+      <c r="A52" s="402"/>
+      <c r="B52" s="403"/>
+      <c r="C52" s="432"/>
       <c r="D52" s="73" t="s">
         <v>143</v>
       </c>
@@ -49914,9 +49915,9 @@
       </c>
     </row>
     <row r="53" spans="1:10" ht="30" x14ac:dyDescent="0.2">
-      <c r="A53" s="406"/>
-      <c r="B53" s="407"/>
-      <c r="C53" s="427"/>
+      <c r="A53" s="402"/>
+      <c r="B53" s="403"/>
+      <c r="C53" s="432"/>
       <c r="D53" s="73" t="s">
         <v>76</v>
       </c>
@@ -49936,9 +49937,9 @@
       </c>
     </row>
     <row r="54" spans="1:10" ht="75" x14ac:dyDescent="0.2">
-      <c r="A54" s="406"/>
-      <c r="B54" s="407"/>
-      <c r="C54" s="427"/>
+      <c r="A54" s="402"/>
+      <c r="B54" s="403"/>
+      <c r="C54" s="432"/>
       <c r="D54" s="73" t="s">
         <v>79</v>
       </c>
@@ -49960,9 +49961,9 @@
       </c>
     </row>
     <row r="55" spans="1:10" ht="60" x14ac:dyDescent="0.2">
-      <c r="A55" s="406"/>
-      <c r="B55" s="407"/>
-      <c r="C55" s="427"/>
+      <c r="A55" s="402"/>
+      <c r="B55" s="403"/>
+      <c r="C55" s="432"/>
       <c r="D55" s="73" t="s">
         <v>83</v>
       </c>
@@ -49984,9 +49985,9 @@
       </c>
     </row>
     <row r="56" spans="1:10" ht="60" x14ac:dyDescent="0.2">
-      <c r="A56" s="406"/>
-      <c r="B56" s="407"/>
-      <c r="C56" s="427"/>
+      <c r="A56" s="402"/>
+      <c r="B56" s="403"/>
+      <c r="C56" s="432"/>
       <c r="D56" s="73" t="s">
         <v>106</v>
       </c>
@@ -50008,9 +50009,9 @@
       </c>
     </row>
     <row r="57" spans="1:10" ht="30" x14ac:dyDescent="0.2">
-      <c r="A57" s="406"/>
-      <c r="B57" s="407"/>
-      <c r="C57" s="427"/>
+      <c r="A57" s="402"/>
+      <c r="B57" s="403"/>
+      <c r="C57" s="432"/>
       <c r="D57" s="73" t="s">
         <v>92</v>
       </c>
@@ -50032,9 +50033,9 @@
       </c>
     </row>
     <row r="58" spans="1:10" ht="30" x14ac:dyDescent="0.2">
-      <c r="A58" s="406"/>
-      <c r="B58" s="407"/>
-      <c r="C58" s="427"/>
+      <c r="A58" s="402"/>
+      <c r="B58" s="403"/>
+      <c r="C58" s="432"/>
       <c r="D58" s="73" t="s">
         <v>94</v>
       </c>
@@ -50054,13 +50055,13 @@
       </c>
     </row>
     <row r="59" spans="1:10" ht="36" x14ac:dyDescent="0.2">
-      <c r="A59" s="393" t="s">
+      <c r="A59" s="413" t="s">
         <v>108</v>
       </c>
-      <c r="B59" s="428" t="s">
+      <c r="B59" s="427" t="s">
         <v>109</v>
       </c>
-      <c r="C59" s="439" t="s">
+      <c r="C59" s="430" t="s">
         <v>218</v>
       </c>
       <c r="D59" s="73" t="s">
@@ -50082,9 +50083,9 @@
       </c>
     </row>
     <row r="60" spans="1:10" ht="36" x14ac:dyDescent="0.2">
-      <c r="A60" s="394"/>
-      <c r="B60" s="429"/>
-      <c r="C60" s="440"/>
+      <c r="A60" s="414"/>
+      <c r="B60" s="428"/>
+      <c r="C60" s="431"/>
       <c r="D60" s="73" t="s">
         <v>56</v>
       </c>
@@ -50106,9 +50107,9 @@
       </c>
     </row>
     <row r="61" spans="1:10" ht="30" x14ac:dyDescent="0.2">
-      <c r="A61" s="394"/>
-      <c r="B61" s="429"/>
-      <c r="C61" s="440"/>
+      <c r="A61" s="414"/>
+      <c r="B61" s="428"/>
+      <c r="C61" s="431"/>
       <c r="D61" s="73" t="s">
         <v>61</v>
       </c>
@@ -50130,13 +50131,13 @@
       </c>
     </row>
     <row r="62" spans="1:10" ht="15" x14ac:dyDescent="0.2">
-      <c r="A62" s="394"/>
-      <c r="B62" s="429"/>
-      <c r="C62" s="440"/>
-      <c r="D62" s="427" t="s">
+      <c r="A62" s="414"/>
+      <c r="B62" s="428"/>
+      <c r="C62" s="431"/>
+      <c r="D62" s="432" t="s">
         <v>76</v>
       </c>
-      <c r="E62" s="431" t="s">
+      <c r="E62" s="433" t="s">
         <v>77</v>
       </c>
       <c r="F62" s="73" t="s">
@@ -50152,11 +50153,11 @@
       </c>
     </row>
     <row r="63" spans="1:10" ht="30" x14ac:dyDescent="0.2">
-      <c r="A63" s="394"/>
-      <c r="B63" s="429"/>
-      <c r="C63" s="440"/>
-      <c r="D63" s="427"/>
-      <c r="E63" s="432"/>
+      <c r="A63" s="414"/>
+      <c r="B63" s="428"/>
+      <c r="C63" s="431"/>
+      <c r="D63" s="432"/>
+      <c r="E63" s="434"/>
       <c r="F63" s="73" t="s">
         <v>113</v>
       </c>
@@ -50172,9 +50173,9 @@
       </c>
     </row>
     <row r="64" spans="1:10" ht="75" x14ac:dyDescent="0.2">
-      <c r="A64" s="394"/>
-      <c r="B64" s="429"/>
-      <c r="C64" s="440"/>
+      <c r="A64" s="414"/>
+      <c r="B64" s="428"/>
+      <c r="C64" s="431"/>
       <c r="D64" s="73" t="s">
         <v>79</v>
       </c>
@@ -50196,9 +50197,9 @@
       </c>
     </row>
     <row r="65" spans="1:133" ht="60" x14ac:dyDescent="0.2">
-      <c r="A65" s="394"/>
-      <c r="B65" s="429"/>
-      <c r="C65" s="440"/>
+      <c r="A65" s="414"/>
+      <c r="B65" s="428"/>
+      <c r="C65" s="431"/>
       <c r="D65" s="73" t="s">
         <v>83</v>
       </c>
@@ -50220,9 +50221,9 @@
       </c>
     </row>
     <row r="66" spans="1:133" s="47" customFormat="1" ht="48" x14ac:dyDescent="0.2">
-      <c r="A66" s="394"/>
-      <c r="B66" s="429"/>
-      <c r="C66" s="440"/>
+      <c r="A66" s="414"/>
+      <c r="B66" s="428"/>
+      <c r="C66" s="431"/>
       <c r="D66" s="73" t="s">
         <v>114</v>
       </c>
@@ -50367,9 +50368,9 @@
       <c r="EC66" s="36"/>
     </row>
     <row r="67" spans="1:133" s="47" customFormat="1" ht="30" x14ac:dyDescent="0.2">
-      <c r="A67" s="394"/>
-      <c r="B67" s="429"/>
-      <c r="C67" s="440"/>
+      <c r="A67" s="414"/>
+      <c r="B67" s="428"/>
+      <c r="C67" s="431"/>
       <c r="D67" s="73" t="s">
         <v>92</v>
       </c>
@@ -50514,9 +50515,9 @@
       <c r="EC67" s="36"/>
     </row>
     <row r="68" spans="1:133" ht="30" x14ac:dyDescent="0.2">
-      <c r="A68" s="395"/>
-      <c r="B68" s="430"/>
-      <c r="C68" s="440"/>
+      <c r="A68" s="415"/>
+      <c r="B68" s="429"/>
+      <c r="C68" s="431"/>
       <c r="D68" s="73" t="s">
         <v>94</v>
       </c>
@@ -50538,32 +50539,32 @@
   </sheetData>
   <autoFilter ref="A2:EC43" xr:uid="{92218EDD-6442-41B5-9565-D949ECDDA5BC}"/>
   <mergeCells count="26">
-    <mergeCell ref="A59:A68"/>
-    <mergeCell ref="B59:B68"/>
-    <mergeCell ref="C59:C68"/>
-    <mergeCell ref="D62:D63"/>
-    <mergeCell ref="E62:E63"/>
-    <mergeCell ref="A16:A25"/>
-    <mergeCell ref="B16:B25"/>
-    <mergeCell ref="C16:C25"/>
-    <mergeCell ref="D19:D20"/>
-    <mergeCell ref="E19:E20"/>
-    <mergeCell ref="A1:G1"/>
-    <mergeCell ref="I1:J1"/>
-    <mergeCell ref="A4:A15"/>
-    <mergeCell ref="B4:B15"/>
-    <mergeCell ref="C4:C15"/>
-    <mergeCell ref="D29:D30"/>
-    <mergeCell ref="E29:E30"/>
-    <mergeCell ref="A36:A45"/>
-    <mergeCell ref="B36:B45"/>
-    <mergeCell ref="C36:C45"/>
     <mergeCell ref="A47:A58"/>
     <mergeCell ref="B47:B58"/>
     <mergeCell ref="C47:C58"/>
     <mergeCell ref="A26:A35"/>
     <mergeCell ref="B26:B35"/>
     <mergeCell ref="C26:C35"/>
+    <mergeCell ref="D29:D30"/>
+    <mergeCell ref="E29:E30"/>
+    <mergeCell ref="A36:A45"/>
+    <mergeCell ref="B36:B45"/>
+    <mergeCell ref="C36:C45"/>
+    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="I1:J1"/>
+    <mergeCell ref="A4:A15"/>
+    <mergeCell ref="B4:B15"/>
+    <mergeCell ref="C4:C15"/>
+    <mergeCell ref="A16:A25"/>
+    <mergeCell ref="B16:B25"/>
+    <mergeCell ref="C16:C25"/>
+    <mergeCell ref="D19:D20"/>
+    <mergeCell ref="E19:E20"/>
+    <mergeCell ref="A59:A68"/>
+    <mergeCell ref="B59:B68"/>
+    <mergeCell ref="C59:C68"/>
+    <mergeCell ref="D62:D63"/>
+    <mergeCell ref="E62:E63"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait"/>
@@ -50710,10 +50711,10 @@
       </c>
     </row>
     <row r="4" spans="1:5" ht="64" x14ac:dyDescent="0.2">
-      <c r="A4" s="443">
+      <c r="A4" s="444">
         <v>1</v>
       </c>
-      <c r="B4" s="444" t="s">
+      <c r="B4" s="445" t="s">
         <v>152</v>
       </c>
       <c r="C4" s="365" t="s">
@@ -50728,8 +50729,8 @@
       </c>
     </row>
     <row r="5" spans="1:5" ht="80" x14ac:dyDescent="0.2">
-      <c r="A5" s="443"/>
-      <c r="B5" s="445"/>
+      <c r="A5" s="444"/>
+      <c r="B5" s="446"/>
       <c r="C5" s="365" t="s">
         <v>239</v>
       </c>
@@ -50742,10 +50743,10 @@
       </c>
     </row>
     <row r="6" spans="1:5" ht="64" x14ac:dyDescent="0.2">
-      <c r="A6" s="443">
+      <c r="A6" s="444">
         <v>2</v>
       </c>
-      <c r="B6" s="445"/>
+      <c r="B6" s="446"/>
       <c r="C6" s="366" t="s">
         <v>241</v>
       </c>
@@ -50758,8 +50759,8 @@
       </c>
     </row>
     <row r="7" spans="1:5" ht="112" x14ac:dyDescent="0.2">
-      <c r="A7" s="444"/>
-      <c r="B7" s="446"/>
+      <c r="A7" s="445"/>
+      <c r="B7" s="447"/>
       <c r="C7" s="366" t="s">
         <v>243</v>
       </c>
@@ -50772,10 +50773,10 @@
       </c>
     </row>
     <row r="8" spans="1:5" ht="45" x14ac:dyDescent="0.2">
-      <c r="A8" s="447">
+      <c r="A8" s="448">
         <v>3</v>
       </c>
-      <c r="B8" s="447" t="s">
+      <c r="B8" s="448" t="s">
         <v>245</v>
       </c>
       <c r="C8" s="370" t="s">
@@ -50790,8 +50791,8 @@
       </c>
     </row>
     <row r="9" spans="1:5" ht="45" x14ac:dyDescent="0.2">
-      <c r="A9" s="448"/>
-      <c r="B9" s="448"/>
+      <c r="A9" s="449"/>
+      <c r="B9" s="449"/>
       <c r="C9" s="370" t="s">
         <v>248</v>
       </c>
@@ -50804,8 +50805,8 @@
       </c>
     </row>
     <row r="10" spans="1:5" ht="45" x14ac:dyDescent="0.2">
-      <c r="A10" s="448"/>
-      <c r="B10" s="448"/>
+      <c r="A10" s="449"/>
+      <c r="B10" s="449"/>
       <c r="C10" s="370" t="s">
         <v>250</v>
       </c>
@@ -50818,8 +50819,8 @@
       </c>
     </row>
     <row r="11" spans="1:5" ht="64" x14ac:dyDescent="0.2">
-      <c r="A11" s="449"/>
-      <c r="B11" s="449"/>
+      <c r="A11" s="450"/>
+      <c r="B11" s="450"/>
       <c r="C11" s="371" t="s">
         <v>252</v>
       </c>
@@ -50832,10 +50833,10 @@
       </c>
     </row>
     <row r="12" spans="1:5" ht="60" x14ac:dyDescent="0.2">
-      <c r="A12" s="441">
+      <c r="A12" s="442">
         <v>4</v>
       </c>
-      <c r="B12" s="442" t="s">
+      <c r="B12" s="443" t="s">
         <v>254</v>
       </c>
       <c r="C12" s="370" t="s">
@@ -50850,8 +50851,8 @@
       </c>
     </row>
     <row r="13" spans="1:5" ht="48" x14ac:dyDescent="0.2">
-      <c r="A13" s="441"/>
-      <c r="B13" s="442"/>
+      <c r="A13" s="442"/>
+      <c r="B13" s="443"/>
       <c r="C13" s="370" t="s">
         <v>154</v>
       </c>
@@ -50910,11 +50911,11 @@
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A4" s="4"/>
-      <c r="B4" s="452" t="s">
+      <c r="B4" s="453" t="s">
         <v>157</v>
       </c>
-      <c r="C4" s="453"/>
-      <c r="D4" s="454"/>
+      <c r="C4" s="454"/>
+      <c r="D4" s="455"/>
       <c r="E4" s="153" t="s">
         <v>158</v>
       </c>
@@ -50937,12 +50938,12 @@
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="B7" s="455" t="s">
+      <c r="B7" s="456" t="s">
         <v>163</v>
       </c>
-      <c r="C7" s="455"/>
-      <c r="D7" s="455"/>
-      <c r="E7" s="455"/>
+      <c r="C7" s="456"/>
+      <c r="D7" s="456"/>
+      <c r="E7" s="456"/>
       <c r="F7" s="222"/>
     </row>
     <row r="8" spans="1:6" ht="16" x14ac:dyDescent="0.2">
@@ -51010,12 +51011,12 @@
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="B12" s="455" t="s">
+      <c r="B12" s="456" t="s">
         <v>175</v>
       </c>
-      <c r="C12" s="455"/>
-      <c r="D12" s="455"/>
-      <c r="E12" s="455"/>
+      <c r="C12" s="456"/>
+      <c r="D12" s="456"/>
+      <c r="E12" s="456"/>
       <c r="F12" s="223"/>
     </row>
     <row r="13" spans="1:6" ht="80" x14ac:dyDescent="0.2">
@@ -51263,46 +51264,46 @@
       </c>
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="C35" s="456" t="s">
+      <c r="C35" s="457" t="s">
         <v>125</v>
       </c>
-      <c r="D35" s="457" t="s">
+      <c r="D35" s="458" t="s">
         <v>259</v>
       </c>
-      <c r="E35" s="456" t="s">
+      <c r="E35" s="457" t="s">
         <v>205</v>
       </c>
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="C36" s="456"/>
-      <c r="D36" s="457"/>
-      <c r="E36" s="456"/>
+      <c r="C36" s="457"/>
+      <c r="D36" s="458"/>
+      <c r="E36" s="457"/>
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="C37" s="456"/>
-      <c r="D37" s="457"/>
-      <c r="E37" s="456"/>
+      <c r="C37" s="457"/>
+      <c r="D37" s="458"/>
+      <c r="E37" s="457"/>
     </row>
     <row r="38" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="C38" s="450" t="s">
+      <c r="C38" s="451" t="s">
         <v>133</v>
       </c>
-      <c r="D38" s="451" t="s">
+      <c r="D38" s="452" t="s">
         <v>206</v>
       </c>
-      <c r="E38" s="450" t="s">
+      <c r="E38" s="451" t="s">
         <v>205</v>
       </c>
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="C39" s="450"/>
-      <c r="D39" s="451"/>
-      <c r="E39" s="450"/>
+      <c r="C39" s="451"/>
+      <c r="D39" s="452"/>
+      <c r="E39" s="451"/>
     </row>
     <row r="40" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="C40" s="450"/>
-      <c r="D40" s="451"/>
-      <c r="E40" s="450"/>
+      <c r="C40" s="451"/>
+      <c r="D40" s="452"/>
+      <c r="E40" s="451"/>
     </row>
     <row r="41" spans="1:5" x14ac:dyDescent="0.2">
       <c r="C41" s="251" t="s">
@@ -51549,8 +51550,8 @@
       <c r="F1" s="188"/>
       <c r="G1" s="188"/>
       <c r="H1" s="105"/>
-      <c r="I1" s="413"/>
-      <c r="J1" s="413"/>
+      <c r="I1" s="394"/>
+      <c r="J1" s="394"/>
       <c r="L1" s="30"/>
       <c r="M1" s="30"/>
     </row>
@@ -51735,13 +51736,13 @@
       <c r="EH3" s="36"/>
     </row>
     <row r="4" spans="1:138" ht="44.25" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="414">
+      <c r="A4" s="395">
         <v>1</v>
       </c>
-      <c r="B4" s="416" t="s">
+      <c r="B4" s="397" t="s">
         <v>50</v>
       </c>
-      <c r="C4" s="418" t="s">
+      <c r="C4" s="399" t="s">
         <v>51</v>
       </c>
       <c r="D4" s="73" t="s">
@@ -51769,9 +51770,9 @@
       </c>
     </row>
     <row r="5" spans="1:138" ht="30" outlineLevel="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="415"/>
-      <c r="B5" s="417"/>
-      <c r="C5" s="419"/>
+      <c r="A5" s="396"/>
+      <c r="B5" s="398"/>
+      <c r="C5" s="400"/>
       <c r="D5" s="73" t="s">
         <v>56</v>
       </c>
@@ -51793,9 +51794,9 @@
       <c r="M5" s="76"/>
     </row>
     <row r="6" spans="1:138" ht="48" outlineLevel="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="415"/>
-      <c r="B6" s="417"/>
-      <c r="C6" s="419"/>
+      <c r="A6" s="396"/>
+      <c r="B6" s="398"/>
+      <c r="C6" s="400"/>
       <c r="D6" s="73" t="s">
         <v>55</v>
       </c>
@@ -51820,9 +51821,9 @@
       </c>
     </row>
     <row r="7" spans="1:138" ht="144" outlineLevel="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="415"/>
-      <c r="B7" s="417"/>
-      <c r="C7" s="419"/>
+      <c r="A7" s="396"/>
+      <c r="B7" s="398"/>
+      <c r="C7" s="400"/>
       <c r="D7" s="73" t="s">
         <v>63</v>
       </c>
@@ -51845,9 +51846,9 @@
       <c r="M7" s="76"/>
     </row>
     <row r="8" spans="1:138" ht="108" outlineLevel="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="415"/>
-      <c r="B8" s="417"/>
-      <c r="C8" s="419"/>
+      <c r="A8" s="396"/>
+      <c r="B8" s="398"/>
+      <c r="C8" s="400"/>
       <c r="D8" s="73" t="s">
         <v>68</v>
       </c>
@@ -51869,9 +51870,9 @@
       <c r="M8" s="76"/>
     </row>
     <row r="9" spans="1:138" ht="36" outlineLevel="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="415"/>
-      <c r="B9" s="417"/>
-      <c r="C9" s="419"/>
+      <c r="A9" s="396"/>
+      <c r="B9" s="398"/>
+      <c r="C9" s="400"/>
       <c r="D9" s="73" t="s">
         <v>72</v>
       </c>
@@ -51893,9 +51894,9 @@
       <c r="M9" s="76"/>
     </row>
     <row r="10" spans="1:138" ht="48" outlineLevel="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="415"/>
-      <c r="B10" s="417"/>
-      <c r="C10" s="419"/>
+      <c r="A10" s="396"/>
+      <c r="B10" s="398"/>
+      <c r="C10" s="400"/>
       <c r="D10" s="73" t="s">
         <v>86</v>
       </c>
@@ -51919,9 +51920,9 @@
       <c r="M10" s="76"/>
     </row>
     <row r="11" spans="1:138" s="42" customFormat="1" ht="30" outlineLevel="1" x14ac:dyDescent="0.2">
-      <c r="A11" s="415"/>
-      <c r="B11" s="417"/>
-      <c r="C11" s="419"/>
+      <c r="A11" s="396"/>
+      <c r="B11" s="398"/>
+      <c r="C11" s="400"/>
       <c r="D11" s="73" t="s">
         <v>92</v>
       </c>
@@ -52071,9 +52072,9 @@
       <c r="EH11" s="41"/>
     </row>
     <row r="12" spans="1:138" ht="60" outlineLevel="1" x14ac:dyDescent="0.2">
-      <c r="A12" s="415"/>
-      <c r="B12" s="417"/>
-      <c r="C12" s="420"/>
+      <c r="A12" s="396"/>
+      <c r="B12" s="398"/>
+      <c r="C12" s="401"/>
       <c r="D12" s="73" t="s">
         <v>277</v>
       </c>
@@ -52094,14 +52095,14 @@
       <c r="L12" s="76"/>
       <c r="M12" s="76"/>
     </row>
-    <row r="13" spans="1:138" ht="36" outlineLevel="1" x14ac:dyDescent="0.2">
-      <c r="A13" s="406">
+    <row r="13" spans="1:138" ht="45" outlineLevel="1" x14ac:dyDescent="0.2">
+      <c r="A13" s="402">
         <v>1.1000000000000001</v>
       </c>
-      <c r="B13" s="407" t="s">
+      <c r="B13" s="403" t="s">
         <v>98</v>
       </c>
-      <c r="C13" s="421" t="s">
+      <c r="C13" s="404" t="s">
         <v>99</v>
       </c>
       <c r="D13" s="73" t="s">
@@ -52127,9 +52128,9 @@
       <c r="M13" s="76"/>
     </row>
     <row r="14" spans="1:138" ht="60" outlineLevel="1" x14ac:dyDescent="0.2">
-      <c r="A14" s="406"/>
-      <c r="B14" s="407"/>
-      <c r="C14" s="422"/>
+      <c r="A14" s="402"/>
+      <c r="B14" s="403"/>
+      <c r="C14" s="405"/>
       <c r="D14" s="73" t="s">
         <v>56</v>
       </c>
@@ -52155,9 +52156,9 @@
       <c r="M14" s="76"/>
     </row>
     <row r="15" spans="1:138" ht="409.6" outlineLevel="1" x14ac:dyDescent="0.2">
-      <c r="A15" s="406"/>
-      <c r="B15" s="407"/>
-      <c r="C15" s="422"/>
+      <c r="A15" s="402"/>
+      <c r="B15" s="403"/>
+      <c r="C15" s="405"/>
       <c r="D15" s="73" t="s">
         <v>279</v>
       </c>
@@ -52204,9 +52205,9 @@
       <c r="M15" s="76"/>
     </row>
     <row r="16" spans="1:138" ht="30" outlineLevel="1" x14ac:dyDescent="0.2">
-      <c r="A16" s="406"/>
-      <c r="B16" s="407"/>
-      <c r="C16" s="422"/>
+      <c r="A16" s="402"/>
+      <c r="B16" s="403"/>
+      <c r="C16" s="405"/>
       <c r="D16" s="73" t="s">
         <v>281</v>
       </c>
@@ -52225,9 +52226,9 @@
       <c r="M16" s="76"/>
     </row>
     <row r="17" spans="1:138" s="47" customFormat="1" ht="409.6" outlineLevel="1" x14ac:dyDescent="0.2">
-      <c r="A17" s="406"/>
-      <c r="B17" s="407"/>
-      <c r="C17" s="422"/>
+      <c r="A17" s="402"/>
+      <c r="B17" s="403"/>
+      <c r="C17" s="405"/>
       <c r="D17" s="73" t="s">
         <v>106</v>
       </c>
@@ -52388,9 +52389,9 @@
       <c r="EH17" s="36"/>
     </row>
     <row r="18" spans="1:138" s="47" customFormat="1" ht="409.6" outlineLevel="1" x14ac:dyDescent="0.2">
-      <c r="A18" s="406"/>
-      <c r="B18" s="407"/>
-      <c r="C18" s="422"/>
+      <c r="A18" s="402"/>
+      <c r="B18" s="403"/>
+      <c r="C18" s="405"/>
       <c r="D18" s="73" t="s">
         <v>92</v>
       </c>
@@ -52551,9 +52552,9 @@
       <c r="EH18" s="36"/>
     </row>
     <row r="19" spans="1:138" ht="60" outlineLevel="1" x14ac:dyDescent="0.2">
-      <c r="A19" s="414"/>
-      <c r="B19" s="416"/>
-      <c r="C19" s="422"/>
+      <c r="A19" s="395"/>
+      <c r="B19" s="397"/>
+      <c r="C19" s="405"/>
       <c r="D19" s="189" t="s">
         <v>277</v>
       </c>
@@ -52575,10 +52576,10 @@
       <c r="M19" s="76"/>
     </row>
     <row r="20" spans="1:138" ht="45" outlineLevel="1" x14ac:dyDescent="0.2">
-      <c r="A20" s="458">
+      <c r="A20" s="459">
         <v>2</v>
       </c>
-      <c r="B20" s="459" t="s">
+      <c r="B20" s="460" t="s">
         <v>109</v>
       </c>
       <c r="C20" s="461" t="s">
@@ -52607,8 +52608,8 @@
       <c r="M20" s="76"/>
     </row>
     <row r="21" spans="1:138" ht="60" outlineLevel="1" x14ac:dyDescent="0.2">
-      <c r="A21" s="458"/>
-      <c r="B21" s="459"/>
+      <c r="A21" s="459"/>
+      <c r="B21" s="460"/>
       <c r="C21" s="461"/>
       <c r="D21" s="73" t="s">
         <v>56</v>
@@ -52635,8 +52636,8 @@
       <c r="M21" s="76"/>
     </row>
     <row r="22" spans="1:138" ht="409.6" outlineLevel="1" x14ac:dyDescent="0.2">
-      <c r="A22" s="458"/>
-      <c r="B22" s="459"/>
+      <c r="A22" s="459"/>
+      <c r="B22" s="460"/>
       <c r="C22" s="461"/>
       <c r="D22" s="189" t="s">
         <v>279</v>
@@ -52668,8 +52669,8 @@
       <c r="M22" s="76"/>
     </row>
     <row r="23" spans="1:138" ht="30" outlineLevel="1" x14ac:dyDescent="0.2">
-      <c r="A23" s="458"/>
-      <c r="B23" s="459"/>
+      <c r="A23" s="459"/>
+      <c r="B23" s="460"/>
       <c r="C23" s="462"/>
       <c r="D23" s="73" t="s">
         <v>281</v>
@@ -52688,8 +52689,8 @@
       <c r="M23" s="76"/>
     </row>
     <row r="24" spans="1:138" s="47" customFormat="1" ht="409.6" outlineLevel="1" x14ac:dyDescent="0.2">
-      <c r="A24" s="458"/>
-      <c r="B24" s="459"/>
+      <c r="A24" s="459"/>
+      <c r="B24" s="460"/>
       <c r="C24" s="461"/>
       <c r="D24" s="271" t="s">
         <v>114</v>
@@ -52847,8 +52848,8 @@
       <c r="EH24" s="36"/>
     </row>
     <row r="25" spans="1:138" s="47" customFormat="1" ht="409.6" outlineLevel="1" x14ac:dyDescent="0.2">
-      <c r="A25" s="458"/>
-      <c r="B25" s="459"/>
+      <c r="A25" s="459"/>
+      <c r="B25" s="460"/>
       <c r="C25" s="461"/>
       <c r="D25" s="272" t="s">
         <v>92</v>
@@ -53006,8 +53007,8 @@
       <c r="EH25" s="36"/>
     </row>
     <row r="26" spans="1:138" ht="196.5" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.2">
-      <c r="A26" s="458"/>
-      <c r="B26" s="459"/>
+      <c r="A26" s="459"/>
+      <c r="B26" s="460"/>
       <c r="C26" s="462"/>
       <c r="D26" s="73" t="s">
         <v>94</v>
@@ -53030,13 +53031,13 @@
       <c r="M26" s="76"/>
     </row>
     <row r="27" spans="1:138" ht="60" outlineLevel="1" x14ac:dyDescent="0.2">
-      <c r="A27" s="393">
+      <c r="A27" s="413">
         <v>2.1</v>
       </c>
-      <c r="B27" s="396" t="s">
+      <c r="B27" s="416" t="s">
         <v>116</v>
       </c>
-      <c r="C27" s="410" t="s">
+      <c r="C27" s="419" t="s">
         <v>117</v>
       </c>
       <c r="D27" s="73" t="s">
@@ -53062,9 +53063,9 @@
       <c r="M27" s="76"/>
     </row>
     <row r="28" spans="1:138" ht="60" outlineLevel="1" x14ac:dyDescent="0.2">
-      <c r="A28" s="394"/>
-      <c r="B28" s="397"/>
-      <c r="C28" s="411"/>
+      <c r="A28" s="414"/>
+      <c r="B28" s="417"/>
+      <c r="C28" s="420"/>
       <c r="D28" s="73" t="s">
         <v>122</v>
       </c>
@@ -53084,9 +53085,9 @@
       <c r="M28" s="76"/>
     </row>
     <row r="29" spans="1:138" ht="84" outlineLevel="1" x14ac:dyDescent="0.2">
-      <c r="A29" s="394"/>
-      <c r="B29" s="397"/>
-      <c r="C29" s="411"/>
+      <c r="A29" s="414"/>
+      <c r="B29" s="417"/>
+      <c r="C29" s="420"/>
       <c r="D29" s="73" t="s">
         <v>130</v>
       </c>
@@ -53110,9 +53111,9 @@
       <c r="M29" s="76"/>
     </row>
     <row r="30" spans="1:138" ht="60" outlineLevel="1" x14ac:dyDescent="0.2">
-      <c r="A30" s="394"/>
-      <c r="B30" s="397"/>
-      <c r="C30" s="411"/>
+      <c r="A30" s="414"/>
+      <c r="B30" s="417"/>
+      <c r="C30" s="420"/>
       <c r="D30" s="189" t="s">
         <v>55</v>
       </c>
@@ -53136,9 +53137,9 @@
       <c r="M30" s="76"/>
     </row>
     <row r="31" spans="1:138" ht="36" outlineLevel="1" x14ac:dyDescent="0.2">
-      <c r="A31" s="394"/>
-      <c r="B31" s="397"/>
-      <c r="C31" s="411"/>
+      <c r="A31" s="414"/>
+      <c r="B31" s="417"/>
+      <c r="C31" s="420"/>
       <c r="D31" s="73" t="s">
         <v>134</v>
       </c>
@@ -53162,9 +53163,9 @@
       </c>
     </row>
     <row r="32" spans="1:138" ht="48" outlineLevel="1" x14ac:dyDescent="0.2">
-      <c r="A32" s="394"/>
-      <c r="B32" s="397"/>
-      <c r="C32" s="411"/>
+      <c r="A32" s="414"/>
+      <c r="B32" s="417"/>
+      <c r="C32" s="420"/>
       <c r="D32" s="271" t="s">
         <v>114</v>
       </c>
@@ -53188,9 +53189,9 @@
       <c r="M32" s="76"/>
     </row>
     <row r="33" spans="1:13" ht="30" outlineLevel="1" x14ac:dyDescent="0.2">
-      <c r="A33" s="394"/>
-      <c r="B33" s="397"/>
-      <c r="C33" s="411"/>
+      <c r="A33" s="414"/>
+      <c r="B33" s="417"/>
+      <c r="C33" s="420"/>
       <c r="D33" s="272" t="s">
         <v>92</v>
       </c>
@@ -53214,9 +53215,9 @@
       <c r="M33" s="76"/>
     </row>
     <row r="34" spans="1:13" ht="45" outlineLevel="1" x14ac:dyDescent="0.2">
-      <c r="A34" s="395"/>
-      <c r="B34" s="398"/>
-      <c r="C34" s="412"/>
+      <c r="A34" s="415"/>
+      <c r="B34" s="418"/>
+      <c r="C34" s="421"/>
       <c r="D34" s="73" t="s">
         <v>94</v>
       </c>
@@ -53256,10 +53257,10 @@
       <c r="M35" s="76"/>
     </row>
     <row r="36" spans="1:13" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A36" s="414">
+      <c r="A36" s="395">
         <v>1</v>
       </c>
-      <c r="B36" s="416" t="s">
+      <c r="B36" s="397" t="s">
         <v>50</v>
       </c>
       <c r="C36" s="463" t="s">
@@ -53284,8 +53285,8 @@
       </c>
     </row>
     <row r="37" spans="1:13" ht="30" x14ac:dyDescent="0.2">
-      <c r="A37" s="415"/>
-      <c r="B37" s="417"/>
+      <c r="A37" s="396"/>
+      <c r="B37" s="398"/>
       <c r="C37" s="464"/>
       <c r="D37" s="73" t="s">
         <v>56</v>
@@ -53306,8 +53307,8 @@
       </c>
     </row>
     <row r="38" spans="1:13" ht="48" x14ac:dyDescent="0.2">
-      <c r="A38" s="415"/>
-      <c r="B38" s="417"/>
+      <c r="A38" s="396"/>
+      <c r="B38" s="398"/>
       <c r="C38" s="464"/>
       <c r="D38" s="73" t="s">
         <v>55</v>
@@ -53328,8 +53329,8 @@
       </c>
     </row>
     <row r="39" spans="1:13" ht="144" x14ac:dyDescent="0.2">
-      <c r="A39" s="415"/>
-      <c r="B39" s="417"/>
+      <c r="A39" s="396"/>
+      <c r="B39" s="398"/>
       <c r="C39" s="464"/>
       <c r="D39" s="73" t="s">
         <v>63</v>
@@ -53350,8 +53351,8 @@
       </c>
     </row>
     <row r="40" spans="1:13" ht="108" x14ac:dyDescent="0.2">
-      <c r="A40" s="415"/>
-      <c r="B40" s="417"/>
+      <c r="A40" s="396"/>
+      <c r="B40" s="398"/>
       <c r="C40" s="464"/>
       <c r="D40" s="73" t="s">
         <v>68</v>
@@ -53372,8 +53373,8 @@
       </c>
     </row>
     <row r="41" spans="1:13" ht="36" x14ac:dyDescent="0.2">
-      <c r="A41" s="415"/>
-      <c r="B41" s="417"/>
+      <c r="A41" s="396"/>
+      <c r="B41" s="398"/>
       <c r="C41" s="464"/>
       <c r="D41" s="73" t="s">
         <v>72</v>
@@ -53394,8 +53395,8 @@
       </c>
     </row>
     <row r="42" spans="1:13" ht="48" x14ac:dyDescent="0.2">
-      <c r="A42" s="415"/>
-      <c r="B42" s="417"/>
+      <c r="A42" s="396"/>
+      <c r="B42" s="398"/>
       <c r="C42" s="464"/>
       <c r="D42" s="73" t="s">
         <v>86</v>
@@ -53418,8 +53419,8 @@
       </c>
     </row>
     <row r="43" spans="1:13" ht="30" x14ac:dyDescent="0.2">
-      <c r="A43" s="415"/>
-      <c r="B43" s="417"/>
+      <c r="A43" s="396"/>
+      <c r="B43" s="398"/>
       <c r="C43" s="464"/>
       <c r="D43" s="73" t="s">
         <v>92</v>
@@ -53442,8 +53443,8 @@
       </c>
     </row>
     <row r="44" spans="1:13" ht="60" x14ac:dyDescent="0.2">
-      <c r="A44" s="415"/>
-      <c r="B44" s="417"/>
+      <c r="A44" s="396"/>
+      <c r="B44" s="398"/>
       <c r="C44" s="464"/>
       <c r="D44" s="73" t="s">
         <v>277</v>
@@ -53464,13 +53465,13 @@
       </c>
     </row>
     <row r="45" spans="1:13" ht="36" x14ac:dyDescent="0.2">
-      <c r="A45" s="406">
+      <c r="A45" s="402">
         <v>1.1000000000000001</v>
       </c>
-      <c r="B45" s="407" t="s">
+      <c r="B45" s="403" t="s">
         <v>98</v>
       </c>
-      <c r="C45" s="421" t="s">
+      <c r="C45" s="404" t="s">
         <v>99</v>
       </c>
       <c r="D45" s="73" t="s">
@@ -53492,9 +53493,9 @@
       </c>
     </row>
     <row r="46" spans="1:13" ht="30" x14ac:dyDescent="0.2">
-      <c r="A46" s="406"/>
-      <c r="B46" s="407"/>
-      <c r="C46" s="422"/>
+      <c r="A46" s="402"/>
+      <c r="B46" s="403"/>
+      <c r="C46" s="405"/>
       <c r="D46" s="73" t="s">
         <v>56</v>
       </c>
@@ -53516,9 +53517,9 @@
       </c>
     </row>
     <row r="47" spans="1:13" ht="409.6" x14ac:dyDescent="0.2">
-      <c r="A47" s="406"/>
-      <c r="B47" s="407"/>
-      <c r="C47" s="422"/>
+      <c r="A47" s="402"/>
+      <c r="B47" s="403"/>
+      <c r="C47" s="405"/>
       <c r="D47" s="73" t="s">
         <v>279</v>
       </c>
@@ -53562,9 +53563,9 @@
       </c>
     </row>
     <row r="48" spans="1:13" ht="30" x14ac:dyDescent="0.2">
-      <c r="A48" s="406"/>
-      <c r="B48" s="407"/>
-      <c r="C48" s="422"/>
+      <c r="A48" s="402"/>
+      <c r="B48" s="403"/>
+      <c r="C48" s="405"/>
       <c r="D48" s="73" t="s">
         <v>281</v>
       </c>
@@ -53580,9 +53581,9 @@
       </c>
     </row>
     <row r="49" spans="1:10" ht="409.6" x14ac:dyDescent="0.2">
-      <c r="A49" s="406"/>
-      <c r="B49" s="407"/>
-      <c r="C49" s="422"/>
+      <c r="A49" s="402"/>
+      <c r="B49" s="403"/>
+      <c r="C49" s="405"/>
       <c r="D49" s="73" t="s">
         <v>106</v>
       </c>
@@ -53615,9 +53616,9 @@
       </c>
     </row>
     <row r="50" spans="1:10" ht="409.6" x14ac:dyDescent="0.2">
-      <c r="A50" s="406"/>
-      <c r="B50" s="407"/>
-      <c r="C50" s="422"/>
+      <c r="A50" s="402"/>
+      <c r="B50" s="403"/>
+      <c r="C50" s="405"/>
       <c r="D50" s="73" t="s">
         <v>92</v>
       </c>
@@ -53650,9 +53651,9 @@
       </c>
     </row>
     <row r="51" spans="1:10" ht="60" x14ac:dyDescent="0.2">
-      <c r="A51" s="414"/>
-      <c r="B51" s="416"/>
-      <c r="C51" s="422"/>
+      <c r="A51" s="395"/>
+      <c r="B51" s="397"/>
+      <c r="C51" s="405"/>
       <c r="D51" s="189" t="s">
         <v>277</v>
       </c>
@@ -53672,13 +53673,13 @@
       </c>
     </row>
     <row r="52" spans="1:10" ht="36" x14ac:dyDescent="0.2">
-      <c r="A52" s="458">
+      <c r="A52" s="459">
         <v>2</v>
       </c>
-      <c r="B52" s="459" t="s">
+      <c r="B52" s="460" t="s">
         <v>109</v>
       </c>
-      <c r="C52" s="460" t="s">
+      <c r="C52" s="465" t="s">
         <v>292</v>
       </c>
       <c r="D52" s="73" t="s">
@@ -53700,8 +53701,8 @@
       </c>
     </row>
     <row r="53" spans="1:10" ht="409.6" x14ac:dyDescent="0.2">
-      <c r="A53" s="458"/>
-      <c r="B53" s="459"/>
+      <c r="A53" s="459"/>
+      <c r="B53" s="460"/>
       <c r="C53" s="461"/>
       <c r="D53" s="37" t="s">
         <v>293</v>
@@ -53731,8 +53732,8 @@
       </c>
     </row>
     <row r="54" spans="1:10" ht="30" x14ac:dyDescent="0.2">
-      <c r="A54" s="458"/>
-      <c r="B54" s="459"/>
+      <c r="A54" s="459"/>
+      <c r="B54" s="460"/>
       <c r="C54" s="461"/>
       <c r="D54" s="37" t="s">
         <v>295</v>
@@ -53753,8 +53754,8 @@
       </c>
     </row>
     <row r="55" spans="1:10" ht="409.6" x14ac:dyDescent="0.2">
-      <c r="A55" s="458"/>
-      <c r="B55" s="459"/>
+      <c r="A55" s="459"/>
+      <c r="B55" s="460"/>
       <c r="C55" s="461"/>
       <c r="D55" s="189" t="s">
         <v>279</v>
@@ -53784,8 +53785,8 @@
       </c>
     </row>
     <row r="56" spans="1:10" ht="30" x14ac:dyDescent="0.2">
-      <c r="A56" s="458"/>
-      <c r="B56" s="459"/>
+      <c r="A56" s="459"/>
+      <c r="B56" s="460"/>
       <c r="C56" s="462"/>
       <c r="D56" s="73" t="s">
         <v>281</v>
@@ -53802,8 +53803,8 @@
       </c>
     </row>
     <row r="57" spans="1:10" ht="409.6" x14ac:dyDescent="0.2">
-      <c r="A57" s="458"/>
-      <c r="B57" s="459"/>
+      <c r="A57" s="459"/>
+      <c r="B57" s="460"/>
       <c r="C57" s="461"/>
       <c r="D57" s="271" t="s">
         <v>114</v>
@@ -53833,8 +53834,8 @@
       </c>
     </row>
     <row r="58" spans="1:10" ht="409.6" x14ac:dyDescent="0.2">
-      <c r="A58" s="458"/>
-      <c r="B58" s="459"/>
+      <c r="A58" s="459"/>
+      <c r="B58" s="460"/>
       <c r="C58" s="461"/>
       <c r="D58" s="272" t="s">
         <v>92</v>
@@ -53864,8 +53865,8 @@
       </c>
     </row>
     <row r="59" spans="1:10" ht="45" x14ac:dyDescent="0.2">
-      <c r="A59" s="458"/>
-      <c r="B59" s="459"/>
+      <c r="A59" s="459"/>
+      <c r="B59" s="460"/>
       <c r="C59" s="462"/>
       <c r="D59" s="73" t="s">
         <v>94</v>
@@ -53886,13 +53887,13 @@
       </c>
     </row>
     <row r="60" spans="1:10" ht="60" x14ac:dyDescent="0.2">
-      <c r="A60" s="393">
+      <c r="A60" s="413">
         <v>2.1</v>
       </c>
-      <c r="B60" s="396" t="s">
+      <c r="B60" s="416" t="s">
         <v>116</v>
       </c>
-      <c r="C60" s="410" t="s">
+      <c r="C60" s="419" t="s">
         <v>117</v>
       </c>
       <c r="D60" s="73" t="s">
@@ -53914,9 +53915,9 @@
       </c>
     </row>
     <row r="61" spans="1:10" ht="60" x14ac:dyDescent="0.2">
-      <c r="A61" s="394"/>
-      <c r="B61" s="397"/>
-      <c r="C61" s="411"/>
+      <c r="A61" s="414"/>
+      <c r="B61" s="417"/>
+      <c r="C61" s="420"/>
       <c r="D61" s="73" t="s">
         <v>122</v>
       </c>
@@ -53934,9 +53935,9 @@
       </c>
     </row>
     <row r="62" spans="1:10" ht="84" x14ac:dyDescent="0.2">
-      <c r="A62" s="394"/>
-      <c r="B62" s="397"/>
-      <c r="C62" s="411"/>
+      <c r="A62" s="414"/>
+      <c r="B62" s="417"/>
+      <c r="C62" s="420"/>
       <c r="D62" s="73" t="s">
         <v>130</v>
       </c>
@@ -53956,9 +53957,9 @@
       </c>
     </row>
     <row r="63" spans="1:10" ht="60" x14ac:dyDescent="0.2">
-      <c r="A63" s="394"/>
-      <c r="B63" s="397"/>
-      <c r="C63" s="411"/>
+      <c r="A63" s="414"/>
+      <c r="B63" s="417"/>
+      <c r="C63" s="420"/>
       <c r="D63" s="189" t="s">
         <v>55</v>
       </c>
@@ -53980,9 +53981,9 @@
       </c>
     </row>
     <row r="64" spans="1:10" ht="36" x14ac:dyDescent="0.2">
-      <c r="A64" s="394"/>
-      <c r="B64" s="397"/>
-      <c r="C64" s="411"/>
+      <c r="A64" s="414"/>
+      <c r="B64" s="417"/>
+      <c r="C64" s="420"/>
       <c r="D64" s="73" t="s">
         <v>134</v>
       </c>
@@ -54000,9 +54001,9 @@
       </c>
     </row>
     <row r="65" spans="1:10" ht="48" x14ac:dyDescent="0.2">
-      <c r="A65" s="394"/>
-      <c r="B65" s="397"/>
-      <c r="C65" s="411"/>
+      <c r="A65" s="414"/>
+      <c r="B65" s="417"/>
+      <c r="C65" s="420"/>
       <c r="D65" s="271" t="s">
         <v>114</v>
       </c>
@@ -54024,9 +54025,9 @@
       </c>
     </row>
     <row r="66" spans="1:10" ht="30" x14ac:dyDescent="0.2">
-      <c r="A66" s="394"/>
-      <c r="B66" s="397"/>
-      <c r="C66" s="411"/>
+      <c r="A66" s="414"/>
+      <c r="B66" s="417"/>
+      <c r="C66" s="420"/>
       <c r="D66" s="272" t="s">
         <v>92</v>
       </c>
@@ -54048,9 +54049,9 @@
       </c>
     </row>
     <row r="67" spans="1:10" ht="45" x14ac:dyDescent="0.2">
-      <c r="A67" s="395"/>
-      <c r="B67" s="398"/>
-      <c r="C67" s="412"/>
+      <c r="A67" s="415"/>
+      <c r="B67" s="418"/>
+      <c r="C67" s="421"/>
       <c r="D67" s="73" t="s">
         <v>94</v>
       </c>
@@ -54072,6 +54073,24 @@
   </sheetData>
   <autoFilter ref="A2:EH34" xr:uid="{92218EDD-6442-41B5-9565-D949ECDDA5BC}"/>
   <mergeCells count="25">
+    <mergeCell ref="A52:A59"/>
+    <mergeCell ref="B52:B59"/>
+    <mergeCell ref="C52:C59"/>
+    <mergeCell ref="A60:A67"/>
+    <mergeCell ref="B60:B67"/>
+    <mergeCell ref="C60:C67"/>
+    <mergeCell ref="A36:A44"/>
+    <mergeCell ref="B36:B44"/>
+    <mergeCell ref="C36:C44"/>
+    <mergeCell ref="A45:A51"/>
+    <mergeCell ref="B45:B51"/>
+    <mergeCell ref="C45:C51"/>
+    <mergeCell ref="A20:A26"/>
+    <mergeCell ref="B20:B26"/>
+    <mergeCell ref="C20:C26"/>
+    <mergeCell ref="A27:A34"/>
+    <mergeCell ref="B27:B34"/>
+    <mergeCell ref="C27:C34"/>
     <mergeCell ref="I1:J1"/>
     <mergeCell ref="A4:A12"/>
     <mergeCell ref="B4:B12"/>
@@ -54079,24 +54098,6 @@
     <mergeCell ref="A13:A19"/>
     <mergeCell ref="B13:B19"/>
     <mergeCell ref="C13:C19"/>
-    <mergeCell ref="A20:A26"/>
-    <mergeCell ref="B20:B26"/>
-    <mergeCell ref="C20:C26"/>
-    <mergeCell ref="A27:A34"/>
-    <mergeCell ref="B27:B34"/>
-    <mergeCell ref="C27:C34"/>
-    <mergeCell ref="A36:A44"/>
-    <mergeCell ref="B36:B44"/>
-    <mergeCell ref="C36:C44"/>
-    <mergeCell ref="A45:A51"/>
-    <mergeCell ref="B45:B51"/>
-    <mergeCell ref="C45:C51"/>
-    <mergeCell ref="A52:A59"/>
-    <mergeCell ref="B52:B59"/>
-    <mergeCell ref="C52:C59"/>
-    <mergeCell ref="A60:A67"/>
-    <mergeCell ref="B60:B67"/>
-    <mergeCell ref="C60:C67"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait"/>
@@ -54135,11 +54136,11 @@
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A4" s="4"/>
-      <c r="B4" s="452" t="s">
+      <c r="B4" s="453" t="s">
         <v>157</v>
       </c>
-      <c r="C4" s="453"/>
-      <c r="D4" s="454"/>
+      <c r="C4" s="454"/>
+      <c r="D4" s="455"/>
       <c r="E4" s="153" t="s">
         <v>158</v>
       </c>
@@ -54162,12 +54163,12 @@
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="B7" s="455" t="s">
+      <c r="B7" s="456" t="s">
         <v>163</v>
       </c>
-      <c r="C7" s="455"/>
-      <c r="D7" s="455"/>
-      <c r="E7" s="455"/>
+      <c r="C7" s="456"/>
+      <c r="D7" s="456"/>
+      <c r="E7" s="456"/>
       <c r="F7" s="222"/>
     </row>
     <row r="8" spans="1:6" ht="16" x14ac:dyDescent="0.2">
@@ -54235,12 +54236,12 @@
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="B12" s="455" t="s">
+      <c r="B12" s="456" t="s">
         <v>175</v>
       </c>
-      <c r="C12" s="455"/>
-      <c r="D12" s="455"/>
-      <c r="E12" s="455"/>
+      <c r="C12" s="456"/>
+      <c r="D12" s="456"/>
+      <c r="E12" s="456"/>
       <c r="F12" s="223"/>
     </row>
     <row r="13" spans="1:6" ht="16" x14ac:dyDescent="0.2">
@@ -54647,51 +54648,51 @@
       </c>
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="C45" s="456" t="s">
+      <c r="C45" s="457" t="s">
         <v>125</v>
       </c>
-      <c r="D45" s="465" t="s">
+      <c r="D45" s="466" t="s">
         <v>259</v>
       </c>
-      <c r="E45" s="466" t="s">
+      <c r="E45" s="467" t="s">
         <v>205</v>
       </c>
       <c r="F45" s="250"/>
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="C46" s="456"/>
-      <c r="D46" s="465"/>
-      <c r="E46" s="466"/>
+      <c r="C46" s="457"/>
+      <c r="D46" s="466"/>
+      <c r="E46" s="467"/>
       <c r="F46" s="250"/>
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="C47" s="456"/>
-      <c r="D47" s="465"/>
-      <c r="E47" s="466"/>
+      <c r="C47" s="457"/>
+      <c r="D47" s="466"/>
+      <c r="E47" s="467"/>
       <c r="F47" s="250"/>
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="C48" s="450" t="s">
+      <c r="C48" s="451" t="s">
         <v>133</v>
       </c>
-      <c r="D48" s="450" t="s">
+      <c r="D48" s="451" t="s">
         <v>206</v>
       </c>
-      <c r="E48" s="451" t="s">
+      <c r="E48" s="452" t="s">
         <v>205</v>
       </c>
       <c r="F48" s="250"/>
     </row>
     <row r="49" spans="3:6" x14ac:dyDescent="0.2">
-      <c r="C49" s="450"/>
-      <c r="D49" s="450"/>
-      <c r="E49" s="451"/>
+      <c r="C49" s="451"/>
+      <c r="D49" s="451"/>
+      <c r="E49" s="452"/>
       <c r="F49" s="250"/>
     </row>
     <row r="50" spans="3:6" x14ac:dyDescent="0.2">
-      <c r="C50" s="450"/>
-      <c r="D50" s="450"/>
-      <c r="E50" s="451"/>
+      <c r="C50" s="451"/>
+      <c r="D50" s="451"/>
+      <c r="E50" s="452"/>
       <c r="F50" s="250"/>
     </row>
     <row r="51" spans="3:6" x14ac:dyDescent="0.2">
@@ -54799,15 +54800,6 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100F52F3FC1CD8EC649B3AFADF3835D38B7" ma:contentTypeVersion="0" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="585bd31a01b77638b6ff73c684db7301">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="500c6692915ba10984c0aabd49f31b22">
     <xsd:element name="properties">
@@ -54921,6 +54913,15 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FB3A44B8-EE3C-49AF-BF49-698BCE2C5CA8}">
   <ds:schemaRefs>
@@ -54931,14 +54932,6 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BEA3B3A7-4C5B-4FB5-B9FC-8D6E6D28CE9F}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{38A554B1-B6E8-4F95-B069-71B18B767B61}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -54954,6 +54947,14 @@
 </ds:datastoreItem>
 </file>
 
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BEA3B3A7-4C5B-4FB5-B9FC-8D6E6D28CE9F}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
 <file path=docMetadata/LabelInfo.xml><?xml version="1.0" encoding="utf-8"?>
 <clbl:labelList xmlns:clbl="http://schemas.microsoft.com/office/2020/mipLabelMetadata">
   <clbl:label id="{f01e930a-b52e-42b1-b70f-a8882b5d043b}" enabled="0" method="" siteId="{f01e930a-b52e-42b1-b70f-a8882b5d043b}" removed="1"/>
